--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -16121,7 +16121,7 @@
         <v>129108149</v>
       </c>
       <c r="B134" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16506,48 +16506,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129112796</v>
+        <v>129112087</v>
       </c>
       <c r="B138" t="n">
-        <v>102971</v>
+        <v>92847</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>223246</v>
+        <v>4366</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>707141</v>
+        <v>707031</v>
       </c>
       <c r="R138" t="n">
-        <v>6670348</v>
+        <v>6670179</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16603,48 +16603,48 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129112087</v>
+        <v>129112796</v>
       </c>
       <c r="B139" t="n">
-        <v>92844</v>
+        <v>102974</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4366</v>
+        <v>223246</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>707031</v>
+        <v>707141</v>
       </c>
       <c r="R139" t="n">
-        <v>6670179</v>
+        <v>6670348</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>129108341</v>
       </c>
       <c r="B140" t="n">
-        <v>98630</v>
+        <v>98633</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16806,45 +16806,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129114059</v>
+        <v>129110670</v>
       </c>
       <c r="B141" t="n">
-        <v>80149</v>
+        <v>91995</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>1619</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Apelticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Aurantiporus fissilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>707168</v>
+        <v>706880</v>
       </c>
       <c r="R141" t="n">
-        <v>6670669</v>
+        <v>6670333</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16899,49 +16899,53 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY141" t="inlineStr"/>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129110670</v>
+        <v>129114059</v>
       </c>
       <c r="B142" t="n">
-        <v>91992</v>
+        <v>80149</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1619</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Apelticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Aurantiporus fissilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>706880</v>
+        <v>707168</v>
       </c>
       <c r="R142" t="n">
-        <v>6670333</v>
+        <v>6670669</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16996,18 +17000,14 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY142" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
         <v>129112389</v>
       </c>
       <c r="B143" t="n">
-        <v>102971</v>
+        <v>102974</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17198,45 +17198,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129112698</v>
+        <v>129108937</v>
       </c>
       <c r="B145" t="n">
-        <v>86988</v>
+        <v>91326</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>460</v>
+        <v>3215</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>707129</v>
+        <v>707027</v>
       </c>
       <c r="R145" t="n">
-        <v>6670306</v>
+        <v>6670701</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17295,45 +17295,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129108937</v>
+        <v>129112698</v>
       </c>
       <c r="B146" t="n">
-        <v>91323</v>
+        <v>86988</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3215</v>
+        <v>460</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Cordier) Gillet</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>707027</v>
+        <v>707129</v>
       </c>
       <c r="R146" t="n">
-        <v>6670701</v>
+        <v>6670306</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17392,45 +17392,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129108051</v>
+        <v>129109792</v>
       </c>
       <c r="B147" t="n">
-        <v>98702</v>
+        <v>80149</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>219798</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>707017</v>
+        <v>706790</v>
       </c>
       <c r="R147" t="n">
-        <v>6670761</v>
+        <v>6670404</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17489,45 +17489,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129109792</v>
+        <v>129108051</v>
       </c>
       <c r="B148" t="n">
-        <v>80149</v>
+        <v>98705</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>219798</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>706790</v>
+        <v>707017</v>
       </c>
       <c r="R148" t="n">
-        <v>6670404</v>
+        <v>6670761</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17586,48 +17586,48 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129112466</v>
+        <v>129112890</v>
       </c>
       <c r="B149" t="n">
-        <v>91534</v>
+        <v>91113</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4660</v>
+        <v>937</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>707055</v>
+        <v>707141</v>
       </c>
       <c r="R149" t="n">
-        <v>6670286</v>
+        <v>6670348</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>129112646</v>
       </c>
       <c r="B150" t="n">
-        <v>99943</v>
+        <v>99946</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17780,48 +17780,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129112890</v>
+        <v>129114030</v>
       </c>
       <c r="B151" t="n">
-        <v>91110</v>
+        <v>91326</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>937</v>
+        <v>3215</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>707141</v>
+        <v>707151</v>
       </c>
       <c r="R151" t="n">
-        <v>6670348</v>
+        <v>6670622</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17877,10 +17877,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129114030</v>
+        <v>129112791</v>
       </c>
       <c r="B152" t="n">
-        <v>91323</v>
+        <v>91610</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17888,37 +17888,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3215</v>
+        <v>5321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>707151</v>
+        <v>707141</v>
       </c>
       <c r="R152" t="n">
-        <v>6670622</v>
+        <v>6670348</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>129111060</v>
       </c>
       <c r="B153" t="n">
-        <v>92040</v>
+        <v>92043</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18071,10 +18071,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129112791</v>
+        <v>129112466</v>
       </c>
       <c r="B154" t="n">
-        <v>91607</v>
+        <v>91537</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18082,37 +18082,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5321</v>
+        <v>4660</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>707141</v>
+        <v>707055</v>
       </c>
       <c r="R154" t="n">
-        <v>6670348</v>
+        <v>6670286</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -18168,10 +18168,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129113101</v>
+        <v>129112925</v>
       </c>
       <c r="B155" t="n">
-        <v>80149</v>
+        <v>91113</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18179,21 +18179,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>937</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18203,10 +18203,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>707194</v>
+        <v>707185</v>
       </c>
       <c r="R155" t="n">
-        <v>6670479</v>
+        <v>6670371</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18265,10 +18265,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129113068</v>
+        <v>129110999</v>
       </c>
       <c r="B156" t="n">
-        <v>110855</v>
+        <v>92508</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18276,37 +18276,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219711</v>
+        <v>4769</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>707202</v>
+        <v>707002</v>
       </c>
       <c r="R156" t="n">
-        <v>6670431</v>
+        <v>6670297</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129112925</v>
+        <v>129113101</v>
       </c>
       <c r="B157" t="n">
-        <v>91110</v>
+        <v>80149</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18373,21 +18373,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>937</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18397,10 +18397,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>707185</v>
+        <v>707194</v>
       </c>
       <c r="R157" t="n">
-        <v>6670371</v>
+        <v>6670479</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18459,10 +18459,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129110999</v>
+        <v>129113229</v>
       </c>
       <c r="B158" t="n">
-        <v>92505</v>
+        <v>92871</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18470,37 +18470,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>707002</v>
+        <v>707145</v>
       </c>
       <c r="R158" t="n">
-        <v>6670297</v>
+        <v>6670534</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18556,10 +18556,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129113229</v>
+        <v>129113068</v>
       </c>
       <c r="B159" t="n">
-        <v>92868</v>
+        <v>110858</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18567,21 +18567,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18591,13 +18591,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>707145</v>
+        <v>707202</v>
       </c>
       <c r="R159" t="n">
-        <v>6670534</v>
+        <v>6670431</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18653,10 +18653,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129109134</v>
+        <v>129113903</v>
       </c>
       <c r="B160" t="n">
-        <v>98630</v>
+        <v>92271</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18664,43 +18664,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>504</v>
+        <v>3298</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>706945</v>
+        <v>707129</v>
       </c>
       <c r="R160" t="n">
-        <v>6670657</v>
+        <v>6670627</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18759,10 +18750,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129112708</v>
+        <v>129108270</v>
       </c>
       <c r="B161" t="n">
-        <v>110855</v>
+        <v>92847</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18770,34 +18761,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>707129</v>
+        <v>706961</v>
       </c>
       <c r="R161" t="n">
-        <v>6670306</v>
+        <v>6670741</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18856,56 +18847,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129111656</v>
+        <v>129112708</v>
       </c>
       <c r="B162" t="n">
-        <v>90344</v>
+        <v>110858</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6003116</v>
+        <v>219711</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Davidmusseron</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tricholoma ilkkae</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>707000</v>
+        <v>707129</v>
       </c>
       <c r="R162" t="n">
-        <v>6670196</v>
+        <v>6670306</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18946,24 +18926,8 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
-        </is>
-      </c>
-      <c r="AL162" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
@@ -18976,53 +18940,60 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY162" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129113903</v>
+        <v>129111656</v>
       </c>
       <c r="B163" t="n">
-        <v>92268</v>
+        <v>90347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3298</v>
+        <v>6003116</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Davidmusseron</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tricholoma ilkkae</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>Mort.Chr. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>707129</v>
+        <v>707000</v>
       </c>
       <c r="R163" t="n">
-        <v>6670627</v>
+        <v>6670196</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19063,8 +19034,24 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
+        </is>
+      </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
@@ -19077,14 +19064,18 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY163" t="inlineStr"/>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129108270</v>
+        <v>129109134</v>
       </c>
       <c r="B164" t="n">
-        <v>92844</v>
+        <v>98633</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19092,34 +19083,43 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4366</v>
+        <v>504</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>706961</v>
+        <v>706945</v>
       </c>
       <c r="R164" t="n">
-        <v>6670741</v>
+        <v>6670657</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19178,10 +19178,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129107991</v>
+        <v>129114112</v>
       </c>
       <c r="B165" t="n">
-        <v>8439</v>
+        <v>86968</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19189,37 +19189,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>706990</v>
+        <v>707154</v>
       </c>
       <c r="R165" t="n">
-        <v>6670767</v>
+        <v>6670701</v>
       </c>
       <c r="S165" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19275,48 +19275,48 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129110603</v>
+        <v>129107991</v>
       </c>
       <c r="B166" t="n">
-        <v>102971</v>
+        <v>8439</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>223246</v>
+        <v>106554</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>706848</v>
+        <v>706990</v>
       </c>
       <c r="R166" t="n">
-        <v>6670352</v>
+        <v>6670767</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19372,32 +19372,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129109788</v>
+        <v>129110603</v>
       </c>
       <c r="B167" t="n">
-        <v>110855</v>
+        <v>102974</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>219711</v>
+        <v>223246</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -19407,10 +19407,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>706790</v>
+        <v>706848</v>
       </c>
       <c r="R167" t="n">
-        <v>6670404</v>
+        <v>6670352</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19469,45 +19469,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129109137</v>
+        <v>129112397</v>
       </c>
       <c r="B168" t="n">
-        <v>101820</v>
+        <v>86988</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221235</v>
+        <v>460</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Cordier) Gillet</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>706945</v>
+        <v>707055</v>
       </c>
       <c r="R168" t="n">
-        <v>6670657</v>
+        <v>6670286</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19566,48 +19566,48 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129113794</v>
+        <v>129108054</v>
       </c>
       <c r="B169" t="n">
-        <v>87005</v>
+        <v>98633</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6003295</v>
+        <v>504</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>707144</v>
+        <v>707017</v>
       </c>
       <c r="R169" t="n">
-        <v>6670568</v>
+        <v>6670761</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>129112386</v>
       </c>
       <c r="B170" t="n">
-        <v>99943</v>
+        <v>99946</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19778,10 +19778,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129112397</v>
+        <v>129112545</v>
       </c>
       <c r="B171" t="n">
-        <v>86988</v>
+        <v>79663</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19789,21 +19789,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>460</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19813,10 +19813,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>707055</v>
+        <v>707088</v>
       </c>
       <c r="R171" t="n">
-        <v>6670286</v>
+        <v>6670309</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19875,10 +19875,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129108054</v>
+        <v>129108500</v>
       </c>
       <c r="B172" t="n">
-        <v>98630</v>
+        <v>88761</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19886,21 +19886,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>504</v>
+        <v>4394</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19910,10 +19910,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>707017</v>
+        <v>706954</v>
       </c>
       <c r="R172" t="n">
-        <v>6670761</v>
+        <v>6670717</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19972,10 +19972,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129114112</v>
+        <v>129109788</v>
       </c>
       <c r="B173" t="n">
-        <v>86968</v>
+        <v>110858</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19983,37 +19983,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3674</v>
+        <v>219711</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>707154</v>
+        <v>706790</v>
       </c>
       <c r="R173" t="n">
-        <v>6670701</v>
+        <v>6670404</v>
       </c>
       <c r="S173" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -20069,10 +20069,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129112545</v>
+        <v>129113794</v>
       </c>
       <c r="B174" t="n">
-        <v>79663</v>
+        <v>87005</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20080,37 +20080,37 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>6003295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>707088</v>
+        <v>707144</v>
       </c>
       <c r="R174" t="n">
-        <v>6670309</v>
+        <v>6670568</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20166,10 +20166,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129108500</v>
+        <v>129109813</v>
       </c>
       <c r="B175" t="n">
-        <v>88761</v>
+        <v>100821</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20177,34 +20177,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4394</v>
+        <v>222771</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>706954</v>
+        <v>706790</v>
       </c>
       <c r="R175" t="n">
-        <v>6670717</v>
+        <v>6670404</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20263,10 +20263,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129109813</v>
+        <v>129109137</v>
       </c>
       <c r="B176" t="n">
-        <v>100818</v>
+        <v>101823</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20274,34 +20274,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>706790</v>
+        <v>706945</v>
       </c>
       <c r="R176" t="n">
-        <v>6670404</v>
+        <v>6670657</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20360,48 +20360,48 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129108275</v>
+        <v>129113803</v>
       </c>
       <c r="B177" t="n">
-        <v>87027</v>
+        <v>91326</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>449</v>
+        <v>3215</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>706961</v>
+        <v>707144</v>
       </c>
       <c r="R177" t="n">
-        <v>6670741</v>
+        <v>6670568</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20457,10 +20457,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129113803</v>
+        <v>129108056</v>
       </c>
       <c r="B178" t="n">
-        <v>91323</v>
+        <v>98749</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20468,37 +20468,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3215</v>
+        <v>219862</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>707144</v>
+        <v>707017</v>
       </c>
       <c r="R178" t="n">
-        <v>6670568</v>
+        <v>6670761</v>
       </c>
       <c r="S178" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20554,32 +20554,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129108056</v>
+        <v>129108275</v>
       </c>
       <c r="B179" t="n">
-        <v>98746</v>
+        <v>87027</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -20589,10 +20589,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>707017</v>
+        <v>706961</v>
       </c>
       <c r="R179" t="n">
-        <v>6670761</v>
+        <v>6670741</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20651,48 +20651,48 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129111077</v>
+        <v>129108563</v>
       </c>
       <c r="B180" t="n">
-        <v>80149</v>
+        <v>98633</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>706998</v>
+        <v>706958</v>
       </c>
       <c r="R180" t="n">
-        <v>6670322</v>
+        <v>6670705</v>
       </c>
       <c r="S180" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20748,45 +20748,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129109796</v>
+        <v>129109438</v>
       </c>
       <c r="B181" t="n">
-        <v>91561</v>
+        <v>92873</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1205</v>
+        <v>5966</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>706790</v>
+        <v>706816</v>
       </c>
       <c r="R181" t="n">
-        <v>6670404</v>
+        <v>6670564</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20845,45 +20845,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129109438</v>
+        <v>129112011</v>
       </c>
       <c r="B182" t="n">
-        <v>92870</v>
+        <v>98749</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5966</v>
+        <v>219862</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>706816</v>
+        <v>707031</v>
       </c>
       <c r="R182" t="n">
-        <v>6670564</v>
+        <v>6670179</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20942,32 +20942,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129112011</v>
+        <v>129111132</v>
       </c>
       <c r="B183" t="n">
-        <v>98746</v>
+        <v>91553</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>219862</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20977,10 +20977,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>707031</v>
+        <v>707028</v>
       </c>
       <c r="R183" t="n">
-        <v>6670179</v>
+        <v>6670245</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21039,32 +21039,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129110679</v>
+        <v>129109796</v>
       </c>
       <c r="B184" t="n">
-        <v>106352</v>
+        <v>91564</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220785</v>
+        <v>1205</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21074,10 +21074,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>706880</v>
+        <v>706790</v>
       </c>
       <c r="R184" t="n">
-        <v>6670333</v>
+        <v>6670404</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21136,10 +21136,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129111132</v>
+        <v>129110811</v>
       </c>
       <c r="B185" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21147,21 +21147,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21171,10 +21171,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>707028</v>
+        <v>706912</v>
       </c>
       <c r="R185" t="n">
-        <v>6670245</v>
+        <v>6670280</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21233,48 +21233,48 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129108563</v>
+        <v>129111077</v>
       </c>
       <c r="B186" t="n">
-        <v>98630</v>
+        <v>80149</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>706958</v>
+        <v>706998</v>
       </c>
       <c r="R186" t="n">
-        <v>6670705</v>
+        <v>6670322</v>
       </c>
       <c r="S186" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21330,32 +21330,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129110811</v>
+        <v>129110679</v>
       </c>
       <c r="B187" t="n">
-        <v>80149</v>
+        <v>106355</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6458</v>
+        <v>220785</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21365,10 +21365,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>706912</v>
+        <v>706880</v>
       </c>
       <c r="R187" t="n">
-        <v>6670280</v>
+        <v>6670333</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21427,10 +21427,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129110767</v>
+        <v>129110639</v>
       </c>
       <c r="B188" t="n">
-        <v>103249</v>
+        <v>99946</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21438,34 +21438,46 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>222002</v>
+        <v>174</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>706939</v>
+        <v>706867</v>
       </c>
       <c r="R188" t="n">
-        <v>6670322</v>
+        <v>6670336</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21500,12 +21512,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Stort bestånd.</t>
+        </is>
+      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
       <c r="AE188" t="b">
         <v>0</v>
       </c>
+      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -21524,10 +21542,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129110639</v>
+        <v>129112656</v>
       </c>
       <c r="B189" t="n">
-        <v>99943</v>
+        <v>92847</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21535,46 +21553,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>174</v>
+        <v>4366</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>706867</v>
+        <v>707129</v>
       </c>
       <c r="R189" t="n">
-        <v>6670336</v>
+        <v>6670306</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21609,18 +21615,12 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Stort bestånd.</t>
-        </is>
-      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -21639,10 +21639,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129112656</v>
+        <v>129110767</v>
       </c>
       <c r="B190" t="n">
-        <v>92844</v>
+        <v>103252</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21650,21 +21650,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4366</v>
+        <v>222002</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21674,10 +21674,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>707129</v>
+        <v>706939</v>
       </c>
       <c r="R190" t="n">
-        <v>6670306</v>
+        <v>6670322</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21836,7 +21836,7 @@
         <v>129109832</v>
       </c>
       <c r="B192" t="n">
-        <v>91607</v>
+        <v>91610</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22027,10 +22027,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129109288</v>
+        <v>129108939</v>
       </c>
       <c r="B194" t="n">
-        <v>91059</v>
+        <v>110858</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22038,34 +22038,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5741</v>
+        <v>219711</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>706876</v>
+        <v>707027</v>
       </c>
       <c r="R194" t="n">
-        <v>6670589</v>
+        <v>6670701</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22127,7 +22127,7 @@
         <v>129109238</v>
       </c>
       <c r="B195" t="n">
-        <v>104195</v>
+        <v>104198</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>129112425</v>
       </c>
       <c r="B196" t="n">
-        <v>103249</v>
+        <v>103252</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22318,48 +22318,48 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129108939</v>
+        <v>129112836</v>
       </c>
       <c r="B197" t="n">
-        <v>110855</v>
+        <v>91777</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>219711</v>
+        <v>1106</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>707027</v>
+        <v>707141</v>
       </c>
       <c r="R197" t="n">
-        <v>6670701</v>
+        <v>6670348</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -22516,48 +22516,48 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129112836</v>
+        <v>129109288</v>
       </c>
       <c r="B199" t="n">
-        <v>91774</v>
+        <v>91062</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1106</v>
+        <v>5741</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>707141</v>
+        <v>706876</v>
       </c>
       <c r="R199" t="n">
-        <v>6670348</v>
+        <v>6670589</v>
       </c>
       <c r="S199" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -22613,32 +22613,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129112379</v>
+        <v>129112410</v>
       </c>
       <c r="B200" t="n">
-        <v>102971</v>
+        <v>89562</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>223246</v>
+        <v>5581</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gulfotsskölding</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Pluteus romellii</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Britzelm.) Sacc.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22648,13 +22648,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>707012</v>
+        <v>707055</v>
       </c>
       <c r="R200" t="n">
-        <v>6670187</v>
+        <v>6670286</v>
       </c>
       <c r="S200" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>129111205</v>
       </c>
       <c r="B201" t="n">
-        <v>92846</v>
+        <v>92849</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22807,32 +22807,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129112733</v>
+        <v>129112405</v>
       </c>
       <c r="B202" t="n">
-        <v>90314</v>
+        <v>91113</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1595</v>
+        <v>937</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22842,10 +22842,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>707129</v>
+        <v>707055</v>
       </c>
       <c r="R202" t="n">
-        <v>6670306</v>
+        <v>6670286</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22904,45 +22904,54 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129112405</v>
+        <v>129108856</v>
       </c>
       <c r="B203" t="n">
-        <v>91110</v>
+        <v>98633</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>937</v>
+        <v>504</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>707055</v>
+        <v>707027</v>
       </c>
       <c r="R203" t="n">
-        <v>6670286</v>
+        <v>6670701</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23001,10 +23010,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129108856</v>
+        <v>129112733</v>
       </c>
       <c r="B204" t="n">
-        <v>98630</v>
+        <v>90317</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23012,43 +23021,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>504</v>
+        <v>1595</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>707027</v>
+        <v>707129</v>
       </c>
       <c r="R204" t="n">
-        <v>6670701</v>
+        <v>6670306</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23107,32 +23107,32 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129112410</v>
+        <v>129112379</v>
       </c>
       <c r="B205" t="n">
-        <v>89560</v>
+        <v>102974</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5581</v>
+        <v>223246</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Gulfotsskölding</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Pluteus romellii</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Britzelm.) Sacc.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23142,13 +23142,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>707055</v>
+        <v>707012</v>
       </c>
       <c r="R205" t="n">
-        <v>6670286</v>
+        <v>6670187</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -23301,10 +23301,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129110564</v>
+        <v>129108973</v>
       </c>
       <c r="B207" t="n">
-        <v>91607</v>
+        <v>87071</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23312,37 +23312,33 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5321</v>
+        <v>3624</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>706831</v>
+        <v>707027</v>
       </c>
       <c r="R207" t="n">
-        <v>6670326</v>
+        <v>6670701</v>
       </c>
       <c r="S207" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -23398,10 +23394,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129108973</v>
+        <v>129110564</v>
       </c>
       <c r="B208" t="n">
-        <v>87071</v>
+        <v>91610</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23409,33 +23405,37 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>3624</v>
+        <v>5321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr"/>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>707027</v>
+        <v>706831</v>
       </c>
       <c r="R208" t="n">
-        <v>6670701</v>
+        <v>6670326</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23491,45 +23491,45 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129112905</v>
+        <v>129108444</v>
       </c>
       <c r="B209" t="n">
-        <v>80149</v>
+        <v>91088</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6458</v>
+        <v>5747</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>707166</v>
+        <v>706954</v>
       </c>
       <c r="R209" t="n">
-        <v>6670369</v>
+        <v>6670717</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23588,32 +23588,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129108444</v>
+        <v>129108141</v>
       </c>
       <c r="B210" t="n">
-        <v>91085</v>
+        <v>92871</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23623,13 +23623,13 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>706954</v>
+        <v>707011</v>
       </c>
       <c r="R210" t="n">
-        <v>6670717</v>
+        <v>6670734</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23685,48 +23685,48 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129108141</v>
+        <v>129112905</v>
       </c>
       <c r="B211" t="n">
-        <v>92868</v>
+        <v>80149</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5964</v>
+        <v>6458</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>707011</v>
+        <v>707166</v>
       </c>
       <c r="R211" t="n">
-        <v>6670734</v>
+        <v>6670369</v>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23976,48 +23976,48 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129114035</v>
+        <v>129113073</v>
       </c>
       <c r="B214" t="n">
-        <v>86806</v>
+        <v>80149</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>3762</v>
+        <v>6458</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>707165</v>
+        <v>707212</v>
       </c>
       <c r="R214" t="n">
-        <v>6670655</v>
+        <v>6670436</v>
       </c>
       <c r="S214" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24073,10 +24073,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129110955</v>
+        <v>129111662</v>
       </c>
       <c r="B215" t="n">
-        <v>86806</v>
+        <v>92847</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24084,21 +24084,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -24108,13 +24108,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>706983</v>
+        <v>707011</v>
       </c>
       <c r="R215" t="n">
-        <v>6670276</v>
+        <v>6670220</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24170,10 +24170,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129111662</v>
+        <v>129108289</v>
       </c>
       <c r="B216" t="n">
-        <v>92844</v>
+        <v>43982</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24181,37 +24181,37 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4366</v>
+        <v>101735</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>707011</v>
+        <v>706961</v>
       </c>
       <c r="R216" t="n">
-        <v>6670220</v>
+        <v>6670741</v>
       </c>
       <c r="S216" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -24267,45 +24267,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129113073</v>
+        <v>129108076</v>
       </c>
       <c r="B217" t="n">
-        <v>80149</v>
+        <v>101823</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>707212</v>
+        <v>707017</v>
       </c>
       <c r="R217" t="n">
-        <v>6670436</v>
+        <v>6670761</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24364,10 +24364,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129108289</v>
+        <v>129114035</v>
       </c>
       <c r="B218" t="n">
-        <v>43982</v>
+        <v>86806</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24375,37 +24375,37 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>101735</v>
+        <v>3762</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>706961</v>
+        <v>707165</v>
       </c>
       <c r="R218" t="n">
-        <v>6670741</v>
+        <v>6670655</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24461,10 +24461,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129108076</v>
+        <v>129110955</v>
       </c>
       <c r="B219" t="n">
-        <v>101820</v>
+        <v>86806</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24472,34 +24472,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221235</v>
+        <v>3762</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>707017</v>
+        <v>706983</v>
       </c>
       <c r="R219" t="n">
-        <v>6670761</v>
+        <v>6670276</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129108458</v>
+        <v>129111122</v>
       </c>
       <c r="B220" t="n">
-        <v>80374</v>
+        <v>91788</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24569,29 +24569,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>228430</v>
+        <v>1100</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Rosetticka</t>
+        </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Quél.) Jülich</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>706954</v>
+        <v>707049</v>
       </c>
       <c r="R220" t="n">
-        <v>6670717</v>
+        <v>6670267</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24646,14 +24651,18 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY220" t="inlineStr"/>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129112111</v>
+        <v>129112862</v>
       </c>
       <c r="B221" t="n">
-        <v>92868</v>
+        <v>96073</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24661,37 +24670,37 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5964</v>
+        <v>2818</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>707012</v>
+        <v>707141</v>
       </c>
       <c r="R221" t="n">
-        <v>6670187</v>
+        <v>6670348</v>
       </c>
       <c r="S221" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24747,48 +24756,48 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129111122</v>
+        <v>129108567</v>
       </c>
       <c r="B222" t="n">
-        <v>91785</v>
+        <v>86806</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1100</v>
+        <v>3762</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Rosetticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Postia floriformis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Quél.) Jülich</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>707049</v>
+        <v>706958</v>
       </c>
       <c r="R222" t="n">
-        <v>6670267</v>
+        <v>6670705</v>
       </c>
       <c r="S222" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24840,18 +24849,14 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY222" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129108567</v>
+        <v>129112111</v>
       </c>
       <c r="B223" t="n">
-        <v>86806</v>
+        <v>92871</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24859,34 +24864,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>706958</v>
+        <v>707012</v>
       </c>
       <c r="R223" t="n">
-        <v>6670705</v>
+        <v>6670187</v>
       </c>
       <c r="S223" t="n">
         <v>15</v>
@@ -24945,48 +24950,43 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129112862</v>
+        <v>129108458</v>
       </c>
       <c r="B224" t="n">
-        <v>96070</v>
+        <v>80374</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2818</v>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Stubbspretmossa</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>707141</v>
+        <v>706954</v>
       </c>
       <c r="R224" t="n">
-        <v>6670348</v>
+        <v>6670717</v>
       </c>
       <c r="S224" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -25042,45 +25042,45 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129112746</v>
+        <v>129112901</v>
       </c>
       <c r="B225" t="n">
-        <v>102971</v>
+        <v>91113</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>223246</v>
+        <v>937</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>707129</v>
+        <v>707166</v>
       </c>
       <c r="R225" t="n">
-        <v>6670306</v>
+        <v>6670369</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25139,10 +25139,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129109815</v>
+        <v>129108591</v>
       </c>
       <c r="B226" t="n">
-        <v>101820</v>
+        <v>92508</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25150,37 +25150,37 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>706790</v>
+        <v>706958</v>
       </c>
       <c r="R226" t="n">
-        <v>6670404</v>
+        <v>6670705</v>
       </c>
       <c r="S226" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -25236,10 +25236,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129108561</v>
+        <v>129108343</v>
       </c>
       <c r="B227" t="n">
-        <v>101820</v>
+        <v>92508</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25247,21 +25247,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -25271,13 +25271,13 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>706954</v>
+        <v>706937</v>
       </c>
       <c r="R227" t="n">
-        <v>6670717</v>
+        <v>6670745</v>
       </c>
       <c r="S227" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25333,45 +25333,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129112901</v>
+        <v>129112746</v>
       </c>
       <c r="B228" t="n">
-        <v>91110</v>
+        <v>102974</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>937</v>
+        <v>223246</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>707166</v>
+        <v>707129</v>
       </c>
       <c r="R228" t="n">
-        <v>6670369</v>
+        <v>6670306</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25430,10 +25430,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129108653</v>
+        <v>129109815</v>
       </c>
       <c r="B229" t="n">
-        <v>98630</v>
+        <v>101823</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25441,43 +25441,34 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>504</v>
+        <v>221235</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>706984</v>
+        <v>706790</v>
       </c>
       <c r="R229" t="n">
-        <v>6670689</v>
+        <v>6670404</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25536,10 +25527,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129108591</v>
+        <v>129108561</v>
       </c>
       <c r="B230" t="n">
-        <v>92505</v>
+        <v>101823</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25547,21 +25538,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -25571,13 +25562,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>706958</v>
+        <v>706954</v>
       </c>
       <c r="R230" t="n">
-        <v>6670705</v>
+        <v>6670717</v>
       </c>
       <c r="S230" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -25633,10 +25624,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129108343</v>
+        <v>129108653</v>
       </c>
       <c r="B231" t="n">
-        <v>92505</v>
+        <v>98633</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25644,37 +25635,46 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4769</v>
+        <v>504</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>706937</v>
+        <v>706984</v>
       </c>
       <c r="R231" t="n">
-        <v>6670745</v>
+        <v>6670689</v>
       </c>
       <c r="S231" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -25730,10 +25730,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129113799</v>
+        <v>129108929</v>
       </c>
       <c r="B232" t="n">
-        <v>92505</v>
+        <v>92871</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25741,37 +25741,37 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>707144</v>
+        <v>707027</v>
       </c>
       <c r="R232" t="n">
-        <v>6670568</v>
+        <v>6670701</v>
       </c>
       <c r="S232" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -25827,10 +25827,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129108929</v>
+        <v>129113799</v>
       </c>
       <c r="B233" t="n">
-        <v>92868</v>
+        <v>92508</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25838,37 +25838,37 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>707027</v>
+        <v>707144</v>
       </c>
       <c r="R233" t="n">
-        <v>6670701</v>
+        <v>6670568</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>129108059</v>
       </c>
       <c r="B235" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26118,10 +26118,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129109794</v>
+        <v>129108620</v>
       </c>
       <c r="B236" t="n">
-        <v>104195</v>
+        <v>98749</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26129,34 +26129,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>706790</v>
+        <v>706971</v>
       </c>
       <c r="R236" t="n">
-        <v>6670404</v>
+        <v>6670688</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26215,45 +26215,45 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129108620</v>
+        <v>129114064</v>
       </c>
       <c r="B237" t="n">
-        <v>98746</v>
+        <v>92327</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>219862</v>
+        <v>232138</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>706971</v>
+        <v>707168</v>
       </c>
       <c r="R237" t="n">
-        <v>6670688</v>
+        <v>6670669</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26312,45 +26312,45 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129114064</v>
+        <v>129109794</v>
       </c>
       <c r="B238" t="n">
-        <v>92324</v>
+        <v>104198</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>232138</v>
+        <v>222412</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>707168</v>
+        <v>706790</v>
       </c>
       <c r="R238" t="n">
-        <v>6670669</v>
+        <v>6670404</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26412,7 +26412,7 @@
         <v>129112433</v>
       </c>
       <c r="B239" t="n">
-        <v>89565</v>
+        <v>89567</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -16118,48 +16118,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129108149</v>
+        <v>129112588</v>
       </c>
       <c r="B134" t="n">
-        <v>91326</v>
+        <v>79581</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3215</v>
+        <v>1352</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>707011</v>
+        <v>707101</v>
       </c>
       <c r="R134" t="n">
-        <v>6670734</v>
+        <v>6670297</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16215,48 +16215,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129110669</v>
+        <v>129108149</v>
       </c>
       <c r="B135" t="n">
-        <v>80149</v>
+        <v>91326</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>706880</v>
+        <v>707011</v>
       </c>
       <c r="R135" t="n">
-        <v>6670333</v>
+        <v>6670734</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16312,32 +16312,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129112482</v>
+        <v>129112087</v>
       </c>
       <c r="B136" t="n">
-        <v>80149</v>
+        <v>92847</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16347,10 +16347,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>707055</v>
+        <v>707031</v>
       </c>
       <c r="R136" t="n">
-        <v>6670286</v>
+        <v>6670179</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16409,10 +16409,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129112588</v>
+        <v>129110669</v>
       </c>
       <c r="B137" t="n">
-        <v>79581</v>
+        <v>80149</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16420,21 +16420,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1352</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16444,13 +16444,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>707101</v>
+        <v>706880</v>
       </c>
       <c r="R137" t="n">
-        <v>6670297</v>
+        <v>6670333</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16506,32 +16506,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129112087</v>
+        <v>129112482</v>
       </c>
       <c r="B138" t="n">
-        <v>92847</v>
+        <v>80149</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16541,10 +16541,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>707031</v>
+        <v>707055</v>
       </c>
       <c r="R138" t="n">
-        <v>6670179</v>
+        <v>6670286</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17004,45 +17004,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129112389</v>
+        <v>129113907</v>
       </c>
       <c r="B143" t="n">
-        <v>102974</v>
+        <v>87005</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>223246</v>
+        <v>6003295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>707049</v>
+        <v>707129</v>
       </c>
       <c r="R143" t="n">
-        <v>6670267</v>
+        <v>6670627</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17101,45 +17101,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129113907</v>
+        <v>129112389</v>
       </c>
       <c r="B144" t="n">
-        <v>87005</v>
+        <v>102974</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6003295</v>
+        <v>223246</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>707129</v>
+        <v>707049</v>
       </c>
       <c r="R144" t="n">
-        <v>6670627</v>
+        <v>6670267</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17198,10 +17198,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129108937</v>
+        <v>129108051</v>
       </c>
       <c r="B145" t="n">
-        <v>91326</v>
+        <v>98705</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17209,21 +17209,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17233,10 +17233,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>707027</v>
+        <v>707017</v>
       </c>
       <c r="R145" t="n">
-        <v>6670701</v>
+        <v>6670761</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17392,45 +17392,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129109792</v>
+        <v>129108937</v>
       </c>
       <c r="B147" t="n">
-        <v>80149</v>
+        <v>91326</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>706790</v>
+        <v>707027</v>
       </c>
       <c r="R147" t="n">
-        <v>6670404</v>
+        <v>6670701</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17489,45 +17489,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129108051</v>
+        <v>129109792</v>
       </c>
       <c r="B148" t="n">
-        <v>98705</v>
+        <v>80149</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>219798</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>707017</v>
+        <v>706790</v>
       </c>
       <c r="R148" t="n">
-        <v>6670761</v>
+        <v>6670404</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17683,10 +17683,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129112646</v>
+        <v>129114030</v>
       </c>
       <c r="B150" t="n">
-        <v>99946</v>
+        <v>91326</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17694,34 +17694,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>174</v>
+        <v>3215</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>707129</v>
+        <v>707151</v>
       </c>
       <c r="R150" t="n">
-        <v>6670306</v>
+        <v>6670622</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17780,10 +17780,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129114030</v>
+        <v>129112791</v>
       </c>
       <c r="B151" t="n">
-        <v>91326</v>
+        <v>91610</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17791,37 +17791,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3215</v>
+        <v>5321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>707151</v>
+        <v>707141</v>
       </c>
       <c r="R151" t="n">
-        <v>6670622</v>
+        <v>6670348</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17877,48 +17877,48 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129112791</v>
+        <v>129111060</v>
       </c>
       <c r="B152" t="n">
-        <v>91610</v>
+        <v>92043</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5321</v>
+        <v>5469</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kärrvaxskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Phlebiodontia subochracea</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>707141</v>
+        <v>706998</v>
       </c>
       <c r="R152" t="n">
-        <v>6670348</v>
+        <v>6670322</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17974,32 +17974,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129111060</v>
+        <v>129112646</v>
       </c>
       <c r="B153" t="n">
-        <v>92043</v>
+        <v>99946</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5469</v>
+        <v>174</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kärrvaxskinn</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phlebiodontia subochracea</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18009,13 +18009,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>706998</v>
+        <v>707129</v>
       </c>
       <c r="R153" t="n">
-        <v>6670322</v>
+        <v>6670306</v>
       </c>
       <c r="S153" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18265,10 +18265,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129110999</v>
+        <v>129113068</v>
       </c>
       <c r="B156" t="n">
-        <v>92508</v>
+        <v>110858</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18276,37 +18276,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4769</v>
+        <v>219711</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>707002</v>
+        <v>707202</v>
       </c>
       <c r="R156" t="n">
-        <v>6670297</v>
+        <v>6670431</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18362,32 +18362,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129113101</v>
+        <v>129113229</v>
       </c>
       <c r="B157" t="n">
-        <v>80149</v>
+        <v>92871</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>5964</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18397,13 +18397,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>707194</v>
+        <v>707145</v>
       </c>
       <c r="R157" t="n">
-        <v>6670479</v>
+        <v>6670534</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18459,32 +18459,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129113229</v>
+        <v>129113101</v>
       </c>
       <c r="B158" t="n">
-        <v>92871</v>
+        <v>80149</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5964</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>707145</v>
+        <v>707194</v>
       </c>
       <c r="R158" t="n">
-        <v>6670534</v>
+        <v>6670479</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18556,10 +18556,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129113068</v>
+        <v>129110999</v>
       </c>
       <c r="B159" t="n">
-        <v>110858</v>
+        <v>92508</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18567,37 +18567,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>219711</v>
+        <v>4769</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>707202</v>
+        <v>707002</v>
       </c>
       <c r="R159" t="n">
-        <v>6670431</v>
+        <v>6670297</v>
       </c>
       <c r="S159" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18944,56 +18944,54 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129111656</v>
+        <v>129109134</v>
       </c>
       <c r="B163" t="n">
-        <v>90347</v>
+        <v>98633</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6003116</v>
+        <v>504</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Davidmusseron</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tricholoma ilkkae</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>707000</v>
+        <v>706945</v>
       </c>
       <c r="R163" t="n">
-        <v>6670196</v>
+        <v>6670657</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19034,24 +19032,8 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
-        </is>
-      </c>
-      <c r="AL163" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
@@ -19064,62 +19046,60 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129109134</v>
+        <v>129111656</v>
       </c>
       <c r="B164" t="n">
-        <v>98633</v>
+        <v>90347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>504</v>
+        <v>6003116</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Davidmusseron</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tricholoma ilkkae</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Mort.Chr. &amp; al.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>706945</v>
+        <v>707000</v>
       </c>
       <c r="R164" t="n">
-        <v>6670657</v>
+        <v>6670196</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19160,8 +19140,24 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -19174,7 +19170,11 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY164" t="inlineStr"/>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19275,10 +19275,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129107991</v>
+        <v>129108500</v>
       </c>
       <c r="B166" t="n">
-        <v>8439</v>
+        <v>88761</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19286,21 +19286,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>106554</v>
+        <v>4394</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19310,13 +19310,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>706990</v>
+        <v>706954</v>
       </c>
       <c r="R166" t="n">
-        <v>6670767</v>
+        <v>6670717</v>
       </c>
       <c r="S166" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19372,32 +19372,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129110603</v>
+        <v>129109788</v>
       </c>
       <c r="B167" t="n">
-        <v>102974</v>
+        <v>110858</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>223246</v>
+        <v>219711</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -19407,10 +19407,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>706848</v>
+        <v>706790</v>
       </c>
       <c r="R167" t="n">
-        <v>6670352</v>
+        <v>6670404</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19469,45 +19469,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129112397</v>
+        <v>129109137</v>
       </c>
       <c r="B168" t="n">
-        <v>86988</v>
+        <v>101823</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>460</v>
+        <v>221235</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>707055</v>
+        <v>706945</v>
       </c>
       <c r="R168" t="n">
-        <v>6670286</v>
+        <v>6670657</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19566,10 +19566,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129108054</v>
+        <v>129109813</v>
       </c>
       <c r="B169" t="n">
-        <v>98633</v>
+        <v>100821</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19577,16 +19577,16 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>504</v>
+        <v>222771</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -19597,14 +19597,14 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>707017</v>
+        <v>706790</v>
       </c>
       <c r="R169" t="n">
-        <v>6670761</v>
+        <v>6670404</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19663,57 +19663,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129112386</v>
+        <v>129110603</v>
       </c>
       <c r="B170" t="n">
-        <v>99946</v>
+        <v>102974</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>174</v>
+        <v>223246</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>707049</v>
+        <v>706848</v>
       </c>
       <c r="R170" t="n">
-        <v>6670267</v>
+        <v>6670352</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19748,18 +19736,12 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Stort bestånd.</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -19778,10 +19760,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129112545</v>
+        <v>129113794</v>
       </c>
       <c r="B171" t="n">
-        <v>79663</v>
+        <v>87005</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19789,37 +19771,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>6003295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>707088</v>
+        <v>707144</v>
       </c>
       <c r="R171" t="n">
-        <v>6670309</v>
+        <v>6670568</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19875,10 +19857,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129108500</v>
+        <v>129107991</v>
       </c>
       <c r="B172" t="n">
-        <v>88761</v>
+        <v>8439</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19886,21 +19868,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4394</v>
+        <v>106554</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19910,13 +19892,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>706954</v>
+        <v>706990</v>
       </c>
       <c r="R172" t="n">
-        <v>6670717</v>
+        <v>6670767</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19972,32 +19954,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129109788</v>
+        <v>129112545</v>
       </c>
       <c r="B173" t="n">
-        <v>110858</v>
+        <v>79663</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>219711</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -20007,10 +19989,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>706790</v>
+        <v>707088</v>
       </c>
       <c r="R173" t="n">
-        <v>6670404</v>
+        <v>6670309</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20069,48 +20051,60 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129113794</v>
+        <v>129112386</v>
       </c>
       <c r="B174" t="n">
-        <v>87005</v>
+        <v>99946</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6003295</v>
+        <v>174</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>707144</v>
+        <v>707049</v>
       </c>
       <c r="R174" t="n">
-        <v>6670568</v>
+        <v>6670267</v>
       </c>
       <c r="S174" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20142,12 +20136,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Stort bestånd.</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -20166,32 +20166,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129109813</v>
+        <v>129112397</v>
       </c>
       <c r="B175" t="n">
-        <v>100821</v>
+        <v>86988</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>222771</v>
+        <v>460</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Cordier) Gillet</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20201,10 +20201,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>706790</v>
+        <v>707055</v>
       </c>
       <c r="R175" t="n">
-        <v>6670404</v>
+        <v>6670286</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20263,10 +20263,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129109137</v>
+        <v>129108054</v>
       </c>
       <c r="B176" t="n">
-        <v>101823</v>
+        <v>98633</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20274,34 +20274,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>221235</v>
+        <v>504</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>706945</v>
+        <v>707017</v>
       </c>
       <c r="R176" t="n">
-        <v>6670657</v>
+        <v>6670761</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20360,10 +20360,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129113803</v>
+        <v>129108056</v>
       </c>
       <c r="B177" t="n">
-        <v>91326</v>
+        <v>98749</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20371,37 +20371,37 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3215</v>
+        <v>219862</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>707144</v>
+        <v>707017</v>
       </c>
       <c r="R177" t="n">
-        <v>6670568</v>
+        <v>6670761</v>
       </c>
       <c r="S177" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20457,10 +20457,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129108056</v>
+        <v>129113803</v>
       </c>
       <c r="B178" t="n">
-        <v>98749</v>
+        <v>91326</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20468,37 +20468,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>219862</v>
+        <v>3215</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>707017</v>
+        <v>707144</v>
       </c>
       <c r="R178" t="n">
-        <v>6670761</v>
+        <v>6670568</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20748,10 +20748,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129109438</v>
+        <v>129110811</v>
       </c>
       <c r="B181" t="n">
-        <v>92873</v>
+        <v>80149</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20759,34 +20759,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>706816</v>
+        <v>706912</v>
       </c>
       <c r="R181" t="n">
-        <v>6670564</v>
+        <v>6670280</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20845,32 +20845,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129112011</v>
+        <v>129111077</v>
       </c>
       <c r="B182" t="n">
-        <v>98749</v>
+        <v>80149</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>219862</v>
+        <v>6458</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20880,13 +20880,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>707031</v>
+        <v>706998</v>
       </c>
       <c r="R182" t="n">
-        <v>6670179</v>
+        <v>6670322</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21136,10 +21136,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129110811</v>
+        <v>129109438</v>
       </c>
       <c r="B185" t="n">
-        <v>80149</v>
+        <v>92873</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21147,34 +21147,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>706912</v>
+        <v>706816</v>
       </c>
       <c r="R185" t="n">
-        <v>6670280</v>
+        <v>6670564</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21233,32 +21233,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129111077</v>
+        <v>129110679</v>
       </c>
       <c r="B186" t="n">
-        <v>80149</v>
+        <v>106355</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6458</v>
+        <v>220785</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21268,13 +21268,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>706998</v>
+        <v>706880</v>
       </c>
       <c r="R186" t="n">
-        <v>6670322</v>
+        <v>6670333</v>
       </c>
       <c r="S186" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21330,32 +21330,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129110679</v>
+        <v>129112011</v>
       </c>
       <c r="B187" t="n">
-        <v>106355</v>
+        <v>98749</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21365,10 +21365,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>706880</v>
+        <v>707031</v>
       </c>
       <c r="R187" t="n">
-        <v>6670333</v>
+        <v>6670179</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21427,10 +21427,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129110639</v>
+        <v>129110767</v>
       </c>
       <c r="B188" t="n">
-        <v>99946</v>
+        <v>103252</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21438,46 +21438,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>174</v>
+        <v>222002</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>706867</v>
+        <v>706939</v>
       </c>
       <c r="R188" t="n">
-        <v>6670336</v>
+        <v>6670322</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21512,18 +21500,12 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Stort bestånd.</t>
-        </is>
-      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -21542,10 +21524,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129112656</v>
+        <v>129110639</v>
       </c>
       <c r="B189" t="n">
-        <v>92847</v>
+        <v>99946</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21553,34 +21535,46 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4366</v>
+        <v>174</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>707129</v>
+        <v>706867</v>
       </c>
       <c r="R189" t="n">
-        <v>6670306</v>
+        <v>6670336</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21615,12 +21609,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Stort bestånd.</t>
+        </is>
+      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -21639,10 +21639,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129110767</v>
+        <v>129112656</v>
       </c>
       <c r="B190" t="n">
-        <v>103252</v>
+        <v>92847</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21650,21 +21650,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>222002</v>
+        <v>4366</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21674,10 +21674,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>706939</v>
+        <v>707129</v>
       </c>
       <c r="R190" t="n">
-        <v>6670322</v>
+        <v>6670306</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21736,10 +21736,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129108900</v>
+        <v>129109832</v>
       </c>
       <c r="B191" t="n">
-        <v>86968</v>
+        <v>91610</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21747,34 +21747,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3674</v>
+        <v>5321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>707027</v>
+        <v>706793</v>
       </c>
       <c r="R191" t="n">
-        <v>6670701</v>
+        <v>6670414</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21833,10 +21833,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129109832</v>
+        <v>129108900</v>
       </c>
       <c r="B192" t="n">
-        <v>91610</v>
+        <v>86968</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21844,34 +21844,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5321</v>
+        <v>3674</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>706793</v>
+        <v>707027</v>
       </c>
       <c r="R192" t="n">
-        <v>6670414</v>
+        <v>6670701</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22027,45 +22027,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129108939</v>
+        <v>129109340</v>
       </c>
       <c r="B194" t="n">
-        <v>110858</v>
+        <v>86897</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>219711</v>
+        <v>445</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>707027</v>
+        <v>706839</v>
       </c>
       <c r="R194" t="n">
-        <v>6670701</v>
+        <v>6670598</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22120,52 +22120,56 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY194" t="inlineStr"/>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129109238</v>
+        <v>129112836</v>
       </c>
       <c r="B195" t="n">
-        <v>104198</v>
+        <v>91777</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>222412</v>
+        <v>1106</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>706876</v>
+        <v>707141</v>
       </c>
       <c r="R195" t="n">
-        <v>6670589</v>
+        <v>6670348</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22221,10 +22225,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129112425</v>
+        <v>129109288</v>
       </c>
       <c r="B196" t="n">
-        <v>103252</v>
+        <v>91062</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22232,34 +22236,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>222002</v>
+        <v>5741</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>707055</v>
+        <v>706876</v>
       </c>
       <c r="R196" t="n">
-        <v>6670286</v>
+        <v>6670589</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22318,48 +22322,48 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129112836</v>
+        <v>129108939</v>
       </c>
       <c r="B197" t="n">
-        <v>91777</v>
+        <v>110858</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1106</v>
+        <v>219711</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>707141</v>
+        <v>707027</v>
       </c>
       <c r="R197" t="n">
-        <v>6670348</v>
+        <v>6670701</v>
       </c>
       <c r="S197" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -22415,45 +22419,45 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129109340</v>
+        <v>129112425</v>
       </c>
       <c r="B198" t="n">
-        <v>86897</v>
+        <v>103252</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>445</v>
+        <v>222002</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>706839</v>
+        <v>707055</v>
       </c>
       <c r="R198" t="n">
-        <v>6670598</v>
+        <v>6670286</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22508,18 +22512,14 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY198" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129109288</v>
+        <v>129109238</v>
       </c>
       <c r="B199" t="n">
-        <v>91062</v>
+        <v>104198</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22527,21 +22527,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5741</v>
+        <v>222412</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22613,10 +22613,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129112410</v>
+        <v>129108856</v>
       </c>
       <c r="B200" t="n">
-        <v>89562</v>
+        <v>98633</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22624,34 +22624,43 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5581</v>
+        <v>504</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Gulfotsskölding</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Pluteus romellii</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Britzelm.) Sacc.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>707055</v>
+        <v>707027</v>
       </c>
       <c r="R200" t="n">
-        <v>6670286</v>
+        <v>6670701</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22710,10 +22719,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129111205</v>
+        <v>129112733</v>
       </c>
       <c r="B201" t="n">
-        <v>92849</v>
+        <v>90317</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22721,19 +22730,23 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6047725</v>
+        <v>1595</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr"/>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
@@ -22741,10 +22754,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>707000</v>
+        <v>707129</v>
       </c>
       <c r="R201" t="n">
-        <v>6670196</v>
+        <v>6670306</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22799,11 +22812,7 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY201" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22904,10 +22913,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129108856</v>
+        <v>129112410</v>
       </c>
       <c r="B203" t="n">
-        <v>98633</v>
+        <v>89562</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22915,43 +22924,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>504</v>
+        <v>5581</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Gulfotsskölding</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pluteus romellii</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Britzelm.) Sacc.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>707027</v>
+        <v>707055</v>
       </c>
       <c r="R203" t="n">
-        <v>6670701</v>
+        <v>6670286</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23010,32 +23010,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129112733</v>
+        <v>129112379</v>
       </c>
       <c r="B204" t="n">
-        <v>90317</v>
+        <v>102974</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1595</v>
+        <v>223246</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -23045,13 +23045,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>707129</v>
+        <v>707012</v>
       </c>
       <c r="R204" t="n">
-        <v>6670306</v>
+        <v>6670187</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -23107,34 +23107,30 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129112379</v>
+        <v>129111205</v>
       </c>
       <c r="B205" t="n">
-        <v>102974</v>
+        <v>92849</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>223246</v>
+        <v>6047725</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Huds.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
@@ -23142,13 +23138,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>707012</v>
+        <v>707000</v>
       </c>
       <c r="R205" t="n">
-        <v>6670187</v>
+        <v>6670196</v>
       </c>
       <c r="S205" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -23200,14 +23196,18 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY205" t="inlineStr"/>
+      <c r="AY205" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129109887</v>
+        <v>129112015</v>
       </c>
       <c r="B206" t="n">
-        <v>88759</v>
+        <v>87005</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23215,21 +23215,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>805</v>
+        <v>6003295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23239,10 +23239,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>706822</v>
+        <v>707031</v>
       </c>
       <c r="R206" t="n">
-        <v>6670378</v>
+        <v>6670179</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23301,41 +23301,45 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129108973</v>
+        <v>129109887</v>
       </c>
       <c r="B207" t="n">
-        <v>87071</v>
+        <v>88759</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>3624</v>
+        <v>805</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr"/>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>707027</v>
+        <v>706822</v>
       </c>
       <c r="R207" t="n">
-        <v>6670701</v>
+        <v>6670378</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23394,10 +23398,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129110564</v>
+        <v>129108973</v>
       </c>
       <c r="B208" t="n">
-        <v>91610</v>
+        <v>87071</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23405,37 +23409,33 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5321</v>
+        <v>3624</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>706831</v>
+        <v>707027</v>
       </c>
       <c r="R208" t="n">
-        <v>6670326</v>
+        <v>6670701</v>
       </c>
       <c r="S208" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23491,32 +23491,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129108444</v>
+        <v>129108141</v>
       </c>
       <c r="B209" t="n">
-        <v>91088</v>
+        <v>92871</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23526,13 +23526,13 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>706954</v>
+        <v>707011</v>
       </c>
       <c r="R209" t="n">
-        <v>6670717</v>
+        <v>6670734</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23588,32 +23588,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129108141</v>
+        <v>129108444</v>
       </c>
       <c r="B210" t="n">
-        <v>92871</v>
+        <v>91088</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23623,13 +23623,13 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>707011</v>
+        <v>706954</v>
       </c>
       <c r="R210" t="n">
-        <v>6670734</v>
+        <v>6670717</v>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23879,32 +23879,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129112015</v>
+        <v>129110564</v>
       </c>
       <c r="B213" t="n">
-        <v>87005</v>
+        <v>91610</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6003295</v>
+        <v>5321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23914,13 +23914,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>707031</v>
+        <v>706831</v>
       </c>
       <c r="R213" t="n">
-        <v>6670179</v>
+        <v>6670326</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23976,45 +23976,45 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129113073</v>
+        <v>129108289</v>
       </c>
       <c r="B214" t="n">
-        <v>80149</v>
+        <v>43982</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6458</v>
+        <v>101735</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>707212</v>
+        <v>706961</v>
       </c>
       <c r="R214" t="n">
-        <v>6670436</v>
+        <v>6670741</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24073,10 +24073,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129111662</v>
+        <v>129114035</v>
       </c>
       <c r="B215" t="n">
-        <v>92847</v>
+        <v>86806</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24084,34 +24084,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>707011</v>
+        <v>707165</v>
       </c>
       <c r="R215" t="n">
-        <v>6670220</v>
+        <v>6670655</v>
       </c>
       <c r="S215" t="n">
         <v>15</v>
@@ -24170,10 +24170,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129108289</v>
+        <v>129110955</v>
       </c>
       <c r="B216" t="n">
-        <v>43982</v>
+        <v>86806</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24181,34 +24181,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>101735</v>
+        <v>3762</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>706961</v>
+        <v>706983</v>
       </c>
       <c r="R216" t="n">
-        <v>6670741</v>
+        <v>6670276</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24267,45 +24267,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129108076</v>
+        <v>129113073</v>
       </c>
       <c r="B217" t="n">
-        <v>101823</v>
+        <v>80149</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>707017</v>
+        <v>707212</v>
       </c>
       <c r="R217" t="n">
-        <v>6670761</v>
+        <v>6670436</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24364,10 +24364,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129114035</v>
+        <v>129111662</v>
       </c>
       <c r="B218" t="n">
-        <v>86806</v>
+        <v>92847</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24375,34 +24375,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>707165</v>
+        <v>707011</v>
       </c>
       <c r="R218" t="n">
-        <v>6670655</v>
+        <v>6670220</v>
       </c>
       <c r="S218" t="n">
         <v>15</v>
@@ -24461,10 +24461,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129110955</v>
+        <v>129108076</v>
       </c>
       <c r="B219" t="n">
-        <v>86806</v>
+        <v>101823</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24472,34 +24472,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>3762</v>
+        <v>221235</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>706983</v>
+        <v>707017</v>
       </c>
       <c r="R219" t="n">
-        <v>6670276</v>
+        <v>6670761</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24659,10 +24659,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129112862</v>
+        <v>129108567</v>
       </c>
       <c r="B221" t="n">
-        <v>96073</v>
+        <v>86806</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24670,37 +24670,37 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2818</v>
+        <v>3762</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>707141</v>
+        <v>706958</v>
       </c>
       <c r="R221" t="n">
-        <v>6670348</v>
+        <v>6670705</v>
       </c>
       <c r="S221" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24756,10 +24756,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129108567</v>
+        <v>129112111</v>
       </c>
       <c r="B222" t="n">
-        <v>86806</v>
+        <v>92871</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24767,34 +24767,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>706958</v>
+        <v>707012</v>
       </c>
       <c r="R222" t="n">
-        <v>6670705</v>
+        <v>6670187</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -24853,10 +24853,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129112111</v>
+        <v>129112862</v>
       </c>
       <c r="B223" t="n">
-        <v>92871</v>
+        <v>96073</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24864,37 +24864,37 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5964</v>
+        <v>2818</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>707012</v>
+        <v>707141</v>
       </c>
       <c r="R223" t="n">
-        <v>6670187</v>
+        <v>6670348</v>
       </c>
       <c r="S223" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -25042,48 +25042,48 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129112901</v>
+        <v>129108343</v>
       </c>
       <c r="B225" t="n">
-        <v>91113</v>
+        <v>92508</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>937</v>
+        <v>4769</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>707166</v>
+        <v>706937</v>
       </c>
       <c r="R225" t="n">
-        <v>6670369</v>
+        <v>6670745</v>
       </c>
       <c r="S225" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -25139,10 +25139,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129108591</v>
+        <v>129108653</v>
       </c>
       <c r="B226" t="n">
-        <v>92508</v>
+        <v>98633</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25150,37 +25150,46 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4769</v>
+        <v>504</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>706958</v>
+        <v>706984</v>
       </c>
       <c r="R226" t="n">
-        <v>6670705</v>
+        <v>6670689</v>
       </c>
       <c r="S226" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -25236,48 +25245,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129108343</v>
+        <v>129112901</v>
       </c>
       <c r="B227" t="n">
-        <v>92508</v>
+        <v>91113</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4769</v>
+        <v>937</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>706937</v>
+        <v>707166</v>
       </c>
       <c r="R227" t="n">
-        <v>6670745</v>
+        <v>6670369</v>
       </c>
       <c r="S227" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25333,48 +25342,48 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129112746</v>
+        <v>129108591</v>
       </c>
       <c r="B228" t="n">
-        <v>102974</v>
+        <v>92508</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>223246</v>
+        <v>4769</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>707129</v>
+        <v>706958</v>
       </c>
       <c r="R228" t="n">
-        <v>6670306</v>
+        <v>6670705</v>
       </c>
       <c r="S228" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -25624,54 +25633,45 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129108653</v>
+        <v>129112746</v>
       </c>
       <c r="B231" t="n">
-        <v>98633</v>
+        <v>102974</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>504</v>
+        <v>223246</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>706984</v>
+        <v>707129</v>
       </c>
       <c r="R231" t="n">
-        <v>6670689</v>
+        <v>6670306</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25730,45 +25730,45 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129108929</v>
+        <v>129109932</v>
       </c>
       <c r="B232" t="n">
-        <v>92871</v>
+        <v>5493</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5964</v>
+        <v>101410</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>707027</v>
+        <v>706801</v>
       </c>
       <c r="R232" t="n">
-        <v>6670701</v>
+        <v>6670352</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25924,45 +25924,45 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129109932</v>
+        <v>129108929</v>
       </c>
       <c r="B234" t="n">
-        <v>5493</v>
+        <v>92871</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>101410</v>
+        <v>5964</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>706801</v>
+        <v>707027</v>
       </c>
       <c r="R234" t="n">
-        <v>6670352</v>
+        <v>6670701</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26021,10 +26021,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129108059</v>
+        <v>129108620</v>
       </c>
       <c r="B235" t="n">
-        <v>92508</v>
+        <v>98749</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26032,21 +26032,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4769</v>
+        <v>219862</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -26056,10 +26056,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>707017</v>
+        <v>706971</v>
       </c>
       <c r="R235" t="n">
-        <v>6670761</v>
+        <v>6670688</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26118,10 +26118,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129108620</v>
+        <v>129109794</v>
       </c>
       <c r="B236" t="n">
-        <v>98749</v>
+        <v>104198</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26129,34 +26129,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>219862</v>
+        <v>222412</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>706971</v>
+        <v>706790</v>
       </c>
       <c r="R236" t="n">
-        <v>6670688</v>
+        <v>6670404</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26312,10 +26312,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129109794</v>
+        <v>129108059</v>
       </c>
       <c r="B238" t="n">
-        <v>104198</v>
+        <v>92508</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26323,34 +26323,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>706790</v>
+        <v>707017</v>
       </c>
       <c r="R238" t="n">
-        <v>6670404</v>
+        <v>6670761</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -16118,48 +16118,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129112588</v>
+        <v>129108149</v>
       </c>
       <c r="B134" t="n">
-        <v>79581</v>
+        <v>91326</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1352</v>
+        <v>3215</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>707101</v>
+        <v>707011</v>
       </c>
       <c r="R134" t="n">
-        <v>6670297</v>
+        <v>6670734</v>
       </c>
       <c r="S134" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16215,48 +16215,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129108149</v>
+        <v>129110669</v>
       </c>
       <c r="B135" t="n">
-        <v>91326</v>
+        <v>80149</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3215</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>707011</v>
+        <v>706880</v>
       </c>
       <c r="R135" t="n">
-        <v>6670734</v>
+        <v>6670333</v>
       </c>
       <c r="S135" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16312,32 +16312,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129112087</v>
+        <v>129112482</v>
       </c>
       <c r="B136" t="n">
-        <v>92847</v>
+        <v>80149</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16347,10 +16347,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>707031</v>
+        <v>707055</v>
       </c>
       <c r="R136" t="n">
-        <v>6670179</v>
+        <v>6670286</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16409,10 +16409,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129110669</v>
+        <v>129112588</v>
       </c>
       <c r="B137" t="n">
-        <v>80149</v>
+        <v>79581</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16420,21 +16420,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>1352</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16444,13 +16444,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>706880</v>
+        <v>707101</v>
       </c>
       <c r="R137" t="n">
-        <v>6670333</v>
+        <v>6670297</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16506,32 +16506,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129112482</v>
+        <v>129112087</v>
       </c>
       <c r="B138" t="n">
-        <v>80149</v>
+        <v>92847</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16541,10 +16541,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>707055</v>
+        <v>707031</v>
       </c>
       <c r="R138" t="n">
-        <v>6670286</v>
+        <v>6670179</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16700,57 +16700,48 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129108341</v>
+        <v>129112389</v>
       </c>
       <c r="B140" t="n">
-        <v>98633</v>
+        <v>102974</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>504</v>
+        <v>223246</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>706937</v>
+        <v>707049</v>
       </c>
       <c r="R140" t="n">
-        <v>6670745</v>
+        <v>6670267</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16806,48 +16797,57 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129110670</v>
+        <v>129108341</v>
       </c>
       <c r="B141" t="n">
-        <v>91995</v>
+        <v>98633</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1619</v>
+        <v>504</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Apelticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Aurantiporus fissilis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>706880</v>
+        <v>706937</v>
       </c>
       <c r="R141" t="n">
-        <v>6670333</v>
+        <v>6670745</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16899,53 +16899,49 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY141" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129114059</v>
+        <v>129110670</v>
       </c>
       <c r="B142" t="n">
-        <v>80149</v>
+        <v>91995</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>1619</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Apelticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Aurantiporus fissilis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>707168</v>
+        <v>706880</v>
       </c>
       <c r="R142" t="n">
-        <v>6670669</v>
+        <v>6670333</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17000,14 +16996,18 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY142" t="inlineStr"/>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129113907</v>
+        <v>129114059</v>
       </c>
       <c r="B143" t="n">
-        <v>87005</v>
+        <v>80149</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17015,21 +17015,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6003295</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -17039,10 +17039,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>707129</v>
+        <v>707168</v>
       </c>
       <c r="R143" t="n">
-        <v>6670627</v>
+        <v>6670669</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17101,45 +17101,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129112389</v>
+        <v>129113907</v>
       </c>
       <c r="B144" t="n">
-        <v>102974</v>
+        <v>87005</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>223246</v>
+        <v>6003295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>707049</v>
+        <v>707129</v>
       </c>
       <c r="R144" t="n">
-        <v>6670267</v>
+        <v>6670627</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17198,10 +17198,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129108051</v>
+        <v>129108937</v>
       </c>
       <c r="B145" t="n">
-        <v>98705</v>
+        <v>91326</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17209,21 +17209,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17233,10 +17233,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>707017</v>
+        <v>707027</v>
       </c>
       <c r="R145" t="n">
-        <v>6670761</v>
+        <v>6670701</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17392,45 +17392,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129108937</v>
+        <v>129109792</v>
       </c>
       <c r="B147" t="n">
-        <v>91326</v>
+        <v>80149</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3215</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>707027</v>
+        <v>706790</v>
       </c>
       <c r="R147" t="n">
-        <v>6670701</v>
+        <v>6670404</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17489,45 +17489,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129109792</v>
+        <v>129108051</v>
       </c>
       <c r="B148" t="n">
-        <v>80149</v>
+        <v>98705</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>219798</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>706790</v>
+        <v>707017</v>
       </c>
       <c r="R148" t="n">
-        <v>6670404</v>
+        <v>6670761</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17780,10 +17780,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129112791</v>
+        <v>129112466</v>
       </c>
       <c r="B151" t="n">
-        <v>91610</v>
+        <v>91537</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17791,37 +17791,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5321</v>
+        <v>4660</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>707141</v>
+        <v>707055</v>
       </c>
       <c r="R151" t="n">
-        <v>6670348</v>
+        <v>6670286</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17877,32 +17877,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129111060</v>
+        <v>129112646</v>
       </c>
       <c r="B152" t="n">
-        <v>92043</v>
+        <v>99946</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5469</v>
+        <v>174</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kärrvaxskinn</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phlebiodontia subochracea</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17912,13 +17912,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>706998</v>
+        <v>707129</v>
       </c>
       <c r="R152" t="n">
-        <v>6670322</v>
+        <v>6670306</v>
       </c>
       <c r="S152" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17974,32 +17974,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129112646</v>
+        <v>129111060</v>
       </c>
       <c r="B153" t="n">
-        <v>99946</v>
+        <v>92043</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>174</v>
+        <v>5469</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Kärrvaxskinn</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Phlebiodontia subochracea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18009,13 +18009,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>707129</v>
+        <v>706998</v>
       </c>
       <c r="R153" t="n">
-        <v>6670306</v>
+        <v>6670322</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18071,10 +18071,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129112466</v>
+        <v>129112791</v>
       </c>
       <c r="B154" t="n">
-        <v>91537</v>
+        <v>91610</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18082,37 +18082,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4660</v>
+        <v>5321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>707055</v>
+        <v>707141</v>
       </c>
       <c r="R154" t="n">
-        <v>6670286</v>
+        <v>6670348</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -18265,10 +18265,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129113068</v>
+        <v>129113229</v>
       </c>
       <c r="B156" t="n">
-        <v>110858</v>
+        <v>92871</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18276,21 +18276,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18300,13 +18300,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>707202</v>
+        <v>707145</v>
       </c>
       <c r="R156" t="n">
-        <v>6670431</v>
+        <v>6670534</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129113229</v>
+        <v>129110999</v>
       </c>
       <c r="B157" t="n">
-        <v>92871</v>
+        <v>92508</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18373,37 +18373,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>707145</v>
+        <v>707002</v>
       </c>
       <c r="R157" t="n">
-        <v>6670534</v>
+        <v>6670297</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18556,10 +18556,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129110999</v>
+        <v>129113068</v>
       </c>
       <c r="B159" t="n">
-        <v>92508</v>
+        <v>110858</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18567,37 +18567,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4769</v>
+        <v>219711</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>707002</v>
+        <v>707202</v>
       </c>
       <c r="R159" t="n">
-        <v>6670297</v>
+        <v>6670431</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18750,10 +18750,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129108270</v>
+        <v>129109134</v>
       </c>
       <c r="B161" t="n">
-        <v>92847</v>
+        <v>98633</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18761,34 +18761,43 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4366</v>
+        <v>504</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>706961</v>
+        <v>706945</v>
       </c>
       <c r="R161" t="n">
-        <v>6670741</v>
+        <v>6670657</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18847,10 +18856,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129112708</v>
+        <v>129108270</v>
       </c>
       <c r="B162" t="n">
-        <v>110858</v>
+        <v>92847</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18858,34 +18867,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>707129</v>
+        <v>706961</v>
       </c>
       <c r="R162" t="n">
-        <v>6670306</v>
+        <v>6670741</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18944,54 +18953,56 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129109134</v>
+        <v>129111656</v>
       </c>
       <c r="B163" t="n">
-        <v>98633</v>
+        <v>90347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>504</v>
+        <v>6003116</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Davidmusseron</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tricholoma ilkkae</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Mort.Chr. &amp; al.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>706945</v>
+        <v>707000</v>
       </c>
       <c r="R163" t="n">
-        <v>6670657</v>
+        <v>6670196</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19032,8 +19043,24 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
+        </is>
+      </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
@@ -19046,60 +19073,53 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY163" t="inlineStr"/>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129111656</v>
+        <v>129112708</v>
       </c>
       <c r="B164" t="n">
-        <v>90347</v>
+        <v>110858</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6003116</v>
+        <v>219711</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Davidmusseron</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tricholoma ilkkae</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>707000</v>
+        <v>707129</v>
       </c>
       <c r="R164" t="n">
-        <v>6670196</v>
+        <v>6670306</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19140,24 +19160,8 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
-        </is>
-      </c>
-      <c r="AL164" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -19170,56 +19174,52 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129114112</v>
+        <v>129112397</v>
       </c>
       <c r="B165" t="n">
-        <v>86968</v>
+        <v>86988</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3674</v>
+        <v>460</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Cordier) Gillet</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>707154</v>
+        <v>707055</v>
       </c>
       <c r="R165" t="n">
-        <v>6670701</v>
+        <v>6670286</v>
       </c>
       <c r="S165" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19275,10 +19275,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129108500</v>
+        <v>129108054</v>
       </c>
       <c r="B166" t="n">
-        <v>88761</v>
+        <v>98633</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19286,21 +19286,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4394</v>
+        <v>504</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19310,10 +19310,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>706954</v>
+        <v>707017</v>
       </c>
       <c r="R166" t="n">
-        <v>6670717</v>
+        <v>6670761</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19372,10 +19372,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129109788</v>
+        <v>129112386</v>
       </c>
       <c r="B167" t="n">
-        <v>110858</v>
+        <v>99946</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19383,34 +19383,46 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>219711</v>
+        <v>174</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>706790</v>
+        <v>707049</v>
       </c>
       <c r="R167" t="n">
-        <v>6670404</v>
+        <v>6670267</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19445,12 +19457,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Stort bestånd.</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -19469,10 +19487,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129109137</v>
+        <v>129114112</v>
       </c>
       <c r="B168" t="n">
-        <v>101823</v>
+        <v>86968</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19480,21 +19498,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221235</v>
+        <v>3674</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -19504,13 +19522,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>706945</v>
+        <v>707154</v>
       </c>
       <c r="R168" t="n">
-        <v>6670657</v>
+        <v>6670701</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19566,10 +19584,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129109813</v>
+        <v>129108500</v>
       </c>
       <c r="B169" t="n">
-        <v>100821</v>
+        <v>88761</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19577,34 +19595,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>222771</v>
+        <v>4394</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>706790</v>
+        <v>706954</v>
       </c>
       <c r="R169" t="n">
-        <v>6670404</v>
+        <v>6670717</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19663,32 +19681,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129110603</v>
+        <v>129112545</v>
       </c>
       <c r="B170" t="n">
-        <v>102974</v>
+        <v>79663</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>223246</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19698,10 +19716,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>706848</v>
+        <v>707088</v>
       </c>
       <c r="R170" t="n">
-        <v>6670352</v>
+        <v>6670309</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19760,48 +19778,48 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129113794</v>
+        <v>129109788</v>
       </c>
       <c r="B171" t="n">
-        <v>87005</v>
+        <v>110858</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6003295</v>
+        <v>219711</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>707144</v>
+        <v>706790</v>
       </c>
       <c r="R171" t="n">
-        <v>6670568</v>
+        <v>6670404</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19954,45 +19972,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129112545</v>
+        <v>129109137</v>
       </c>
       <c r="B173" t="n">
-        <v>79663</v>
+        <v>101823</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>221235</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>707088</v>
+        <v>706945</v>
       </c>
       <c r="R173" t="n">
-        <v>6670309</v>
+        <v>6670657</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20051,10 +20069,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129112386</v>
+        <v>129109813</v>
       </c>
       <c r="B174" t="n">
-        <v>99946</v>
+        <v>100821</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20062,46 +20080,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>174</v>
+        <v>222771</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>707049</v>
+        <v>706790</v>
       </c>
       <c r="R174" t="n">
-        <v>6670267</v>
+        <v>6670404</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20136,18 +20142,12 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Stort bestånd.</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -20166,32 +20166,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129112397</v>
+        <v>129110603</v>
       </c>
       <c r="B175" t="n">
-        <v>86988</v>
+        <v>102974</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>460</v>
+        <v>223246</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20201,10 +20201,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>707055</v>
+        <v>706848</v>
       </c>
       <c r="R175" t="n">
-        <v>6670286</v>
+        <v>6670352</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20263,48 +20263,48 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129108054</v>
+        <v>129113794</v>
       </c>
       <c r="B176" t="n">
-        <v>98633</v>
+        <v>87005</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>504</v>
+        <v>6003295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>707017</v>
+        <v>707144</v>
       </c>
       <c r="R176" t="n">
-        <v>6670761</v>
+        <v>6670568</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20457,48 +20457,48 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129113803</v>
+        <v>129108275</v>
       </c>
       <c r="B178" t="n">
-        <v>91326</v>
+        <v>87027</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3215</v>
+        <v>449</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>707144</v>
+        <v>706961</v>
       </c>
       <c r="R178" t="n">
-        <v>6670568</v>
+        <v>6670741</v>
       </c>
       <c r="S178" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20554,48 +20554,48 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129108275</v>
+        <v>129113803</v>
       </c>
       <c r="B179" t="n">
-        <v>87027</v>
+        <v>91326</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>449</v>
+        <v>3215</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>706961</v>
+        <v>707144</v>
       </c>
       <c r="R179" t="n">
-        <v>6670741</v>
+        <v>6670568</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20651,10 +20651,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129108563</v>
+        <v>129109796</v>
       </c>
       <c r="B180" t="n">
-        <v>98633</v>
+        <v>91564</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20662,37 +20662,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>504</v>
+        <v>1205</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>706958</v>
+        <v>706790</v>
       </c>
       <c r="R180" t="n">
-        <v>6670705</v>
+        <v>6670404</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20748,10 +20748,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129110811</v>
+        <v>129111132</v>
       </c>
       <c r="B181" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20759,21 +20759,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20783,10 +20783,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>706912</v>
+        <v>707028</v>
       </c>
       <c r="R181" t="n">
-        <v>6670280</v>
+        <v>6670245</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20845,48 +20845,48 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129111077</v>
+        <v>129108563</v>
       </c>
       <c r="B182" t="n">
-        <v>80149</v>
+        <v>98633</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>706998</v>
+        <v>706958</v>
       </c>
       <c r="R182" t="n">
-        <v>6670322</v>
+        <v>6670705</v>
       </c>
       <c r="S182" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20942,10 +20942,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129111132</v>
+        <v>129109438</v>
       </c>
       <c r="B183" t="n">
-        <v>91553</v>
+        <v>92873</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20953,34 +20953,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>707028</v>
+        <v>706816</v>
       </c>
       <c r="R183" t="n">
-        <v>6670245</v>
+        <v>6670564</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21039,32 +21039,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129109796</v>
+        <v>129110811</v>
       </c>
       <c r="B184" t="n">
-        <v>91564</v>
+        <v>80149</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21074,10 +21074,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>706790</v>
+        <v>706912</v>
       </c>
       <c r="R184" t="n">
-        <v>6670404</v>
+        <v>6670280</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21136,10 +21136,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129109438</v>
+        <v>129111077</v>
       </c>
       <c r="B185" t="n">
-        <v>92873</v>
+        <v>80149</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21147,37 +21147,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>706816</v>
+        <v>706998</v>
       </c>
       <c r="R185" t="n">
-        <v>6670564</v>
+        <v>6670322</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21736,10 +21736,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129109832</v>
+        <v>129108900</v>
       </c>
       <c r="B191" t="n">
-        <v>91610</v>
+        <v>86968</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21747,34 +21747,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5321</v>
+        <v>3674</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>706793</v>
+        <v>707027</v>
       </c>
       <c r="R191" t="n">
-        <v>6670414</v>
+        <v>6670701</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21833,10 +21833,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129108900</v>
+        <v>129109832</v>
       </c>
       <c r="B192" t="n">
-        <v>86968</v>
+        <v>91610</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21844,34 +21844,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>3674</v>
+        <v>5321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>707027</v>
+        <v>706793</v>
       </c>
       <c r="R192" t="n">
-        <v>6670701</v>
+        <v>6670414</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22613,54 +22613,45 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129108856</v>
+        <v>129112405</v>
       </c>
       <c r="B200" t="n">
-        <v>98633</v>
+        <v>91113</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>504</v>
+        <v>937</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>707027</v>
+        <v>707055</v>
       </c>
       <c r="R200" t="n">
-        <v>6670701</v>
+        <v>6670286</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22816,45 +22807,54 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129112405</v>
+        <v>129108856</v>
       </c>
       <c r="B202" t="n">
-        <v>91113</v>
+        <v>98633</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>937</v>
+        <v>504</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>707055</v>
+        <v>707027</v>
       </c>
       <c r="R202" t="n">
-        <v>6670286</v>
+        <v>6670701</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23204,32 +23204,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129112015</v>
+        <v>129110527</v>
       </c>
       <c r="B206" t="n">
-        <v>87005</v>
+        <v>4995</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6003295</v>
+        <v>100517</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Åttafläckig praktbagge</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Buprestis octoguttata</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23239,10 +23239,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>707031</v>
+        <v>706802</v>
       </c>
       <c r="R206" t="n">
-        <v>6670179</v>
+        <v>6670363</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23301,10 +23301,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129109887</v>
+        <v>129112015</v>
       </c>
       <c r="B207" t="n">
-        <v>88759</v>
+        <v>87005</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23312,21 +23312,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>805</v>
+        <v>6003295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23336,10 +23336,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>706822</v>
+        <v>707031</v>
       </c>
       <c r="R207" t="n">
-        <v>6670378</v>
+        <v>6670179</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23491,32 +23491,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129108141</v>
+        <v>129108444</v>
       </c>
       <c r="B209" t="n">
-        <v>92871</v>
+        <v>91088</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23526,13 +23526,13 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>707011</v>
+        <v>706954</v>
       </c>
       <c r="R209" t="n">
-        <v>6670734</v>
+        <v>6670717</v>
       </c>
       <c r="S209" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23588,32 +23588,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129108444</v>
+        <v>129108141</v>
       </c>
       <c r="B210" t="n">
-        <v>91088</v>
+        <v>92871</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23623,13 +23623,13 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>706954</v>
+        <v>707011</v>
       </c>
       <c r="R210" t="n">
-        <v>6670717</v>
+        <v>6670734</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23685,48 +23685,48 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129112905</v>
+        <v>129110564</v>
       </c>
       <c r="B211" t="n">
-        <v>80149</v>
+        <v>91610</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6458</v>
+        <v>5321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>707166</v>
+        <v>706831</v>
       </c>
       <c r="R211" t="n">
-        <v>6670369</v>
+        <v>6670326</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23782,45 +23782,45 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129110527</v>
+        <v>129112905</v>
       </c>
       <c r="B212" t="n">
-        <v>4995</v>
+        <v>80149</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100517</v>
+        <v>6458</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Åttafläckig praktbagge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Buprestis octoguttata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>706802</v>
+        <v>707166</v>
       </c>
       <c r="R212" t="n">
-        <v>6670363</v>
+        <v>6670369</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23879,32 +23879,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129110564</v>
+        <v>129109887</v>
       </c>
       <c r="B213" t="n">
-        <v>91610</v>
+        <v>88759</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>5321</v>
+        <v>805</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23914,13 +23914,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>706831</v>
+        <v>706822</v>
       </c>
       <c r="R213" t="n">
-        <v>6670326</v>
+        <v>6670378</v>
       </c>
       <c r="S213" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23976,10 +23976,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129108289</v>
+        <v>129114035</v>
       </c>
       <c r="B214" t="n">
-        <v>43982</v>
+        <v>86806</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23987,37 +23987,37 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>101735</v>
+        <v>3762</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>706961</v>
+        <v>707165</v>
       </c>
       <c r="R214" t="n">
-        <v>6670741</v>
+        <v>6670655</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129114035</v>
+        <v>129110955</v>
       </c>
       <c r="B215" t="n">
         <v>86806</v>
@@ -24104,17 +24104,17 @@
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>707165</v>
+        <v>706983</v>
       </c>
       <c r="R215" t="n">
-        <v>6670655</v>
+        <v>6670276</v>
       </c>
       <c r="S215" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24170,45 +24170,45 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129110955</v>
+        <v>129113073</v>
       </c>
       <c r="B216" t="n">
-        <v>86806</v>
+        <v>80149</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>3762</v>
+        <v>6458</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>706983</v>
+        <v>707212</v>
       </c>
       <c r="R216" t="n">
-        <v>6670276</v>
+        <v>6670436</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24267,45 +24267,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129113073</v>
+        <v>129108289</v>
       </c>
       <c r="B217" t="n">
-        <v>80149</v>
+        <v>43982</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6458</v>
+        <v>101735</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>707212</v>
+        <v>706961</v>
       </c>
       <c r="R217" t="n">
-        <v>6670436</v>
+        <v>6670741</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24364,10 +24364,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129111662</v>
+        <v>129108076</v>
       </c>
       <c r="B218" t="n">
-        <v>92847</v>
+        <v>101823</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24375,37 +24375,37 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4366</v>
+        <v>221235</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>707011</v>
+        <v>707017</v>
       </c>
       <c r="R218" t="n">
-        <v>6670220</v>
+        <v>6670761</v>
       </c>
       <c r="S218" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24461,10 +24461,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129108076</v>
+        <v>129111662</v>
       </c>
       <c r="B219" t="n">
-        <v>101823</v>
+        <v>92847</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24472,37 +24472,37 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221235</v>
+        <v>4366</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>707017</v>
+        <v>707011</v>
       </c>
       <c r="R219" t="n">
-        <v>6670761</v>
+        <v>6670220</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24659,10 +24659,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129108567</v>
+        <v>129112862</v>
       </c>
       <c r="B221" t="n">
-        <v>86806</v>
+        <v>96073</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24670,37 +24670,37 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>3762</v>
+        <v>2818</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>706958</v>
+        <v>707141</v>
       </c>
       <c r="R221" t="n">
-        <v>6670705</v>
+        <v>6670348</v>
       </c>
       <c r="S221" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24756,10 +24756,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129112111</v>
+        <v>129108567</v>
       </c>
       <c r="B222" t="n">
-        <v>92871</v>
+        <v>86806</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24767,34 +24767,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>707012</v>
+        <v>706958</v>
       </c>
       <c r="R222" t="n">
-        <v>6670187</v>
+        <v>6670705</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -24853,10 +24853,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129112862</v>
+        <v>129112111</v>
       </c>
       <c r="B223" t="n">
-        <v>96073</v>
+        <v>92871</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24864,37 +24864,37 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2818</v>
+        <v>5964</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>707141</v>
+        <v>707012</v>
       </c>
       <c r="R223" t="n">
-        <v>6670348</v>
+        <v>6670187</v>
       </c>
       <c r="S223" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -25042,48 +25042,48 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129108343</v>
+        <v>129112901</v>
       </c>
       <c r="B225" t="n">
-        <v>92508</v>
+        <v>91113</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4769</v>
+        <v>937</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>706937</v>
+        <v>707166</v>
       </c>
       <c r="R225" t="n">
-        <v>6670745</v>
+        <v>6670369</v>
       </c>
       <c r="S225" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -25245,48 +25245,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129112901</v>
+        <v>129108591</v>
       </c>
       <c r="B227" t="n">
-        <v>91113</v>
+        <v>92508</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>937</v>
+        <v>4769</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>707166</v>
+        <v>706958</v>
       </c>
       <c r="R227" t="n">
-        <v>6670369</v>
+        <v>6670705</v>
       </c>
       <c r="S227" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129108591</v>
+        <v>129108343</v>
       </c>
       <c r="B228" t="n">
         <v>92508</v>
@@ -25377,10 +25377,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>706958</v>
+        <v>706937</v>
       </c>
       <c r="R228" t="n">
-        <v>6670705</v>
+        <v>6670745</v>
       </c>
       <c r="S228" t="n">
         <v>15</v>
@@ -25730,45 +25730,45 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129109932</v>
+        <v>129108929</v>
       </c>
       <c r="B232" t="n">
-        <v>5493</v>
+        <v>92871</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>101410</v>
+        <v>5964</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>706801</v>
+        <v>707027</v>
       </c>
       <c r="R232" t="n">
-        <v>6670352</v>
+        <v>6670701</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25924,45 +25924,45 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129108929</v>
+        <v>129109932</v>
       </c>
       <c r="B234" t="n">
-        <v>92871</v>
+        <v>5493</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5964</v>
+        <v>101410</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>707027</v>
+        <v>706801</v>
       </c>
       <c r="R234" t="n">
-        <v>6670701</v>
+        <v>6670352</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26021,10 +26021,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129108620</v>
+        <v>129108059</v>
       </c>
       <c r="B235" t="n">
-        <v>98749</v>
+        <v>92508</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26032,21 +26032,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>219862</v>
+        <v>4769</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -26056,10 +26056,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>706971</v>
+        <v>707017</v>
       </c>
       <c r="R235" t="n">
-        <v>6670688</v>
+        <v>6670761</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26118,10 +26118,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129109794</v>
+        <v>129108620</v>
       </c>
       <c r="B236" t="n">
-        <v>104198</v>
+        <v>98749</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26129,34 +26129,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>706790</v>
+        <v>706971</v>
       </c>
       <c r="R236" t="n">
-        <v>6670404</v>
+        <v>6670688</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26312,10 +26312,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129108059</v>
+        <v>129109794</v>
       </c>
       <c r="B238" t="n">
-        <v>92508</v>
+        <v>104198</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26323,34 +26323,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>707017</v>
+        <v>706790</v>
       </c>
       <c r="R238" t="n">
-        <v>6670761</v>
+        <v>6670404</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -16118,10 +16118,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129108149</v>
+        <v>129112087</v>
       </c>
       <c r="B134" t="n">
-        <v>91326</v>
+        <v>92847</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16129,37 +16129,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3215</v>
+        <v>4366</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>707011</v>
+        <v>707031</v>
       </c>
       <c r="R134" t="n">
-        <v>6670734</v>
+        <v>6670179</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16215,48 +16215,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129110669</v>
+        <v>129108149</v>
       </c>
       <c r="B135" t="n">
-        <v>80149</v>
+        <v>91326</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>706880</v>
+        <v>707011</v>
       </c>
       <c r="R135" t="n">
-        <v>6670333</v>
+        <v>6670734</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16312,10 +16312,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129112482</v>
+        <v>129112588</v>
       </c>
       <c r="B136" t="n">
-        <v>80149</v>
+        <v>79581</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16323,21 +16323,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>1352</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16347,13 +16347,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>707055</v>
+        <v>707101</v>
       </c>
       <c r="R136" t="n">
-        <v>6670286</v>
+        <v>6670297</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16409,10 +16409,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129112588</v>
+        <v>129110669</v>
       </c>
       <c r="B137" t="n">
-        <v>79581</v>
+        <v>80149</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16420,21 +16420,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1352</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16444,13 +16444,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>707101</v>
+        <v>706880</v>
       </c>
       <c r="R137" t="n">
-        <v>6670297</v>
+        <v>6670333</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16506,32 +16506,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129112087</v>
+        <v>129112482</v>
       </c>
       <c r="B138" t="n">
-        <v>92847</v>
+        <v>80149</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16541,10 +16541,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>707031</v>
+        <v>707055</v>
       </c>
       <c r="R138" t="n">
-        <v>6670179</v>
+        <v>6670286</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17198,45 +17198,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129108937</v>
+        <v>129112698</v>
       </c>
       <c r="B145" t="n">
-        <v>91326</v>
+        <v>86988</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3215</v>
+        <v>460</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Cordier) Gillet</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>707027</v>
+        <v>707129</v>
       </c>
       <c r="R145" t="n">
-        <v>6670701</v>
+        <v>6670306</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17295,45 +17295,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129112698</v>
+        <v>129108937</v>
       </c>
       <c r="B146" t="n">
-        <v>86988</v>
+        <v>91326</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>460</v>
+        <v>3215</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>707129</v>
+        <v>707027</v>
       </c>
       <c r="R146" t="n">
-        <v>6670306</v>
+        <v>6670701</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17586,48 +17586,48 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129112890</v>
+        <v>129112646</v>
       </c>
       <c r="B149" t="n">
-        <v>91113</v>
+        <v>99946</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>937</v>
+        <v>174</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>707141</v>
+        <v>707129</v>
       </c>
       <c r="R149" t="n">
-        <v>6670348</v>
+        <v>6670306</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17683,48 +17683,48 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129114030</v>
+        <v>129112890</v>
       </c>
       <c r="B150" t="n">
-        <v>91326</v>
+        <v>91113</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3215</v>
+        <v>937</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>707151</v>
+        <v>707141</v>
       </c>
       <c r="R150" t="n">
-        <v>6670622</v>
+        <v>6670348</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17780,10 +17780,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129112466</v>
+        <v>129114030</v>
       </c>
       <c r="B151" t="n">
-        <v>91537</v>
+        <v>91326</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17791,34 +17791,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4660</v>
+        <v>3215</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>707055</v>
+        <v>707151</v>
       </c>
       <c r="R151" t="n">
-        <v>6670286</v>
+        <v>6670622</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17877,10 +17877,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129112646</v>
+        <v>129112791</v>
       </c>
       <c r="B152" t="n">
-        <v>99946</v>
+        <v>91610</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17888,37 +17888,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>174</v>
+        <v>5321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>707129</v>
+        <v>707141</v>
       </c>
       <c r="R152" t="n">
-        <v>6670306</v>
+        <v>6670348</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -18071,10 +18071,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129112791</v>
+        <v>129112466</v>
       </c>
       <c r="B154" t="n">
-        <v>91610</v>
+        <v>91537</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18082,37 +18082,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5321</v>
+        <v>4660</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>707141</v>
+        <v>707055</v>
       </c>
       <c r="R154" t="n">
-        <v>6670348</v>
+        <v>6670286</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -18168,45 +18168,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129112925</v>
+        <v>129110999</v>
       </c>
       <c r="B155" t="n">
-        <v>91113</v>
+        <v>92508</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>937</v>
+        <v>4769</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>707185</v>
+        <v>707002</v>
       </c>
       <c r="R155" t="n">
-        <v>6670371</v>
+        <v>6670297</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18265,32 +18265,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129113229</v>
+        <v>129112925</v>
       </c>
       <c r="B156" t="n">
-        <v>92871</v>
+        <v>91113</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5964</v>
+        <v>937</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18300,13 +18300,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>707145</v>
+        <v>707185</v>
       </c>
       <c r="R156" t="n">
-        <v>6670534</v>
+        <v>6670371</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129110999</v>
+        <v>129113229</v>
       </c>
       <c r="B157" t="n">
-        <v>92508</v>
+        <v>92871</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18373,37 +18373,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>707002</v>
+        <v>707145</v>
       </c>
       <c r="R157" t="n">
-        <v>6670297</v>
+        <v>6670534</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18653,45 +18653,56 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129113903</v>
+        <v>129111656</v>
       </c>
       <c r="B160" t="n">
-        <v>92271</v>
+        <v>90347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3298</v>
+        <v>6003116</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Davidmusseron</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tricholoma ilkkae</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>Mort.Chr. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>707129</v>
+        <v>707000</v>
       </c>
       <c r="R160" t="n">
-        <v>6670627</v>
+        <v>6670196</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18732,8 +18743,24 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
@@ -18746,7 +18773,11 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY160" t="inlineStr"/>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18953,56 +18984,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129111656</v>
+        <v>129113903</v>
       </c>
       <c r="B163" t="n">
-        <v>90347</v>
+        <v>92271</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6003116</v>
+        <v>3298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Davidmusseron</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tricholoma ilkkae</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>707000</v>
+        <v>707129</v>
       </c>
       <c r="R163" t="n">
-        <v>6670196</v>
+        <v>6670627</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19043,24 +19063,8 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
-        </is>
-      </c>
-      <c r="AL163" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
@@ -19073,11 +19077,7 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19178,45 +19178,57 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129112397</v>
+        <v>129112386</v>
       </c>
       <c r="B165" t="n">
-        <v>86988</v>
+        <v>99946</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>460</v>
+        <v>174</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>707055</v>
+        <v>707049</v>
       </c>
       <c r="R165" t="n">
-        <v>6670286</v>
+        <v>6670267</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19251,12 +19263,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Stort bestånd.</t>
+        </is>
+      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -19275,10 +19293,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129108054</v>
+        <v>129108500</v>
       </c>
       <c r="B166" t="n">
-        <v>98633</v>
+        <v>88761</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19286,21 +19304,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>504</v>
+        <v>4394</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19310,10 +19328,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>707017</v>
+        <v>706954</v>
       </c>
       <c r="R166" t="n">
-        <v>6670761</v>
+        <v>6670717</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19372,10 +19390,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129112386</v>
+        <v>129114112</v>
       </c>
       <c r="B167" t="n">
-        <v>99946</v>
+        <v>86968</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19383,49 +19401,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>174</v>
+        <v>3674</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>707049</v>
+        <v>707154</v>
       </c>
       <c r="R167" t="n">
-        <v>6670267</v>
+        <v>6670701</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19457,18 +19463,12 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Stort bestånd.</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -19487,48 +19487,48 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129114112</v>
+        <v>129112545</v>
       </c>
       <c r="B168" t="n">
-        <v>86968</v>
+        <v>79663</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3674</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>707154</v>
+        <v>707088</v>
       </c>
       <c r="R168" t="n">
-        <v>6670701</v>
+        <v>6670309</v>
       </c>
       <c r="S168" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19584,10 +19584,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129108500</v>
+        <v>129107991</v>
       </c>
       <c r="B169" t="n">
-        <v>88761</v>
+        <v>8439</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19595,21 +19595,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4394</v>
+        <v>106554</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19619,13 +19619,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>706954</v>
+        <v>706990</v>
       </c>
       <c r="R169" t="n">
-        <v>6670717</v>
+        <v>6670767</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19681,32 +19681,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129112545</v>
+        <v>129109788</v>
       </c>
       <c r="B170" t="n">
-        <v>79663</v>
+        <v>110858</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>219711</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19716,10 +19716,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>707088</v>
+        <v>706790</v>
       </c>
       <c r="R170" t="n">
-        <v>6670309</v>
+        <v>6670404</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19778,10 +19778,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129109788</v>
+        <v>129109813</v>
       </c>
       <c r="B171" t="n">
-        <v>110858</v>
+        <v>100821</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19789,16 +19789,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>219711</v>
+        <v>222771</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -19875,48 +19875,48 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129107991</v>
+        <v>129110603</v>
       </c>
       <c r="B172" t="n">
-        <v>8439</v>
+        <v>102974</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>106554</v>
+        <v>223246</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>706990</v>
+        <v>706848</v>
       </c>
       <c r="R172" t="n">
-        <v>6670767</v>
+        <v>6670352</v>
       </c>
       <c r="S172" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19972,32 +19972,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129109137</v>
+        <v>129113794</v>
       </c>
       <c r="B173" t="n">
-        <v>101823</v>
+        <v>87005</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>221235</v>
+        <v>6003295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -20007,13 +20007,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>706945</v>
+        <v>707144</v>
       </c>
       <c r="R173" t="n">
-        <v>6670657</v>
+        <v>6670568</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -20069,10 +20069,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129109813</v>
+        <v>129109137</v>
       </c>
       <c r="B174" t="n">
-        <v>100821</v>
+        <v>101823</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20080,34 +20080,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>706790</v>
+        <v>706945</v>
       </c>
       <c r="R174" t="n">
-        <v>6670404</v>
+        <v>6670657</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20166,32 +20166,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129110603</v>
+        <v>129112397</v>
       </c>
       <c r="B175" t="n">
-        <v>102974</v>
+        <v>86988</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>223246</v>
+        <v>460</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Cordier) Gillet</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20201,10 +20201,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>706848</v>
+        <v>707055</v>
       </c>
       <c r="R175" t="n">
-        <v>6670352</v>
+        <v>6670286</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20263,48 +20263,48 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129113794</v>
+        <v>129108054</v>
       </c>
       <c r="B176" t="n">
-        <v>87005</v>
+        <v>98633</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6003295</v>
+        <v>504</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>707144</v>
+        <v>707017</v>
       </c>
       <c r="R176" t="n">
-        <v>6670568</v>
+        <v>6670761</v>
       </c>
       <c r="S176" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20360,32 +20360,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129108056</v>
+        <v>129108275</v>
       </c>
       <c r="B177" t="n">
-        <v>98749</v>
+        <v>87027</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20395,10 +20395,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>707017</v>
+        <v>706961</v>
       </c>
       <c r="R177" t="n">
-        <v>6670761</v>
+        <v>6670741</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20457,32 +20457,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129108275</v>
+        <v>129108056</v>
       </c>
       <c r="B178" t="n">
-        <v>87027</v>
+        <v>98749</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20492,10 +20492,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>706961</v>
+        <v>707017</v>
       </c>
       <c r="R178" t="n">
-        <v>6670741</v>
+        <v>6670761</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20651,32 +20651,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129109796</v>
+        <v>129110679</v>
       </c>
       <c r="B180" t="n">
-        <v>91564</v>
+        <v>106355</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1205</v>
+        <v>220785</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20686,10 +20686,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>706790</v>
+        <v>706880</v>
       </c>
       <c r="R180" t="n">
-        <v>6670404</v>
+        <v>6670333</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20748,48 +20748,48 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129111132</v>
+        <v>129108563</v>
       </c>
       <c r="B181" t="n">
-        <v>91553</v>
+        <v>98633</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1202</v>
+        <v>504</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>707028</v>
+        <v>706958</v>
       </c>
       <c r="R181" t="n">
-        <v>6670245</v>
+        <v>6670705</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20845,10 +20845,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129108563</v>
+        <v>129109796</v>
       </c>
       <c r="B182" t="n">
-        <v>98633</v>
+        <v>91564</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20856,37 +20856,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>504</v>
+        <v>1205</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>706958</v>
+        <v>706790</v>
       </c>
       <c r="R182" t="n">
-        <v>6670705</v>
+        <v>6670404</v>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20942,10 +20942,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129109438</v>
+        <v>129111132</v>
       </c>
       <c r="B183" t="n">
-        <v>92873</v>
+        <v>91553</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20953,34 +20953,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>706816</v>
+        <v>707028</v>
       </c>
       <c r="R183" t="n">
-        <v>6670564</v>
+        <v>6670245</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21039,10 +21039,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129110811</v>
+        <v>129109438</v>
       </c>
       <c r="B184" t="n">
-        <v>80149</v>
+        <v>92873</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21050,34 +21050,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>706912</v>
+        <v>706816</v>
       </c>
       <c r="R184" t="n">
-        <v>6670280</v>
+        <v>6670564</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21233,32 +21233,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129110679</v>
+        <v>129110811</v>
       </c>
       <c r="B186" t="n">
-        <v>106355</v>
+        <v>80149</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220785</v>
+        <v>6458</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21268,10 +21268,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>706880</v>
+        <v>706912</v>
       </c>
       <c r="R186" t="n">
-        <v>6670333</v>
+        <v>6670280</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21736,10 +21736,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129108900</v>
+        <v>129109832</v>
       </c>
       <c r="B191" t="n">
-        <v>86968</v>
+        <v>91610</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21747,34 +21747,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3674</v>
+        <v>5321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>707027</v>
+        <v>706793</v>
       </c>
       <c r="R191" t="n">
-        <v>6670701</v>
+        <v>6670414</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21833,10 +21833,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129109832</v>
+        <v>129108900</v>
       </c>
       <c r="B192" t="n">
-        <v>91610</v>
+        <v>86968</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21844,34 +21844,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5321</v>
+        <v>3674</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>706793</v>
+        <v>707027</v>
       </c>
       <c r="R192" t="n">
-        <v>6670414</v>
+        <v>6670701</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22027,45 +22027,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129109340</v>
+        <v>129108939</v>
       </c>
       <c r="B194" t="n">
-        <v>86897</v>
+        <v>110858</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>445</v>
+        <v>219711</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>706839</v>
+        <v>707027</v>
       </c>
       <c r="R194" t="n">
-        <v>6670598</v>
+        <v>6670701</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22120,56 +22120,52 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY194" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129112836</v>
+        <v>129112425</v>
       </c>
       <c r="B195" t="n">
-        <v>91777</v>
+        <v>103252</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1106</v>
+        <v>222002</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>707141</v>
+        <v>707055</v>
       </c>
       <c r="R195" t="n">
-        <v>6670348</v>
+        <v>6670286</v>
       </c>
       <c r="S195" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22225,10 +22221,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129109288</v>
+        <v>129109238</v>
       </c>
       <c r="B196" t="n">
-        <v>91062</v>
+        <v>104198</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22236,21 +22232,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5741</v>
+        <v>222412</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22322,45 +22318,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129108939</v>
+        <v>129109340</v>
       </c>
       <c r="B197" t="n">
-        <v>110858</v>
+        <v>86897</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>219711</v>
+        <v>445</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>707027</v>
+        <v>706839</v>
       </c>
       <c r="R197" t="n">
-        <v>6670701</v>
+        <v>6670598</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22415,52 +22411,56 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY197" t="inlineStr"/>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129112425</v>
+        <v>129112836</v>
       </c>
       <c r="B198" t="n">
-        <v>103252</v>
+        <v>91777</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>222002</v>
+        <v>1106</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>707055</v>
+        <v>707141</v>
       </c>
       <c r="R198" t="n">
-        <v>6670286</v>
+        <v>6670348</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -22516,10 +22516,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129109238</v>
+        <v>129109288</v>
       </c>
       <c r="B199" t="n">
-        <v>104198</v>
+        <v>91062</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22527,21 +22527,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>222412</v>
+        <v>5741</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22710,10 +22710,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129112733</v>
+        <v>129108856</v>
       </c>
       <c r="B201" t="n">
-        <v>90317</v>
+        <v>98633</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22721,34 +22721,43 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1595</v>
+        <v>504</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>707129</v>
+        <v>707027</v>
       </c>
       <c r="R201" t="n">
-        <v>6670306</v>
+        <v>6670701</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22807,10 +22816,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129108856</v>
+        <v>129112733</v>
       </c>
       <c r="B202" t="n">
-        <v>98633</v>
+        <v>90317</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22818,43 +22827,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>504</v>
+        <v>1595</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>707027</v>
+        <v>707129</v>
       </c>
       <c r="R202" t="n">
-        <v>6670701</v>
+        <v>6670306</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23204,32 +23204,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129110527</v>
+        <v>129112015</v>
       </c>
       <c r="B206" t="n">
-        <v>4995</v>
+        <v>87005</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100517</v>
+        <v>6003295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Åttafläckig praktbagge</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Buprestis octoguttata</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23239,10 +23239,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>706802</v>
+        <v>707031</v>
       </c>
       <c r="R206" t="n">
-        <v>6670363</v>
+        <v>6670179</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23301,45 +23301,41 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129112015</v>
+        <v>129108973</v>
       </c>
       <c r="B207" t="n">
-        <v>87005</v>
+        <v>87071</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6003295</v>
+        <v>3624</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>707031</v>
+        <v>707027</v>
       </c>
       <c r="R207" t="n">
-        <v>6670179</v>
+        <v>6670701</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23398,41 +23394,45 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129108973</v>
+        <v>129112905</v>
       </c>
       <c r="B208" t="n">
-        <v>87071</v>
+        <v>80149</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>3624</v>
+        <v>6458</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>707027</v>
+        <v>707166</v>
       </c>
       <c r="R208" t="n">
-        <v>6670701</v>
+        <v>6670369</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23491,45 +23491,45 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129108444</v>
+        <v>129109887</v>
       </c>
       <c r="B209" t="n">
-        <v>91088</v>
+        <v>88759</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>5747</v>
+        <v>805</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>706954</v>
+        <v>706822</v>
       </c>
       <c r="R209" t="n">
-        <v>6670717</v>
+        <v>6670378</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23588,10 +23588,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129108141</v>
+        <v>129110564</v>
       </c>
       <c r="B210" t="n">
-        <v>92871</v>
+        <v>91610</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23599,37 +23599,37 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5964</v>
+        <v>5321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>707011</v>
+        <v>706831</v>
       </c>
       <c r="R210" t="n">
-        <v>6670734</v>
+        <v>6670326</v>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23685,48 +23685,48 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129110564</v>
+        <v>129108444</v>
       </c>
       <c r="B211" t="n">
-        <v>91610</v>
+        <v>91088</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5321</v>
+        <v>5747</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>706831</v>
+        <v>706954</v>
       </c>
       <c r="R211" t="n">
-        <v>6670326</v>
+        <v>6670717</v>
       </c>
       <c r="S211" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23782,48 +23782,48 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129112905</v>
+        <v>129108141</v>
       </c>
       <c r="B212" t="n">
-        <v>80149</v>
+        <v>92871</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6458</v>
+        <v>5964</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>707166</v>
+        <v>707011</v>
       </c>
       <c r="R212" t="n">
-        <v>6670369</v>
+        <v>6670734</v>
       </c>
       <c r="S212" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23879,32 +23879,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129109887</v>
+        <v>129110527</v>
       </c>
       <c r="B213" t="n">
-        <v>88759</v>
+        <v>4995</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>805</v>
+        <v>100517</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Åttafläckig praktbagge</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Buprestis octoguttata</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23914,10 +23914,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>706822</v>
+        <v>706802</v>
       </c>
       <c r="R213" t="n">
-        <v>6670378</v>
+        <v>6670363</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23976,10 +23976,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129114035</v>
+        <v>129111662</v>
       </c>
       <c r="B214" t="n">
-        <v>86806</v>
+        <v>92847</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23987,34 +23987,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>707165</v>
+        <v>707011</v>
       </c>
       <c r="R214" t="n">
-        <v>6670655</v>
+        <v>6670220</v>
       </c>
       <c r="S214" t="n">
         <v>15</v>
@@ -24073,10 +24073,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129110955</v>
+        <v>129108289</v>
       </c>
       <c r="B215" t="n">
-        <v>86806</v>
+        <v>43982</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24084,34 +24084,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>3762</v>
+        <v>101735</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>706983</v>
+        <v>706961</v>
       </c>
       <c r="R215" t="n">
-        <v>6670276</v>
+        <v>6670741</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24170,48 +24170,48 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129113073</v>
+        <v>129114035</v>
       </c>
       <c r="B216" t="n">
-        <v>80149</v>
+        <v>86806</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6458</v>
+        <v>3762</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>707212</v>
+        <v>707165</v>
       </c>
       <c r="R216" t="n">
-        <v>6670436</v>
+        <v>6670655</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -24267,10 +24267,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129108289</v>
+        <v>129110955</v>
       </c>
       <c r="B217" t="n">
-        <v>43982</v>
+        <v>86806</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24278,34 +24278,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>101735</v>
+        <v>3762</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>706961</v>
+        <v>706983</v>
       </c>
       <c r="R217" t="n">
-        <v>6670741</v>
+        <v>6670276</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24364,45 +24364,45 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129108076</v>
+        <v>129113073</v>
       </c>
       <c r="B218" t="n">
-        <v>101823</v>
+        <v>80149</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>707017</v>
+        <v>707212</v>
       </c>
       <c r="R218" t="n">
-        <v>6670761</v>
+        <v>6670436</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24461,10 +24461,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129111662</v>
+        <v>129108076</v>
       </c>
       <c r="B219" t="n">
-        <v>92847</v>
+        <v>101823</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24472,37 +24472,37 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4366</v>
+        <v>221235</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>707011</v>
+        <v>707017</v>
       </c>
       <c r="R219" t="n">
-        <v>6670220</v>
+        <v>6670761</v>
       </c>
       <c r="S219" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24659,10 +24659,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129112862</v>
+        <v>129108567</v>
       </c>
       <c r="B221" t="n">
-        <v>96073</v>
+        <v>86806</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24670,37 +24670,37 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2818</v>
+        <v>3762</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>707141</v>
+        <v>706958</v>
       </c>
       <c r="R221" t="n">
-        <v>6670348</v>
+        <v>6670705</v>
       </c>
       <c r="S221" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24756,10 +24756,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129108567</v>
+        <v>129112862</v>
       </c>
       <c r="B222" t="n">
-        <v>86806</v>
+        <v>96073</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24767,37 +24767,37 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>3762</v>
+        <v>2818</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>706958</v>
+        <v>707141</v>
       </c>
       <c r="R222" t="n">
-        <v>6670705</v>
+        <v>6670348</v>
       </c>
       <c r="S222" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -25730,10 +25730,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129108929</v>
+        <v>129113799</v>
       </c>
       <c r="B232" t="n">
-        <v>92871</v>
+        <v>92508</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25741,37 +25741,37 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>707027</v>
+        <v>707144</v>
       </c>
       <c r="R232" t="n">
-        <v>6670701</v>
+        <v>6670568</v>
       </c>
       <c r="S232" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -25827,10 +25827,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129113799</v>
+        <v>129108929</v>
       </c>
       <c r="B233" t="n">
-        <v>92508</v>
+        <v>92871</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25838,37 +25838,37 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>707144</v>
+        <v>707027</v>
       </c>
       <c r="R233" t="n">
-        <v>6670568</v>
+        <v>6670701</v>
       </c>
       <c r="S233" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -26215,45 +26215,45 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129114064</v>
+        <v>129109794</v>
       </c>
       <c r="B237" t="n">
-        <v>92327</v>
+        <v>104198</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>232138</v>
+        <v>222412</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>707168</v>
+        <v>706790</v>
       </c>
       <c r="R237" t="n">
-        <v>6670669</v>
+        <v>6670404</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26312,45 +26312,45 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129109794</v>
+        <v>129114064</v>
       </c>
       <c r="B238" t="n">
-        <v>104198</v>
+        <v>92327</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>222412</v>
+        <v>232138</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>706790</v>
+        <v>707168</v>
       </c>
       <c r="R238" t="n">
-        <v>6670404</v>
+        <v>6670669</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -16118,32 +16118,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129112087</v>
+        <v>129110669</v>
       </c>
       <c r="B134" t="n">
-        <v>92847</v>
+        <v>80149</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -16153,10 +16153,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>707031</v>
+        <v>706880</v>
       </c>
       <c r="R134" t="n">
-        <v>6670179</v>
+        <v>6670333</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16215,48 +16215,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129108149</v>
+        <v>129112482</v>
       </c>
       <c r="B135" t="n">
-        <v>91326</v>
+        <v>80149</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3215</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>707011</v>
+        <v>707055</v>
       </c>
       <c r="R135" t="n">
-        <v>6670734</v>
+        <v>6670286</v>
       </c>
       <c r="S135" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16312,32 +16312,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129112588</v>
+        <v>129112087</v>
       </c>
       <c r="B136" t="n">
-        <v>79581</v>
+        <v>92847</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1352</v>
+        <v>4366</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16347,13 +16347,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>707101</v>
+        <v>707031</v>
       </c>
       <c r="R136" t="n">
-        <v>6670297</v>
+        <v>6670179</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16409,48 +16409,48 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129110669</v>
+        <v>129108149</v>
       </c>
       <c r="B137" t="n">
-        <v>80149</v>
+        <v>91326</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>706880</v>
+        <v>707011</v>
       </c>
       <c r="R137" t="n">
-        <v>6670333</v>
+        <v>6670734</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16506,10 +16506,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129112482</v>
+        <v>129112588</v>
       </c>
       <c r="B138" t="n">
-        <v>80149</v>
+        <v>79581</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16517,21 +16517,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>1352</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16541,13 +16541,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>707055</v>
+        <v>707101</v>
       </c>
       <c r="R138" t="n">
-        <v>6670286</v>
+        <v>6670297</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16700,48 +16700,57 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129112389</v>
+        <v>129108341</v>
       </c>
       <c r="B140" t="n">
-        <v>102974</v>
+        <v>98633</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>223246</v>
+        <v>504</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>707049</v>
+        <v>706937</v>
       </c>
       <c r="R140" t="n">
-        <v>6670267</v>
+        <v>6670745</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16797,57 +16806,48 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129108341</v>
+        <v>129110670</v>
       </c>
       <c r="B141" t="n">
-        <v>98633</v>
+        <v>91995</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>504</v>
+        <v>1619</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Apelticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Aurantiporus fissilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>706937</v>
+        <v>706880</v>
       </c>
       <c r="R141" t="n">
-        <v>6670745</v>
+        <v>6670333</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16899,49 +16899,53 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY141" t="inlineStr"/>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129110670</v>
+        <v>129114059</v>
       </c>
       <c r="B142" t="n">
-        <v>91995</v>
+        <v>80149</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1619</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Apelticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Aurantiporus fissilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>706880</v>
+        <v>707168</v>
       </c>
       <c r="R142" t="n">
-        <v>6670333</v>
+        <v>6670669</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16996,18 +17000,14 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY142" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129114059</v>
+        <v>129113907</v>
       </c>
       <c r="B143" t="n">
-        <v>80149</v>
+        <v>87005</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17015,21 +17015,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>6003295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -17039,10 +17039,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>707168</v>
+        <v>707129</v>
       </c>
       <c r="R143" t="n">
-        <v>6670669</v>
+        <v>6670627</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17101,45 +17101,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129113907</v>
+        <v>129112389</v>
       </c>
       <c r="B144" t="n">
-        <v>87005</v>
+        <v>102974</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6003295</v>
+        <v>223246</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>707129</v>
+        <v>707049</v>
       </c>
       <c r="R144" t="n">
-        <v>6670627</v>
+        <v>6670267</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17198,10 +17198,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129112698</v>
+        <v>129109792</v>
       </c>
       <c r="B145" t="n">
-        <v>86988</v>
+        <v>80149</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17209,21 +17209,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>460</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17233,10 +17233,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>707129</v>
+        <v>706790</v>
       </c>
       <c r="R145" t="n">
-        <v>6670306</v>
+        <v>6670404</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17295,10 +17295,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129108937</v>
+        <v>129108051</v>
       </c>
       <c r="B146" t="n">
-        <v>91326</v>
+        <v>98705</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17306,21 +17306,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17330,10 +17330,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>707027</v>
+        <v>707017</v>
       </c>
       <c r="R146" t="n">
-        <v>6670701</v>
+        <v>6670761</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17392,10 +17392,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129109792</v>
+        <v>129112698</v>
       </c>
       <c r="B147" t="n">
-        <v>80149</v>
+        <v>86988</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17403,21 +17403,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>460</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Cordier) Gillet</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17427,10 +17427,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>706790</v>
+        <v>707129</v>
       </c>
       <c r="R147" t="n">
-        <v>6670404</v>
+        <v>6670306</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17489,10 +17489,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129108051</v>
+        <v>129108937</v>
       </c>
       <c r="B148" t="n">
-        <v>98705</v>
+        <v>91326</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17500,21 +17500,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17524,10 +17524,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>707017</v>
+        <v>707027</v>
       </c>
       <c r="R148" t="n">
-        <v>6670761</v>
+        <v>6670701</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17586,32 +17586,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129112646</v>
+        <v>129111060</v>
       </c>
       <c r="B149" t="n">
-        <v>99946</v>
+        <v>92043</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>174</v>
+        <v>5469</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Kärrvaxskinn</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Phlebiodontia subochracea</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17621,13 +17621,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>707129</v>
+        <v>706998</v>
       </c>
       <c r="R149" t="n">
-        <v>6670306</v>
+        <v>6670322</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17683,48 +17683,48 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129112890</v>
+        <v>129112646</v>
       </c>
       <c r="B150" t="n">
-        <v>91113</v>
+        <v>99946</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>937</v>
+        <v>174</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>707141</v>
+        <v>707129</v>
       </c>
       <c r="R150" t="n">
-        <v>6670348</v>
+        <v>6670306</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17780,48 +17780,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129114030</v>
+        <v>129112890</v>
       </c>
       <c r="B151" t="n">
-        <v>91326</v>
+        <v>91113</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3215</v>
+        <v>937</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>707151</v>
+        <v>707141</v>
       </c>
       <c r="R151" t="n">
-        <v>6670622</v>
+        <v>6670348</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17877,10 +17877,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129112791</v>
+        <v>129112466</v>
       </c>
       <c r="B152" t="n">
-        <v>91610</v>
+        <v>91537</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17888,37 +17888,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5321</v>
+        <v>4660</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>707141</v>
+        <v>707055</v>
       </c>
       <c r="R152" t="n">
-        <v>6670348</v>
+        <v>6670286</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17974,48 +17974,48 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129111060</v>
+        <v>129112791</v>
       </c>
       <c r="B153" t="n">
-        <v>92043</v>
+        <v>91610</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5469</v>
+        <v>5321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kärrvaxskinn</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phlebiodontia subochracea</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>706998</v>
+        <v>707141</v>
       </c>
       <c r="R153" t="n">
-        <v>6670322</v>
+        <v>6670348</v>
       </c>
       <c r="S153" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18071,10 +18071,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129112466</v>
+        <v>129114030</v>
       </c>
       <c r="B154" t="n">
-        <v>91537</v>
+        <v>91326</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18082,34 +18082,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4660</v>
+        <v>3215</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>707055</v>
+        <v>707151</v>
       </c>
       <c r="R154" t="n">
-        <v>6670286</v>
+        <v>6670622</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18168,10 +18168,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129110999</v>
+        <v>129113068</v>
       </c>
       <c r="B155" t="n">
-        <v>92508</v>
+        <v>110858</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18179,37 +18179,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4769</v>
+        <v>219711</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>707002</v>
+        <v>707202</v>
       </c>
       <c r="R155" t="n">
-        <v>6670297</v>
+        <v>6670431</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18265,45 +18265,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129112925</v>
+        <v>129110999</v>
       </c>
       <c r="B156" t="n">
-        <v>91113</v>
+        <v>92508</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>937</v>
+        <v>4769</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>707185</v>
+        <v>707002</v>
       </c>
       <c r="R156" t="n">
-        <v>6670371</v>
+        <v>6670297</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18362,32 +18362,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129113229</v>
+        <v>129112925</v>
       </c>
       <c r="B157" t="n">
-        <v>92871</v>
+        <v>91113</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5964</v>
+        <v>937</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18397,13 +18397,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>707145</v>
+        <v>707185</v>
       </c>
       <c r="R157" t="n">
-        <v>6670534</v>
+        <v>6670371</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18459,32 +18459,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129113101</v>
+        <v>129113229</v>
       </c>
       <c r="B158" t="n">
-        <v>80149</v>
+        <v>92871</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>5964</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>707194</v>
+        <v>707145</v>
       </c>
       <c r="R158" t="n">
-        <v>6670479</v>
+        <v>6670534</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18556,32 +18556,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129113068</v>
+        <v>129113101</v>
       </c>
       <c r="B159" t="n">
-        <v>110858</v>
+        <v>80149</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>219711</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18591,13 +18591,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>707202</v>
+        <v>707194</v>
       </c>
       <c r="R159" t="n">
-        <v>6670431</v>
+        <v>6670479</v>
       </c>
       <c r="S159" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18653,56 +18653,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129111656</v>
+        <v>129108270</v>
       </c>
       <c r="B160" t="n">
-        <v>90347</v>
+        <v>92847</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6003116</v>
+        <v>4366</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Davidmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tricholoma ilkkae</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>707000</v>
+        <v>706961</v>
       </c>
       <c r="R160" t="n">
-        <v>6670196</v>
+        <v>6670741</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18743,24 +18732,8 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
-        </is>
-      </c>
-      <c r="AL160" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
@@ -18773,18 +18746,14 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY160" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129109134</v>
+        <v>129113903</v>
       </c>
       <c r="B161" t="n">
-        <v>98633</v>
+        <v>92271</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18792,43 +18761,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>504</v>
+        <v>3298</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>706945</v>
+        <v>707129</v>
       </c>
       <c r="R161" t="n">
-        <v>6670657</v>
+        <v>6670627</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18887,45 +18847,56 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129108270</v>
+        <v>129111656</v>
       </c>
       <c r="B162" t="n">
-        <v>92847</v>
+        <v>90347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4366</v>
+        <v>6003116</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Davidmusseron</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma ilkkae</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>Mort.Chr. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>706961</v>
+        <v>707000</v>
       </c>
       <c r="R162" t="n">
-        <v>6670741</v>
+        <v>6670196</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18966,8 +18937,24 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
@@ -18980,14 +18967,18 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY162" t="inlineStr"/>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129113903</v>
+        <v>129109134</v>
       </c>
       <c r="B163" t="n">
-        <v>92271</v>
+        <v>98633</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18995,34 +18986,43 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3298</v>
+        <v>504</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>707129</v>
+        <v>706945</v>
       </c>
       <c r="R163" t="n">
-        <v>6670627</v>
+        <v>6670657</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19178,10 +19178,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129112386</v>
+        <v>129108054</v>
       </c>
       <c r="B165" t="n">
-        <v>99946</v>
+        <v>98633</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19189,46 +19189,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>174</v>
+        <v>504</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>707049</v>
+        <v>707017</v>
       </c>
       <c r="R165" t="n">
-        <v>6670267</v>
+        <v>6670761</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19263,18 +19251,12 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Stort bestånd.</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -19293,45 +19275,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129108500</v>
+        <v>129112397</v>
       </c>
       <c r="B166" t="n">
-        <v>88761</v>
+        <v>86988</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4394</v>
+        <v>460</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(Cordier) Gillet</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>706954</v>
+        <v>707055</v>
       </c>
       <c r="R166" t="n">
-        <v>6670717</v>
+        <v>6670286</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19390,10 +19372,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129114112</v>
+        <v>129112386</v>
       </c>
       <c r="B167" t="n">
-        <v>86968</v>
+        <v>99946</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19401,37 +19383,49 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3674</v>
+        <v>174</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>707154</v>
+        <v>707049</v>
       </c>
       <c r="R167" t="n">
-        <v>6670701</v>
+        <v>6670267</v>
       </c>
       <c r="S167" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19463,12 +19457,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Stort bestånd.</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -19487,45 +19487,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129112545</v>
+        <v>129108500</v>
       </c>
       <c r="B168" t="n">
-        <v>79663</v>
+        <v>88761</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>4394</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>707088</v>
+        <v>706954</v>
       </c>
       <c r="R168" t="n">
-        <v>6670309</v>
+        <v>6670717</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19584,10 +19584,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129107991</v>
+        <v>129114112</v>
       </c>
       <c r="B169" t="n">
-        <v>8439</v>
+        <v>86968</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19595,37 +19595,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>106554</v>
+        <v>3674</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>706990</v>
+        <v>707154</v>
       </c>
       <c r="R169" t="n">
-        <v>6670767</v>
+        <v>6670701</v>
       </c>
       <c r="S169" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19681,32 +19681,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129109788</v>
+        <v>129112545</v>
       </c>
       <c r="B170" t="n">
-        <v>110858</v>
+        <v>79663</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>219711</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19716,10 +19716,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>706790</v>
+        <v>707088</v>
       </c>
       <c r="R170" t="n">
-        <v>6670404</v>
+        <v>6670309</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19875,48 +19875,48 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129110603</v>
+        <v>129113794</v>
       </c>
       <c r="B172" t="n">
-        <v>102974</v>
+        <v>87005</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>223246</v>
+        <v>6003295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>706848</v>
+        <v>707144</v>
       </c>
       <c r="R172" t="n">
-        <v>6670352</v>
+        <v>6670568</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19972,48 +19972,48 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129113794</v>
+        <v>129110603</v>
       </c>
       <c r="B173" t="n">
-        <v>87005</v>
+        <v>102974</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6003295</v>
+        <v>223246</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>707144</v>
+        <v>706848</v>
       </c>
       <c r="R173" t="n">
-        <v>6670568</v>
+        <v>6670352</v>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -20069,10 +20069,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129109137</v>
+        <v>129107991</v>
       </c>
       <c r="B174" t="n">
-        <v>101823</v>
+        <v>8439</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20080,37 +20080,37 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>221235</v>
+        <v>106554</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>706945</v>
+        <v>706990</v>
       </c>
       <c r="R174" t="n">
-        <v>6670657</v>
+        <v>6670767</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20166,32 +20166,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129112397</v>
+        <v>129109788</v>
       </c>
       <c r="B175" t="n">
-        <v>86988</v>
+        <v>110858</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>460</v>
+        <v>219711</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20201,10 +20201,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>707055</v>
+        <v>706790</v>
       </c>
       <c r="R175" t="n">
-        <v>6670286</v>
+        <v>6670404</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20263,10 +20263,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129108054</v>
+        <v>129109137</v>
       </c>
       <c r="B176" t="n">
-        <v>98633</v>
+        <v>101823</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20274,34 +20274,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>504</v>
+        <v>221235</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>707017</v>
+        <v>706945</v>
       </c>
       <c r="R176" t="n">
-        <v>6670761</v>
+        <v>6670657</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20360,32 +20360,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129108275</v>
+        <v>129108056</v>
       </c>
       <c r="B177" t="n">
-        <v>87027</v>
+        <v>98749</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20395,10 +20395,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>706961</v>
+        <v>707017</v>
       </c>
       <c r="R177" t="n">
-        <v>6670741</v>
+        <v>6670761</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20457,32 +20457,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129108056</v>
+        <v>129108275</v>
       </c>
       <c r="B178" t="n">
-        <v>98749</v>
+        <v>87027</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20492,10 +20492,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>707017</v>
+        <v>706961</v>
       </c>
       <c r="R178" t="n">
-        <v>6670761</v>
+        <v>6670741</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20651,27 +20651,27 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129110679</v>
+        <v>129108563</v>
       </c>
       <c r="B180" t="n">
-        <v>106355</v>
+        <v>98633</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220785</v>
+        <v>504</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -20682,17 +20682,17 @@
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>706880</v>
+        <v>706958</v>
       </c>
       <c r="R180" t="n">
-        <v>6670333</v>
+        <v>6670705</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20748,27 +20748,27 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129108563</v>
+        <v>129110679</v>
       </c>
       <c r="B181" t="n">
-        <v>98633</v>
+        <v>106355</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>504</v>
+        <v>220785</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -20779,17 +20779,17 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>706958</v>
+        <v>706880</v>
       </c>
       <c r="R181" t="n">
-        <v>6670705</v>
+        <v>6670333</v>
       </c>
       <c r="S181" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129111077</v>
+        <v>129110811</v>
       </c>
       <c r="B185" t="n">
         <v>80149</v>
@@ -21171,13 +21171,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>706998</v>
+        <v>706912</v>
       </c>
       <c r="R185" t="n">
-        <v>6670322</v>
+        <v>6670280</v>
       </c>
       <c r="S185" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129110811</v>
+        <v>129111077</v>
       </c>
       <c r="B186" t="n">
         <v>80149</v>
@@ -21268,13 +21268,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>706912</v>
+        <v>706998</v>
       </c>
       <c r="R186" t="n">
-        <v>6670280</v>
+        <v>6670322</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -22027,45 +22027,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129108939</v>
+        <v>129109340</v>
       </c>
       <c r="B194" t="n">
-        <v>110858</v>
+        <v>86897</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>219711</v>
+        <v>445</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>707027</v>
+        <v>706839</v>
       </c>
       <c r="R194" t="n">
-        <v>6670701</v>
+        <v>6670598</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22120,52 +22120,56 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY194" t="inlineStr"/>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129112425</v>
+        <v>129112836</v>
       </c>
       <c r="B195" t="n">
-        <v>103252</v>
+        <v>91777</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>222002</v>
+        <v>1106</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>707055</v>
+        <v>707141</v>
       </c>
       <c r="R195" t="n">
-        <v>6670286</v>
+        <v>6670348</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22221,10 +22225,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129109238</v>
+        <v>129109288</v>
       </c>
       <c r="B196" t="n">
-        <v>104198</v>
+        <v>91062</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22232,21 +22236,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>222412</v>
+        <v>5741</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22318,32 +22322,32 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129109340</v>
+        <v>129109238</v>
       </c>
       <c r="B197" t="n">
-        <v>86897</v>
+        <v>104198</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>445</v>
+        <v>222412</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -22353,10 +22357,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>706839</v>
+        <v>706876</v>
       </c>
       <c r="R197" t="n">
-        <v>6670598</v>
+        <v>6670589</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22411,56 +22415,52 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY197" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129112836</v>
+        <v>129112425</v>
       </c>
       <c r="B198" t="n">
-        <v>91777</v>
+        <v>103252</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1106</v>
+        <v>222002</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>707141</v>
+        <v>707055</v>
       </c>
       <c r="R198" t="n">
-        <v>6670348</v>
+        <v>6670286</v>
       </c>
       <c r="S198" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -22516,10 +22516,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129109288</v>
+        <v>129108939</v>
       </c>
       <c r="B199" t="n">
-        <v>91062</v>
+        <v>110858</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22527,34 +22527,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5741</v>
+        <v>219711</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>706876</v>
+        <v>707027</v>
       </c>
       <c r="R199" t="n">
-        <v>6670589</v>
+        <v>6670701</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22613,45 +22613,54 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129112405</v>
+        <v>129108856</v>
       </c>
       <c r="B200" t="n">
-        <v>91113</v>
+        <v>98633</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>937</v>
+        <v>504</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>707055</v>
+        <v>707027</v>
       </c>
       <c r="R200" t="n">
-        <v>6670286</v>
+        <v>6670701</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22710,10 +22719,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129108856</v>
+        <v>129112733</v>
       </c>
       <c r="B201" t="n">
-        <v>98633</v>
+        <v>90317</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22721,43 +22730,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>504</v>
+        <v>1595</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>707027</v>
+        <v>707129</v>
       </c>
       <c r="R201" t="n">
-        <v>6670701</v>
+        <v>6670306</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22816,10 +22816,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129112733</v>
+        <v>129112410</v>
       </c>
       <c r="B202" t="n">
-        <v>90317</v>
+        <v>89562</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22827,21 +22827,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1595</v>
+        <v>5581</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Gulfotsskölding</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Pluteus romellii</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>(Britzelm.) Sacc.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22851,10 +22851,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>707129</v>
+        <v>707055</v>
       </c>
       <c r="R202" t="n">
-        <v>6670306</v>
+        <v>6670286</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22913,10 +22913,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129112410</v>
+        <v>129111205</v>
       </c>
       <c r="B203" t="n">
-        <v>89562</v>
+        <v>92849</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22924,23 +22924,19 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5581</v>
+        <v>6047725</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Gulfotsskölding</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Pluteus romellii</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>(Britzelm.) Sacc.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
@@ -22948,10 +22944,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>707055</v>
+        <v>707000</v>
       </c>
       <c r="R203" t="n">
-        <v>6670286</v>
+        <v>6670196</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23006,7 +23002,11 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY203" t="inlineStr"/>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23107,30 +23107,34 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129111205</v>
+        <v>129112405</v>
       </c>
       <c r="B205" t="n">
-        <v>92849</v>
+        <v>91113</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6047725</v>
+        <v>937</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr"/>
+          <t>Lentaria epichnoa</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
@@ -23138,10 +23142,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>707000</v>
+        <v>707055</v>
       </c>
       <c r="R205" t="n">
-        <v>6670196</v>
+        <v>6670286</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23196,11 +23200,7 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY205" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23301,41 +23301,45 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129108973</v>
+        <v>129109887</v>
       </c>
       <c r="B207" t="n">
-        <v>87071</v>
+        <v>88759</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>3624</v>
+        <v>805</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr"/>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>707027</v>
+        <v>706822</v>
       </c>
       <c r="R207" t="n">
-        <v>6670701</v>
+        <v>6670378</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23394,48 +23398,48 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129112905</v>
+        <v>129110564</v>
       </c>
       <c r="B208" t="n">
-        <v>80149</v>
+        <v>91610</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6458</v>
+        <v>5321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>707166</v>
+        <v>706831</v>
       </c>
       <c r="R208" t="n">
-        <v>6670369</v>
+        <v>6670326</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23491,45 +23495,41 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129109887</v>
+        <v>129108973</v>
       </c>
       <c r="B209" t="n">
-        <v>88759</v>
+        <v>87071</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>805</v>
+        <v>3624</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>706822</v>
+        <v>707027</v>
       </c>
       <c r="R209" t="n">
-        <v>6670378</v>
+        <v>6670701</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23588,48 +23588,48 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129110564</v>
+        <v>129108444</v>
       </c>
       <c r="B210" t="n">
-        <v>91610</v>
+        <v>91088</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5321</v>
+        <v>5747</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>706831</v>
+        <v>706954</v>
       </c>
       <c r="R210" t="n">
-        <v>6670326</v>
+        <v>6670717</v>
       </c>
       <c r="S210" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23685,32 +23685,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129108444</v>
+        <v>129108141</v>
       </c>
       <c r="B211" t="n">
-        <v>91088</v>
+        <v>92871</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23720,13 +23720,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>706954</v>
+        <v>707011</v>
       </c>
       <c r="R211" t="n">
-        <v>6670717</v>
+        <v>6670734</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23782,48 +23782,48 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129108141</v>
+        <v>129112905</v>
       </c>
       <c r="B212" t="n">
-        <v>92871</v>
+        <v>80149</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5964</v>
+        <v>6458</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>707011</v>
+        <v>707166</v>
       </c>
       <c r="R212" t="n">
-        <v>6670734</v>
+        <v>6670369</v>
       </c>
       <c r="S212" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -24073,10 +24073,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129108289</v>
+        <v>129114035</v>
       </c>
       <c r="B215" t="n">
-        <v>43982</v>
+        <v>86806</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24084,37 +24084,37 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>101735</v>
+        <v>3762</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>706961</v>
+        <v>707165</v>
       </c>
       <c r="R215" t="n">
-        <v>6670741</v>
+        <v>6670655</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129114035</v>
+        <v>129110955</v>
       </c>
       <c r="B216" t="n">
         <v>86806</v>
@@ -24201,17 +24201,17 @@
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>707165</v>
+        <v>706983</v>
       </c>
       <c r="R216" t="n">
-        <v>6670655</v>
+        <v>6670276</v>
       </c>
       <c r="S216" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -24267,45 +24267,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129110955</v>
+        <v>129113073</v>
       </c>
       <c r="B217" t="n">
-        <v>86806</v>
+        <v>80149</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>3762</v>
+        <v>6458</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>706983</v>
+        <v>707212</v>
       </c>
       <c r="R217" t="n">
-        <v>6670276</v>
+        <v>6670436</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24364,45 +24364,45 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129113073</v>
+        <v>129108289</v>
       </c>
       <c r="B218" t="n">
-        <v>80149</v>
+        <v>43982</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6458</v>
+        <v>101735</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>707212</v>
+        <v>706961</v>
       </c>
       <c r="R218" t="n">
-        <v>6670436</v>
+        <v>6670741</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24558,32 +24558,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129111122</v>
+        <v>129112111</v>
       </c>
       <c r="B220" t="n">
-        <v>91788</v>
+        <v>92871</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1100</v>
+        <v>5964</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Rosetticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Postia floriformis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Quél.) Jülich</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24593,13 +24593,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>707049</v>
+        <v>707012</v>
       </c>
       <c r="R220" t="n">
-        <v>6670267</v>
+        <v>6670187</v>
       </c>
       <c r="S220" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -24651,56 +24651,52 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY220" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129108567</v>
+        <v>129111122</v>
       </c>
       <c r="B221" t="n">
-        <v>86806</v>
+        <v>91788</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>3762</v>
+        <v>1100</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Quél.) Jülich</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>706958</v>
+        <v>707049</v>
       </c>
       <c r="R221" t="n">
-        <v>6670705</v>
+        <v>6670267</v>
       </c>
       <c r="S221" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24752,14 +24748,18 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY221" t="inlineStr"/>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129112862</v>
+        <v>129108567</v>
       </c>
       <c r="B222" t="n">
-        <v>96073</v>
+        <v>86806</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24767,37 +24767,37 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>2818</v>
+        <v>3762</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>707141</v>
+        <v>706958</v>
       </c>
       <c r="R222" t="n">
-        <v>6670348</v>
+        <v>6670705</v>
       </c>
       <c r="S222" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24853,10 +24853,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129112111</v>
+        <v>129112862</v>
       </c>
       <c r="B223" t="n">
-        <v>92871</v>
+        <v>96073</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24864,37 +24864,37 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5964</v>
+        <v>2818</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>707012</v>
+        <v>707141</v>
       </c>
       <c r="R223" t="n">
-        <v>6670187</v>
+        <v>6670348</v>
       </c>
       <c r="S223" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -25042,45 +25042,45 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129112901</v>
+        <v>129109815</v>
       </c>
       <c r="B225" t="n">
-        <v>91113</v>
+        <v>101823</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>937</v>
+        <v>221235</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>707166</v>
+        <v>706790</v>
       </c>
       <c r="R225" t="n">
-        <v>6670369</v>
+        <v>6670404</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25139,10 +25139,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129108653</v>
+        <v>129108561</v>
       </c>
       <c r="B226" t="n">
-        <v>98633</v>
+        <v>101823</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25150,43 +25150,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>504</v>
+        <v>221235</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>706984</v>
+        <v>706954</v>
       </c>
       <c r="R226" t="n">
-        <v>6670689</v>
+        <v>6670717</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25245,48 +25236,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129108591</v>
+        <v>129112901</v>
       </c>
       <c r="B227" t="n">
-        <v>92508</v>
+        <v>91113</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4769</v>
+        <v>937</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>706958</v>
+        <v>707166</v>
       </c>
       <c r="R227" t="n">
-        <v>6670705</v>
+        <v>6670369</v>
       </c>
       <c r="S227" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25342,7 +25333,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129108343</v>
+        <v>129108591</v>
       </c>
       <c r="B228" t="n">
         <v>92508</v>
@@ -25377,10 +25368,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>706937</v>
+        <v>706958</v>
       </c>
       <c r="R228" t="n">
-        <v>6670745</v>
+        <v>6670705</v>
       </c>
       <c r="S228" t="n">
         <v>15</v>
@@ -25439,10 +25430,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129109815</v>
+        <v>129108343</v>
       </c>
       <c r="B229" t="n">
-        <v>101823</v>
+        <v>92508</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25450,37 +25441,37 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>706790</v>
+        <v>706937</v>
       </c>
       <c r="R229" t="n">
-        <v>6670404</v>
+        <v>6670745</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -25536,10 +25527,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129108561</v>
+        <v>129108653</v>
       </c>
       <c r="B230" t="n">
-        <v>101823</v>
+        <v>98633</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25547,34 +25538,43 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>221235</v>
+        <v>504</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>706954</v>
+        <v>706984</v>
       </c>
       <c r="R230" t="n">
-        <v>6670717</v>
+        <v>6670689</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25827,45 +25827,45 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129108929</v>
+        <v>129109932</v>
       </c>
       <c r="B233" t="n">
-        <v>92871</v>
+        <v>5493</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5964</v>
+        <v>101410</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>707027</v>
+        <v>706801</v>
       </c>
       <c r="R233" t="n">
-        <v>6670701</v>
+        <v>6670352</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25924,45 +25924,45 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129109932</v>
+        <v>129108929</v>
       </c>
       <c r="B234" t="n">
-        <v>5493</v>
+        <v>92871</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>101410</v>
+        <v>5964</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>706801</v>
+        <v>707027</v>
       </c>
       <c r="R234" t="n">
-        <v>6670352</v>
+        <v>6670701</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26118,45 +26118,45 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129108620</v>
+        <v>129114064</v>
       </c>
       <c r="B236" t="n">
-        <v>98749</v>
+        <v>92327</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>219862</v>
+        <v>232138</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>706971</v>
+        <v>707168</v>
       </c>
       <c r="R236" t="n">
-        <v>6670688</v>
+        <v>6670669</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26215,10 +26215,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129109794</v>
+        <v>129108620</v>
       </c>
       <c r="B237" t="n">
-        <v>104198</v>
+        <v>98749</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26226,34 +26226,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>706790</v>
+        <v>706971</v>
       </c>
       <c r="R237" t="n">
-        <v>6670404</v>
+        <v>6670688</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26312,45 +26312,45 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129114064</v>
+        <v>129109794</v>
       </c>
       <c r="B238" t="n">
-        <v>92327</v>
+        <v>104198</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>232138</v>
+        <v>222412</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>707168</v>
+        <v>706790</v>
       </c>
       <c r="R238" t="n">
-        <v>6670669</v>
+        <v>6670404</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -16118,48 +16118,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129110669</v>
+        <v>129108149</v>
       </c>
       <c r="B134" t="n">
-        <v>80149</v>
+        <v>91326</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>706880</v>
+        <v>707011</v>
       </c>
       <c r="R134" t="n">
-        <v>6670333</v>
+        <v>6670734</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16215,10 +16215,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129112482</v>
+        <v>129112588</v>
       </c>
       <c r="B135" t="n">
-        <v>80149</v>
+        <v>79581</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16226,21 +16226,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>1352</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>707055</v>
+        <v>707101</v>
       </c>
       <c r="R135" t="n">
-        <v>6670286</v>
+        <v>6670297</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16312,32 +16312,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129112087</v>
+        <v>129110669</v>
       </c>
       <c r="B136" t="n">
-        <v>92847</v>
+        <v>80149</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16347,10 +16347,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>707031</v>
+        <v>706880</v>
       </c>
       <c r="R136" t="n">
-        <v>6670179</v>
+        <v>6670333</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16409,48 +16409,48 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129108149</v>
+        <v>129112482</v>
       </c>
       <c r="B137" t="n">
-        <v>91326</v>
+        <v>80149</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3215</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>707011</v>
+        <v>707055</v>
       </c>
       <c r="R137" t="n">
-        <v>6670734</v>
+        <v>6670286</v>
       </c>
       <c r="S137" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16506,48 +16506,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129112588</v>
+        <v>129112796</v>
       </c>
       <c r="B138" t="n">
-        <v>79581</v>
+        <v>102974</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1352</v>
+        <v>223246</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>707101</v>
+        <v>707141</v>
       </c>
       <c r="R138" t="n">
-        <v>6670297</v>
+        <v>6670348</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16603,48 +16603,48 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129112796</v>
+        <v>129112087</v>
       </c>
       <c r="B139" t="n">
-        <v>102974</v>
+        <v>92847</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>223246</v>
+        <v>4366</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>707141</v>
+        <v>707031</v>
       </c>
       <c r="R139" t="n">
-        <v>6670348</v>
+        <v>6670179</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -17004,45 +17004,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129113907</v>
+        <v>129112389</v>
       </c>
       <c r="B143" t="n">
-        <v>87005</v>
+        <v>102974</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6003295</v>
+        <v>223246</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>707129</v>
+        <v>707049</v>
       </c>
       <c r="R143" t="n">
-        <v>6670627</v>
+        <v>6670267</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17101,45 +17101,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129112389</v>
+        <v>129113907</v>
       </c>
       <c r="B144" t="n">
-        <v>102974</v>
+        <v>87005</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>223246</v>
+        <v>6003295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>707049</v>
+        <v>707129</v>
       </c>
       <c r="R144" t="n">
-        <v>6670267</v>
+        <v>6670627</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17198,10 +17198,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129109792</v>
+        <v>129112698</v>
       </c>
       <c r="B145" t="n">
-        <v>80149</v>
+        <v>86988</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17209,21 +17209,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>460</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Cordier) Gillet</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17233,10 +17233,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>706790</v>
+        <v>707129</v>
       </c>
       <c r="R145" t="n">
-        <v>6670404</v>
+        <v>6670306</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17295,10 +17295,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129108051</v>
+        <v>129108937</v>
       </c>
       <c r="B146" t="n">
-        <v>98705</v>
+        <v>91326</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17306,21 +17306,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17330,10 +17330,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>707017</v>
+        <v>707027</v>
       </c>
       <c r="R146" t="n">
-        <v>6670761</v>
+        <v>6670701</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17392,10 +17392,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129112698</v>
+        <v>129109792</v>
       </c>
       <c r="B147" t="n">
-        <v>86988</v>
+        <v>80149</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17403,21 +17403,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>460</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17427,10 +17427,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>707129</v>
+        <v>706790</v>
       </c>
       <c r="R147" t="n">
-        <v>6670306</v>
+        <v>6670404</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17489,10 +17489,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129108937</v>
+        <v>129108051</v>
       </c>
       <c r="B148" t="n">
-        <v>91326</v>
+        <v>98705</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17500,21 +17500,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17524,10 +17524,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>707027</v>
+        <v>707017</v>
       </c>
       <c r="R148" t="n">
-        <v>6670701</v>
+        <v>6670761</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17586,10 +17586,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129111060</v>
+        <v>129112890</v>
       </c>
       <c r="B149" t="n">
-        <v>92043</v>
+        <v>91113</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17597,37 +17597,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5469</v>
+        <v>937</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kärrvaxskinn</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phlebiodontia subochracea</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>706998</v>
+        <v>707141</v>
       </c>
       <c r="R149" t="n">
-        <v>6670322</v>
+        <v>6670348</v>
       </c>
       <c r="S149" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17683,10 +17683,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129112646</v>
+        <v>129112466</v>
       </c>
       <c r="B150" t="n">
-        <v>99946</v>
+        <v>91537</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17694,21 +17694,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>174</v>
+        <v>4660</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17718,10 +17718,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>707129</v>
+        <v>707055</v>
       </c>
       <c r="R150" t="n">
-        <v>6670306</v>
+        <v>6670286</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17780,32 +17780,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129112890</v>
+        <v>129112791</v>
       </c>
       <c r="B151" t="n">
-        <v>91113</v>
+        <v>91610</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>937</v>
+        <v>5321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17877,32 +17877,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129112466</v>
+        <v>129111060</v>
       </c>
       <c r="B152" t="n">
-        <v>91537</v>
+        <v>92043</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4660</v>
+        <v>5469</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kärrvaxskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phlebiodontia subochracea</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17912,13 +17912,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>707055</v>
+        <v>706998</v>
       </c>
       <c r="R152" t="n">
-        <v>6670286</v>
+        <v>6670322</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17974,10 +17974,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129112791</v>
+        <v>129112646</v>
       </c>
       <c r="B153" t="n">
-        <v>91610</v>
+        <v>99946</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17985,37 +17985,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5321</v>
+        <v>174</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>707141</v>
+        <v>707129</v>
       </c>
       <c r="R153" t="n">
-        <v>6670348</v>
+        <v>6670306</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18168,10 +18168,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129113068</v>
+        <v>129110999</v>
       </c>
       <c r="B155" t="n">
-        <v>110858</v>
+        <v>92508</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18179,37 +18179,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219711</v>
+        <v>4769</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>707202</v>
+        <v>707002</v>
       </c>
       <c r="R155" t="n">
-        <v>6670431</v>
+        <v>6670297</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18265,45 +18265,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129110999</v>
+        <v>129113101</v>
       </c>
       <c r="B156" t="n">
-        <v>92508</v>
+        <v>80149</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>707002</v>
+        <v>707194</v>
       </c>
       <c r="R156" t="n">
-        <v>6670297</v>
+        <v>6670479</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18362,32 +18362,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129112925</v>
+        <v>129113068</v>
       </c>
       <c r="B157" t="n">
-        <v>91113</v>
+        <v>110858</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>937</v>
+        <v>219711</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18397,13 +18397,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>707185</v>
+        <v>707202</v>
       </c>
       <c r="R157" t="n">
-        <v>6670371</v>
+        <v>6670431</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18459,32 +18459,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129113229</v>
+        <v>129112925</v>
       </c>
       <c r="B158" t="n">
-        <v>92871</v>
+        <v>91113</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5964</v>
+        <v>937</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>707145</v>
+        <v>707185</v>
       </c>
       <c r="R158" t="n">
-        <v>6670534</v>
+        <v>6670371</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18556,32 +18556,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129113101</v>
+        <v>129113229</v>
       </c>
       <c r="B159" t="n">
-        <v>80149</v>
+        <v>92871</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>5964</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18591,13 +18591,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>707194</v>
+        <v>707145</v>
       </c>
       <c r="R159" t="n">
-        <v>6670479</v>
+        <v>6670534</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18653,10 +18653,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129108270</v>
+        <v>129109134</v>
       </c>
       <c r="B160" t="n">
-        <v>92847</v>
+        <v>98633</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18664,34 +18664,43 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4366</v>
+        <v>504</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>706961</v>
+        <v>706945</v>
       </c>
       <c r="R160" t="n">
-        <v>6670741</v>
+        <v>6670657</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18750,10 +18759,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129113903</v>
+        <v>129108270</v>
       </c>
       <c r="B161" t="n">
-        <v>92271</v>
+        <v>92847</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18761,34 +18770,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>3298</v>
+        <v>4366</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>707129</v>
+        <v>706961</v>
       </c>
       <c r="R161" t="n">
-        <v>6670627</v>
+        <v>6670741</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18847,56 +18856,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129111656</v>
+        <v>129112708</v>
       </c>
       <c r="B162" t="n">
-        <v>90347</v>
+        <v>110858</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6003116</v>
+        <v>219711</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Davidmusseron</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tricholoma ilkkae</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>707000</v>
+        <v>707129</v>
       </c>
       <c r="R162" t="n">
-        <v>6670196</v>
+        <v>6670306</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18937,24 +18935,8 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
-        </is>
-      </c>
-      <c r="AL162" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
@@ -18967,18 +18949,14 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY162" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129109134</v>
+        <v>129113903</v>
       </c>
       <c r="B163" t="n">
-        <v>98633</v>
+        <v>92271</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18986,43 +18964,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>504</v>
+        <v>3298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>706945</v>
+        <v>707129</v>
       </c>
       <c r="R163" t="n">
-        <v>6670657</v>
+        <v>6670627</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19081,45 +19050,56 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129112708</v>
+        <v>129111656</v>
       </c>
       <c r="B164" t="n">
-        <v>110858</v>
+        <v>90347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>219711</v>
+        <v>6003116</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Davidmusseron</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tricholoma ilkkae</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>Mort.Chr. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>707129</v>
+        <v>707000</v>
       </c>
       <c r="R164" t="n">
-        <v>6670306</v>
+        <v>6670196</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19160,8 +19140,24 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -19174,14 +19170,18 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY164" t="inlineStr"/>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129108054</v>
+        <v>129112386</v>
       </c>
       <c r="B165" t="n">
-        <v>98633</v>
+        <v>99946</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19189,34 +19189,46 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>504</v>
+        <v>174</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>707017</v>
+        <v>707049</v>
       </c>
       <c r="R165" t="n">
-        <v>6670761</v>
+        <v>6670267</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19251,12 +19263,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Stort bestånd.</t>
+        </is>
+      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -19275,48 +19293,48 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129112397</v>
+        <v>129114112</v>
       </c>
       <c r="B166" t="n">
-        <v>86988</v>
+        <v>86968</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>460</v>
+        <v>3674</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>707055</v>
+        <v>707154</v>
       </c>
       <c r="R166" t="n">
-        <v>6670286</v>
+        <v>6670701</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19372,10 +19390,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129112386</v>
+        <v>129108500</v>
       </c>
       <c r="B167" t="n">
-        <v>99946</v>
+        <v>88761</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19383,46 +19401,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>174</v>
+        <v>4394</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>707049</v>
+        <v>706954</v>
       </c>
       <c r="R167" t="n">
-        <v>6670267</v>
+        <v>6670717</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19457,18 +19463,12 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Stort bestånd.</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -19487,45 +19487,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129108500</v>
+        <v>129112397</v>
       </c>
       <c r="B168" t="n">
-        <v>88761</v>
+        <v>86988</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4394</v>
+        <v>460</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(Cordier) Gillet</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>706954</v>
+        <v>707055</v>
       </c>
       <c r="R168" t="n">
-        <v>6670717</v>
+        <v>6670286</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19584,10 +19584,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129114112</v>
+        <v>129108054</v>
       </c>
       <c r="B169" t="n">
-        <v>86968</v>
+        <v>98633</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19595,37 +19595,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3674</v>
+        <v>504</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>707154</v>
+        <v>707017</v>
       </c>
       <c r="R169" t="n">
-        <v>6670701</v>
+        <v>6670761</v>
       </c>
       <c r="S169" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19778,10 +19778,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129109813</v>
+        <v>129109788</v>
       </c>
       <c r="B171" t="n">
-        <v>100821</v>
+        <v>110858</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19789,16 +19789,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>222771</v>
+        <v>219711</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -19875,48 +19875,48 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129113794</v>
+        <v>129109813</v>
       </c>
       <c r="B172" t="n">
-        <v>87005</v>
+        <v>100821</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6003295</v>
+        <v>222771</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>707144</v>
+        <v>706790</v>
       </c>
       <c r="R172" t="n">
-        <v>6670568</v>
+        <v>6670404</v>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19972,45 +19972,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129110603</v>
+        <v>129109137</v>
       </c>
       <c r="B173" t="n">
-        <v>102974</v>
+        <v>101823</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>223246</v>
+        <v>221235</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>706848</v>
+        <v>706945</v>
       </c>
       <c r="R173" t="n">
-        <v>6670352</v>
+        <v>6670657</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20069,48 +20069,48 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129107991</v>
+        <v>129110603</v>
       </c>
       <c r="B174" t="n">
-        <v>8439</v>
+        <v>102974</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>106554</v>
+        <v>223246</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>706990</v>
+        <v>706848</v>
       </c>
       <c r="R174" t="n">
-        <v>6670767</v>
+        <v>6670352</v>
       </c>
       <c r="S174" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20166,48 +20166,48 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129109788</v>
+        <v>129113794</v>
       </c>
       <c r="B175" t="n">
-        <v>110858</v>
+        <v>87005</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>219711</v>
+        <v>6003295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>706790</v>
+        <v>707144</v>
       </c>
       <c r="R175" t="n">
-        <v>6670404</v>
+        <v>6670568</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -20263,10 +20263,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129109137</v>
+        <v>129107991</v>
       </c>
       <c r="B176" t="n">
-        <v>101823</v>
+        <v>8439</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20274,37 +20274,37 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>221235</v>
+        <v>106554</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>706945</v>
+        <v>706990</v>
       </c>
       <c r="R176" t="n">
-        <v>6670657</v>
+        <v>6670767</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20360,32 +20360,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129108056</v>
+        <v>129108275</v>
       </c>
       <c r="B177" t="n">
-        <v>98749</v>
+        <v>87027</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20395,10 +20395,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>707017</v>
+        <v>706961</v>
       </c>
       <c r="R177" t="n">
-        <v>6670761</v>
+        <v>6670741</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20457,48 +20457,48 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129108275</v>
+        <v>129113803</v>
       </c>
       <c r="B178" t="n">
-        <v>87027</v>
+        <v>91326</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>449</v>
+        <v>3215</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>706961</v>
+        <v>707144</v>
       </c>
       <c r="R178" t="n">
-        <v>6670741</v>
+        <v>6670568</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20554,10 +20554,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129113803</v>
+        <v>129108056</v>
       </c>
       <c r="B179" t="n">
-        <v>91326</v>
+        <v>98749</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20565,37 +20565,37 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>3215</v>
+        <v>219862</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>707144</v>
+        <v>707017</v>
       </c>
       <c r="R179" t="n">
-        <v>6670568</v>
+        <v>6670761</v>
       </c>
       <c r="S179" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20651,10 +20651,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129108563</v>
+        <v>129109796</v>
       </c>
       <c r="B180" t="n">
-        <v>98633</v>
+        <v>91564</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20662,37 +20662,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>504</v>
+        <v>1205</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>706958</v>
+        <v>706790</v>
       </c>
       <c r="R180" t="n">
-        <v>6670705</v>
+        <v>6670404</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20748,32 +20748,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129110679</v>
+        <v>129111132</v>
       </c>
       <c r="B181" t="n">
-        <v>106355</v>
+        <v>91553</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220785</v>
+        <v>1202</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20783,10 +20783,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>706880</v>
+        <v>707028</v>
       </c>
       <c r="R181" t="n">
-        <v>6670333</v>
+        <v>6670245</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20845,45 +20845,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129109796</v>
+        <v>129109438</v>
       </c>
       <c r="B182" t="n">
-        <v>91564</v>
+        <v>92873</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1205</v>
+        <v>5966</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>706790</v>
+        <v>706816</v>
       </c>
       <c r="R182" t="n">
-        <v>6670404</v>
+        <v>6670564</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20942,10 +20942,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129111132</v>
+        <v>129110811</v>
       </c>
       <c r="B183" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20953,21 +20953,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20977,10 +20977,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>707028</v>
+        <v>706912</v>
       </c>
       <c r="R183" t="n">
-        <v>6670245</v>
+        <v>6670280</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21039,10 +21039,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129109438</v>
+        <v>129111077</v>
       </c>
       <c r="B184" t="n">
-        <v>92873</v>
+        <v>80149</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21050,37 +21050,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>706816</v>
+        <v>706998</v>
       </c>
       <c r="R184" t="n">
-        <v>6670564</v>
+        <v>6670322</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21136,32 +21136,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129110811</v>
+        <v>129112011</v>
       </c>
       <c r="B185" t="n">
-        <v>80149</v>
+        <v>98749</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6458</v>
+        <v>219862</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21171,10 +21171,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>706912</v>
+        <v>707031</v>
       </c>
       <c r="R185" t="n">
-        <v>6670280</v>
+        <v>6670179</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21233,32 +21233,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129111077</v>
+        <v>129110679</v>
       </c>
       <c r="B186" t="n">
-        <v>80149</v>
+        <v>106355</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6458</v>
+        <v>220785</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21268,13 +21268,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>706998</v>
+        <v>706880</v>
       </c>
       <c r="R186" t="n">
-        <v>6670322</v>
+        <v>6670333</v>
       </c>
       <c r="S186" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21330,10 +21330,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129112011</v>
+        <v>129108563</v>
       </c>
       <c r="B187" t="n">
-        <v>98749</v>
+        <v>98633</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21341,37 +21341,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>219862</v>
+        <v>504</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>707031</v>
+        <v>706958</v>
       </c>
       <c r="R187" t="n">
-        <v>6670179</v>
+        <v>6670705</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21427,10 +21427,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129110767</v>
+        <v>129110639</v>
       </c>
       <c r="B188" t="n">
-        <v>103252</v>
+        <v>99946</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21438,34 +21438,46 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>222002</v>
+        <v>174</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>706939</v>
+        <v>706867</v>
       </c>
       <c r="R188" t="n">
-        <v>6670322</v>
+        <v>6670336</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21500,12 +21512,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Stort bestånd.</t>
+        </is>
+      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
       <c r="AE188" t="b">
         <v>0</v>
       </c>
+      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -21524,10 +21542,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129110639</v>
+        <v>129112656</v>
       </c>
       <c r="B189" t="n">
-        <v>99946</v>
+        <v>92847</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21535,46 +21553,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>174</v>
+        <v>4366</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>706867</v>
+        <v>707129</v>
       </c>
       <c r="R189" t="n">
-        <v>6670336</v>
+        <v>6670306</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21609,18 +21615,12 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Stort bestånd.</t>
-        </is>
-      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -21639,10 +21639,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129112656</v>
+        <v>129110767</v>
       </c>
       <c r="B190" t="n">
-        <v>92847</v>
+        <v>103252</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21650,21 +21650,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4366</v>
+        <v>222002</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21674,10 +21674,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>707129</v>
+        <v>706939</v>
       </c>
       <c r="R190" t="n">
-        <v>6670306</v>
+        <v>6670322</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21736,10 +21736,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129109832</v>
+        <v>129108900</v>
       </c>
       <c r="B191" t="n">
-        <v>91610</v>
+        <v>86968</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21747,34 +21747,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5321</v>
+        <v>3674</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>706793</v>
+        <v>707027</v>
       </c>
       <c r="R191" t="n">
-        <v>6670414</v>
+        <v>6670701</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21833,10 +21833,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129108900</v>
+        <v>129109832</v>
       </c>
       <c r="B192" t="n">
-        <v>86968</v>
+        <v>91610</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21844,34 +21844,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>3674</v>
+        <v>5321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>707027</v>
+        <v>706793</v>
       </c>
       <c r="R192" t="n">
-        <v>6670701</v>
+        <v>6670414</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22322,10 +22322,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129109238</v>
+        <v>129108939</v>
       </c>
       <c r="B197" t="n">
-        <v>104198</v>
+        <v>110858</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22333,16 +22333,16 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>222412</v>
+        <v>219711</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -22353,14 +22353,14 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>706876</v>
+        <v>707027</v>
       </c>
       <c r="R197" t="n">
-        <v>6670589</v>
+        <v>6670701</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22516,10 +22516,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129108939</v>
+        <v>129109238</v>
       </c>
       <c r="B199" t="n">
-        <v>110858</v>
+        <v>104198</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22527,16 +22527,16 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>219711</v>
+        <v>222412</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -22547,14 +22547,14 @@
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>707027</v>
+        <v>706876</v>
       </c>
       <c r="R199" t="n">
-        <v>6670701</v>
+        <v>6670589</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22613,10 +22613,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129108856</v>
+        <v>129112733</v>
       </c>
       <c r="B200" t="n">
-        <v>98633</v>
+        <v>90317</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22624,43 +22624,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>504</v>
+        <v>1595</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>707027</v>
+        <v>707129</v>
       </c>
       <c r="R200" t="n">
-        <v>6670701</v>
+        <v>6670306</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22719,10 +22710,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129112733</v>
+        <v>129112410</v>
       </c>
       <c r="B201" t="n">
-        <v>90317</v>
+        <v>89562</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22730,21 +22721,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1595</v>
+        <v>5581</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Gulfotsskölding</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Pluteus romellii</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>(Britzelm.) Sacc.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22754,10 +22745,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>707129</v>
+        <v>707055</v>
       </c>
       <c r="R201" t="n">
-        <v>6670306</v>
+        <v>6670286</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22816,32 +22807,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129112410</v>
+        <v>129112379</v>
       </c>
       <c r="B202" t="n">
-        <v>89562</v>
+        <v>102974</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5581</v>
+        <v>223246</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Gulfotsskölding</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Pluteus romellii</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Britzelm.) Sacc.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22851,13 +22842,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>707055</v>
+        <v>707012</v>
       </c>
       <c r="R202" t="n">
-        <v>6670286</v>
+        <v>6670187</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -23010,32 +23001,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129112379</v>
+        <v>129112405</v>
       </c>
       <c r="B204" t="n">
-        <v>102974</v>
+        <v>91113</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>223246</v>
+        <v>937</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -23045,13 +23036,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>707012</v>
+        <v>707055</v>
       </c>
       <c r="R204" t="n">
-        <v>6670187</v>
+        <v>6670286</v>
       </c>
       <c r="S204" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -23107,45 +23098,54 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129112405</v>
+        <v>129108856</v>
       </c>
       <c r="B205" t="n">
-        <v>91113</v>
+        <v>98633</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>937</v>
+        <v>504</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>707055</v>
+        <v>707027</v>
       </c>
       <c r="R205" t="n">
-        <v>6670286</v>
+        <v>6670701</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23204,10 +23204,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129112015</v>
+        <v>129109887</v>
       </c>
       <c r="B206" t="n">
-        <v>87005</v>
+        <v>88759</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23215,21 +23215,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6003295</v>
+        <v>805</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23239,10 +23239,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>707031</v>
+        <v>706822</v>
       </c>
       <c r="R206" t="n">
-        <v>6670179</v>
+        <v>6670378</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23301,32 +23301,32 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129109887</v>
+        <v>129110527</v>
       </c>
       <c r="B207" t="n">
-        <v>88759</v>
+        <v>4995</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>805</v>
+        <v>100517</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Åttafläckig praktbagge</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Buprestis octoguttata</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23336,10 +23336,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>706822</v>
+        <v>706802</v>
       </c>
       <c r="R207" t="n">
-        <v>6670378</v>
+        <v>6670363</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23398,10 +23398,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129110564</v>
+        <v>129108973</v>
       </c>
       <c r="B208" t="n">
-        <v>91610</v>
+        <v>87071</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23409,37 +23409,33 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5321</v>
+        <v>3624</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>706831</v>
+        <v>707027</v>
       </c>
       <c r="R208" t="n">
-        <v>6670326</v>
+        <v>6670701</v>
       </c>
       <c r="S208" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23495,41 +23491,45 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129108973</v>
+        <v>129112015</v>
       </c>
       <c r="B209" t="n">
-        <v>87071</v>
+        <v>87005</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>3624</v>
+        <v>6003295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>707027</v>
+        <v>707031</v>
       </c>
       <c r="R209" t="n">
-        <v>6670701</v>
+        <v>6670179</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23588,45 +23588,45 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129108444</v>
+        <v>129112905</v>
       </c>
       <c r="B210" t="n">
-        <v>91088</v>
+        <v>80149</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5747</v>
+        <v>6458</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>706954</v>
+        <v>707166</v>
       </c>
       <c r="R210" t="n">
-        <v>6670717</v>
+        <v>6670369</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23685,10 +23685,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129108141</v>
+        <v>129110564</v>
       </c>
       <c r="B211" t="n">
-        <v>92871</v>
+        <v>91610</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23696,37 +23696,37 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5964</v>
+        <v>5321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>707011</v>
+        <v>706831</v>
       </c>
       <c r="R211" t="n">
-        <v>6670734</v>
+        <v>6670326</v>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23782,45 +23782,45 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129112905</v>
+        <v>129108444</v>
       </c>
       <c r="B212" t="n">
-        <v>80149</v>
+        <v>91088</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6458</v>
+        <v>5747</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>707166</v>
+        <v>706954</v>
       </c>
       <c r="R212" t="n">
-        <v>6670369</v>
+        <v>6670717</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23879,10 +23879,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129110527</v>
+        <v>129108141</v>
       </c>
       <c r="B213" t="n">
-        <v>4995</v>
+        <v>92871</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23890,37 +23890,37 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100517</v>
+        <v>5964</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Åttafläckig praktbagge</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Buprestis octoguttata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>706802</v>
+        <v>707011</v>
       </c>
       <c r="R213" t="n">
-        <v>6670363</v>
+        <v>6670734</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23976,10 +23976,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129111662</v>
+        <v>129108076</v>
       </c>
       <c r="B214" t="n">
-        <v>92847</v>
+        <v>101823</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23987,37 +23987,37 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4366</v>
+        <v>221235</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>707011</v>
+        <v>707017</v>
       </c>
       <c r="R214" t="n">
-        <v>6670220</v>
+        <v>6670761</v>
       </c>
       <c r="S214" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24073,48 +24073,48 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129114035</v>
+        <v>129113073</v>
       </c>
       <c r="B215" t="n">
-        <v>86806</v>
+        <v>80149</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>3762</v>
+        <v>6458</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>707165</v>
+        <v>707212</v>
       </c>
       <c r="R215" t="n">
-        <v>6670655</v>
+        <v>6670436</v>
       </c>
       <c r="S215" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24170,10 +24170,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129110955</v>
+        <v>129111662</v>
       </c>
       <c r="B216" t="n">
-        <v>86806</v>
+        <v>92847</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24181,21 +24181,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24205,13 +24205,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>706983</v>
+        <v>707011</v>
       </c>
       <c r="R216" t="n">
-        <v>6670276</v>
+        <v>6670220</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -24267,48 +24267,48 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129113073</v>
+        <v>129114035</v>
       </c>
       <c r="B217" t="n">
-        <v>80149</v>
+        <v>86806</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6458</v>
+        <v>3762</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>707212</v>
+        <v>707165</v>
       </c>
       <c r="R217" t="n">
-        <v>6670436</v>
+        <v>6670655</v>
       </c>
       <c r="S217" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24364,10 +24364,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129108289</v>
+        <v>129110955</v>
       </c>
       <c r="B218" t="n">
-        <v>43982</v>
+        <v>86806</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24375,34 +24375,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>101735</v>
+        <v>3762</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>706961</v>
+        <v>706983</v>
       </c>
       <c r="R218" t="n">
-        <v>6670741</v>
+        <v>6670276</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24461,10 +24461,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129108076</v>
+        <v>129108289</v>
       </c>
       <c r="B219" t="n">
-        <v>101823</v>
+        <v>43982</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24472,21 +24472,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221235</v>
+        <v>101735</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24496,10 +24496,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>707017</v>
+        <v>706961</v>
       </c>
       <c r="R219" t="n">
-        <v>6670761</v>
+        <v>6670741</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24558,32 +24558,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129112111</v>
+        <v>129111122</v>
       </c>
       <c r="B220" t="n">
-        <v>92871</v>
+        <v>91788</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5964</v>
+        <v>1100</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Jülich</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24593,13 +24593,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>707012</v>
+        <v>707049</v>
       </c>
       <c r="R220" t="n">
-        <v>6670187</v>
+        <v>6670267</v>
       </c>
       <c r="S220" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -24651,52 +24651,56 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY220" t="inlineStr"/>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129111122</v>
+        <v>129112862</v>
       </c>
       <c r="B221" t="n">
-        <v>91788</v>
+        <v>96073</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1100</v>
+        <v>2818</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Rosetticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Postia floriformis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Quél.) Jülich</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>707049</v>
+        <v>707141</v>
       </c>
       <c r="R221" t="n">
-        <v>6670267</v>
+        <v>6670348</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24748,11 +24752,7 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY221" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24853,10 +24853,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129112862</v>
+        <v>129112111</v>
       </c>
       <c r="B223" t="n">
-        <v>96073</v>
+        <v>92871</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24864,37 +24864,37 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2818</v>
+        <v>5964</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>707141</v>
+        <v>707012</v>
       </c>
       <c r="R223" t="n">
-        <v>6670348</v>
+        <v>6670187</v>
       </c>
       <c r="S223" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -25042,45 +25042,45 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129109815</v>
+        <v>129112901</v>
       </c>
       <c r="B225" t="n">
-        <v>101823</v>
+        <v>91113</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>221235</v>
+        <v>937</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>706790</v>
+        <v>707166</v>
       </c>
       <c r="R225" t="n">
-        <v>6670404</v>
+        <v>6670369</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25139,10 +25139,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129108561</v>
+        <v>129108653</v>
       </c>
       <c r="B226" t="n">
-        <v>101823</v>
+        <v>98633</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25150,34 +25150,43 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>221235</v>
+        <v>504</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>706954</v>
+        <v>706984</v>
       </c>
       <c r="R226" t="n">
-        <v>6670717</v>
+        <v>6670689</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25236,48 +25245,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129112901</v>
+        <v>129108591</v>
       </c>
       <c r="B227" t="n">
-        <v>91113</v>
+        <v>92508</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>937</v>
+        <v>4769</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>707166</v>
+        <v>706958</v>
       </c>
       <c r="R227" t="n">
-        <v>6670369</v>
+        <v>6670705</v>
       </c>
       <c r="S227" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25333,7 +25342,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129108591</v>
+        <v>129108343</v>
       </c>
       <c r="B228" t="n">
         <v>92508</v>
@@ -25368,10 +25377,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>706958</v>
+        <v>706937</v>
       </c>
       <c r="R228" t="n">
-        <v>6670705</v>
+        <v>6670745</v>
       </c>
       <c r="S228" t="n">
         <v>15</v>
@@ -25430,10 +25439,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129108343</v>
+        <v>129108561</v>
       </c>
       <c r="B229" t="n">
-        <v>92508</v>
+        <v>101823</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25441,21 +25450,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -25465,13 +25474,13 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>706937</v>
+        <v>706954</v>
       </c>
       <c r="R229" t="n">
-        <v>6670745</v>
+        <v>6670717</v>
       </c>
       <c r="S229" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -25527,10 +25536,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129108653</v>
+        <v>129109815</v>
       </c>
       <c r="B230" t="n">
-        <v>98633</v>
+        <v>101823</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25538,43 +25547,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>504</v>
+        <v>221235</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>706984</v>
+        <v>706790</v>
       </c>
       <c r="R230" t="n">
-        <v>6670689</v>
+        <v>6670404</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25730,10 +25730,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129113799</v>
+        <v>129108929</v>
       </c>
       <c r="B232" t="n">
-        <v>92508</v>
+        <v>92871</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25741,37 +25741,37 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>707144</v>
+        <v>707027</v>
       </c>
       <c r="R232" t="n">
-        <v>6670568</v>
+        <v>6670701</v>
       </c>
       <c r="S232" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -25827,48 +25827,48 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129109932</v>
+        <v>129113799</v>
       </c>
       <c r="B233" t="n">
-        <v>5493</v>
+        <v>92508</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>101410</v>
+        <v>4769</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>706801</v>
+        <v>707144</v>
       </c>
       <c r="R233" t="n">
-        <v>6670352</v>
+        <v>6670568</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -25924,45 +25924,45 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129108929</v>
+        <v>129109932</v>
       </c>
       <c r="B234" t="n">
-        <v>92871</v>
+        <v>5493</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5964</v>
+        <v>101410</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>707027</v>
+        <v>706801</v>
       </c>
       <c r="R234" t="n">
-        <v>6670701</v>
+        <v>6670352</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26021,45 +26021,45 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129108059</v>
+        <v>129114064</v>
       </c>
       <c r="B235" t="n">
-        <v>92508</v>
+        <v>92327</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4769</v>
+        <v>232138</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>707017</v>
+        <v>707168</v>
       </c>
       <c r="R235" t="n">
-        <v>6670761</v>
+        <v>6670669</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26118,45 +26118,45 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129114064</v>
+        <v>129108620</v>
       </c>
       <c r="B236" t="n">
-        <v>92327</v>
+        <v>98749</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>232138</v>
+        <v>219862</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>707168</v>
+        <v>706971</v>
       </c>
       <c r="R236" t="n">
-        <v>6670669</v>
+        <v>6670688</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26215,10 +26215,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129108620</v>
+        <v>129109794</v>
       </c>
       <c r="B237" t="n">
-        <v>98749</v>
+        <v>104198</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26226,34 +26226,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>219862</v>
+        <v>222412</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>706971</v>
+        <v>706790</v>
       </c>
       <c r="R237" t="n">
-        <v>6670688</v>
+        <v>6670404</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26312,10 +26312,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129109794</v>
+        <v>129108059</v>
       </c>
       <c r="B238" t="n">
-        <v>104198</v>
+        <v>92508</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26323,34 +26323,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>706790</v>
+        <v>707017</v>
       </c>
       <c r="R238" t="n">
-        <v>6670404</v>
+        <v>6670761</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -16118,45 +16118,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129108149</v>
+        <v>129112796</v>
       </c>
       <c r="B134" t="n">
-        <v>91326</v>
+        <v>103003</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3215</v>
+        <v>223246</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>707011</v>
+        <v>707141</v>
       </c>
       <c r="R134" t="n">
-        <v>6670734</v>
+        <v>6670348</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -16218,7 +16218,7 @@
         <v>129112588</v>
       </c>
       <c r="B135" t="n">
-        <v>79581</v>
+        <v>79607</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16312,48 +16312,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129110669</v>
+        <v>129108149</v>
       </c>
       <c r="B136" t="n">
-        <v>80149</v>
+        <v>91354</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>706880</v>
+        <v>707011</v>
       </c>
       <c r="R136" t="n">
-        <v>6670333</v>
+        <v>6670734</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16409,32 +16409,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129112482</v>
+        <v>129112087</v>
       </c>
       <c r="B137" t="n">
-        <v>80149</v>
+        <v>92875</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16444,10 +16444,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>707055</v>
+        <v>707031</v>
       </c>
       <c r="R137" t="n">
-        <v>6670286</v>
+        <v>6670179</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16506,48 +16506,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129112796</v>
+        <v>129110669</v>
       </c>
       <c r="B138" t="n">
-        <v>102974</v>
+        <v>80175</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>223246</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>707141</v>
+        <v>706880</v>
       </c>
       <c r="R138" t="n">
-        <v>6670348</v>
+        <v>6670333</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16603,32 +16603,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129112087</v>
+        <v>129112482</v>
       </c>
       <c r="B139" t="n">
-        <v>92847</v>
+        <v>80175</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16638,10 +16638,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>707031</v>
+        <v>707055</v>
       </c>
       <c r="R139" t="n">
-        <v>6670179</v>
+        <v>6670286</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16700,57 +16700,48 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129108341</v>
+        <v>129110670</v>
       </c>
       <c r="B140" t="n">
-        <v>98633</v>
+        <v>92023</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>504</v>
+        <v>1619</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Apelticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Aurantiporus fissilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>706937</v>
+        <v>706880</v>
       </c>
       <c r="R140" t="n">
-        <v>6670745</v>
+        <v>6670333</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16802,52 +16793,65 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY140" t="inlineStr"/>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129110670</v>
+        <v>129108341</v>
       </c>
       <c r="B141" t="n">
-        <v>91995</v>
+        <v>98662</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1619</v>
+        <v>504</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Apelticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Aurantiporus fissilis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>706880</v>
+        <v>706937</v>
       </c>
       <c r="R141" t="n">
-        <v>6670333</v>
+        <v>6670745</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16899,18 +16903,14 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY141" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
         <v>129114059</v>
       </c>
       <c r="B142" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>129112389</v>
       </c>
       <c r="B143" t="n">
-        <v>102974</v>
+        <v>103003</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>129113907</v>
       </c>
       <c r="B144" t="n">
-        <v>87005</v>
+        <v>87033</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>129112698</v>
       </c>
       <c r="B145" t="n">
-        <v>86988</v>
+        <v>87016</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>129108937</v>
       </c>
       <c r="B146" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>129109792</v>
       </c>
       <c r="B147" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>129108051</v>
       </c>
       <c r="B148" t="n">
-        <v>98705</v>
+        <v>98734</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17586,48 +17586,48 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129112890</v>
+        <v>129112646</v>
       </c>
       <c r="B149" t="n">
-        <v>91113</v>
+        <v>99975</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>937</v>
+        <v>174</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>707141</v>
+        <v>707129</v>
       </c>
       <c r="R149" t="n">
-        <v>6670348</v>
+        <v>6670306</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17683,48 +17683,48 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129112466</v>
+        <v>129112890</v>
       </c>
       <c r="B150" t="n">
-        <v>91537</v>
+        <v>91141</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4660</v>
+        <v>937</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>707055</v>
+        <v>707141</v>
       </c>
       <c r="R150" t="n">
-        <v>6670286</v>
+        <v>6670348</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17780,10 +17780,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129112791</v>
+        <v>129114030</v>
       </c>
       <c r="B151" t="n">
-        <v>91610</v>
+        <v>91354</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17791,37 +17791,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5321</v>
+        <v>3215</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>707141</v>
+        <v>707151</v>
       </c>
       <c r="R151" t="n">
-        <v>6670348</v>
+        <v>6670622</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17877,32 +17877,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129111060</v>
+        <v>129112466</v>
       </c>
       <c r="B152" t="n">
-        <v>92043</v>
+        <v>91565</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5469</v>
+        <v>4660</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kärrvaxskinn</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phlebiodontia subochracea</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17912,13 +17912,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>706998</v>
+        <v>707055</v>
       </c>
       <c r="R152" t="n">
-        <v>6670322</v>
+        <v>6670286</v>
       </c>
       <c r="S152" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17974,10 +17974,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129112646</v>
+        <v>129112791</v>
       </c>
       <c r="B153" t="n">
-        <v>99946</v>
+        <v>91638</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17985,37 +17985,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>174</v>
+        <v>5321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>707129</v>
+        <v>707141</v>
       </c>
       <c r="R153" t="n">
-        <v>6670306</v>
+        <v>6670348</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18071,48 +18071,48 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129114030</v>
+        <v>129111060</v>
       </c>
       <c r="B154" t="n">
-        <v>91326</v>
+        <v>92071</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>3215</v>
+        <v>5469</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kärrvaxskinn</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phlebiodontia subochracea</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Bres.) Motato-Vásq. &amp; Gugliotta</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>707151</v>
+        <v>706998</v>
       </c>
       <c r="R154" t="n">
-        <v>6670622</v>
+        <v>6670322</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -18168,45 +18168,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129110999</v>
+        <v>129112925</v>
       </c>
       <c r="B155" t="n">
-        <v>92508</v>
+        <v>91141</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4769</v>
+        <v>937</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>707002</v>
+        <v>707185</v>
       </c>
       <c r="R155" t="n">
-        <v>6670297</v>
+        <v>6670371</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18265,45 +18265,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129113101</v>
+        <v>129110999</v>
       </c>
       <c r="B156" t="n">
-        <v>80149</v>
+        <v>92536</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>707194</v>
+        <v>707002</v>
       </c>
       <c r="R156" t="n">
-        <v>6670479</v>
+        <v>6670297</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18362,32 +18362,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129113068</v>
+        <v>129113101</v>
       </c>
       <c r="B157" t="n">
-        <v>110858</v>
+        <v>80175</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219711</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18397,13 +18397,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>707202</v>
+        <v>707194</v>
       </c>
       <c r="R157" t="n">
-        <v>6670431</v>
+        <v>6670479</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18459,32 +18459,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129112925</v>
+        <v>129113229</v>
       </c>
       <c r="B158" t="n">
-        <v>91113</v>
+        <v>92899</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>937</v>
+        <v>5964</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>707185</v>
+        <v>707145</v>
       </c>
       <c r="R158" t="n">
-        <v>6670371</v>
+        <v>6670534</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18556,10 +18556,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129113229</v>
+        <v>129113068</v>
       </c>
       <c r="B159" t="n">
-        <v>92871</v>
+        <v>110887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18567,21 +18567,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18591,13 +18591,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>707145</v>
+        <v>707202</v>
       </c>
       <c r="R159" t="n">
-        <v>6670534</v>
+        <v>6670431</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>129109134</v>
       </c>
       <c r="B160" t="n">
-        <v>98633</v>
+        <v>98662</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18759,10 +18759,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129108270</v>
+        <v>129112708</v>
       </c>
       <c r="B161" t="n">
-        <v>92847</v>
+        <v>110887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18770,34 +18770,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>706961</v>
+        <v>707129</v>
       </c>
       <c r="R161" t="n">
-        <v>6670741</v>
+        <v>6670306</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18856,45 +18856,56 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129112708</v>
+        <v>129111656</v>
       </c>
       <c r="B162" t="n">
-        <v>110858</v>
+        <v>90375</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219711</v>
+        <v>6003116</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Davidmusseron</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tricholoma ilkkae</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>Mort.Chr. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>707129</v>
+        <v>707000</v>
       </c>
       <c r="R162" t="n">
-        <v>6670306</v>
+        <v>6670196</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18935,8 +18946,24 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
+        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
@@ -18949,14 +18976,18 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY162" t="inlineStr"/>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129113903</v>
+        <v>129108270</v>
       </c>
       <c r="B163" t="n">
-        <v>92271</v>
+        <v>92875</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18964,34 +18995,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3298</v>
+        <v>4366</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>707129</v>
+        <v>706961</v>
       </c>
       <c r="R163" t="n">
-        <v>6670627</v>
+        <v>6670741</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19050,56 +19081,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129111656</v>
+        <v>129113903</v>
       </c>
       <c r="B164" t="n">
-        <v>90347</v>
+        <v>92299</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6003116</v>
+        <v>3298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Davidmusseron</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tricholoma ilkkae</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>707000</v>
+        <v>707129</v>
       </c>
       <c r="R164" t="n">
-        <v>6670196</v>
+        <v>6670627</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19140,24 +19160,8 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>Örtrik kustnära kalkbarrskog med beteshistorik. Stort inslag av gamla tallar. Asp, lönn och hassel rikligt. Fältskikt av blåsippsmattor, vispstarr, strävlosta (rikligt i partier), vårärt, hasselsprötmossa, kransmossa. Lerig(-sandig) morän och hällmarksmosaik. Växte i hotspot tillsammans med Phellodon melilotinus och Hydnellum rufoconcrescens.</t>
-        </is>
-      </c>
-      <c r="AL164" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Det fanns både gammal tall och gran vid växtplatsen.</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -19170,65 +19174,49 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129112386</v>
+        <v>129112397</v>
       </c>
       <c r="B165" t="n">
-        <v>99946</v>
+        <v>87016</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>174</v>
+        <v>460</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+          <t>(Cordier) Gillet</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>707049</v>
+        <v>707055</v>
       </c>
       <c r="R165" t="n">
-        <v>6670267</v>
+        <v>6670286</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19263,18 +19251,12 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Stort bestånd.</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -19293,10 +19275,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129114112</v>
+        <v>129108054</v>
       </c>
       <c r="B166" t="n">
-        <v>86968</v>
+        <v>98662</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19304,37 +19286,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3674</v>
+        <v>504</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>707154</v>
+        <v>707017</v>
       </c>
       <c r="R166" t="n">
-        <v>6670701</v>
+        <v>6670761</v>
       </c>
       <c r="S166" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19390,45 +19372,45 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129108500</v>
+        <v>129112545</v>
       </c>
       <c r="B167" t="n">
-        <v>88761</v>
+        <v>79689</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4394</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>706954</v>
+        <v>707088</v>
       </c>
       <c r="R167" t="n">
-        <v>6670717</v>
+        <v>6670309</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19487,45 +19469,57 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129112397</v>
+        <v>129112386</v>
       </c>
       <c r="B168" t="n">
-        <v>86988</v>
+        <v>99975</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>460</v>
+        <v>174</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>707055</v>
+        <v>707049</v>
       </c>
       <c r="R168" t="n">
-        <v>6670286</v>
+        <v>6670267</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19560,12 +19554,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Stort bestånd.</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -19584,10 +19584,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129108054</v>
+        <v>129114112</v>
       </c>
       <c r="B169" t="n">
-        <v>98633</v>
+        <v>86996</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19595,37 +19595,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>504</v>
+        <v>3674</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>707017</v>
+        <v>707154</v>
       </c>
       <c r="R169" t="n">
-        <v>6670761</v>
+        <v>6670701</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19681,45 +19681,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129112545</v>
+        <v>129108500</v>
       </c>
       <c r="B170" t="n">
-        <v>79663</v>
+        <v>88789</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>4394</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>707088</v>
+        <v>706954</v>
       </c>
       <c r="R170" t="n">
-        <v>6670309</v>
+        <v>6670717</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19778,10 +19778,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129109788</v>
+        <v>129107991</v>
       </c>
       <c r="B171" t="n">
-        <v>110858</v>
+        <v>8439</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19789,37 +19789,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>706790</v>
+        <v>706990</v>
       </c>
       <c r="R171" t="n">
-        <v>6670404</v>
+        <v>6670767</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19875,10 +19875,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129109813</v>
+        <v>129109788</v>
       </c>
       <c r="B172" t="n">
-        <v>100821</v>
+        <v>110887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19886,16 +19886,16 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>222771</v>
+        <v>219711</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -19975,7 +19975,7 @@
         <v>129109137</v>
       </c>
       <c r="B173" t="n">
-        <v>101823</v>
+        <v>101852</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20069,32 +20069,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129110603</v>
+        <v>129109813</v>
       </c>
       <c r="B174" t="n">
-        <v>102974</v>
+        <v>100850</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>223246</v>
+        <v>222771</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -20104,10 +20104,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>706848</v>
+        <v>706790</v>
       </c>
       <c r="R174" t="n">
-        <v>6670352</v>
+        <v>6670404</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20166,48 +20166,48 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129113794</v>
+        <v>129110603</v>
       </c>
       <c r="B175" t="n">
-        <v>87005</v>
+        <v>103003</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6003295</v>
+        <v>223246</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>707144</v>
+        <v>706848</v>
       </c>
       <c r="R175" t="n">
-        <v>6670568</v>
+        <v>6670352</v>
       </c>
       <c r="S175" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -20263,48 +20263,48 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129107991</v>
+        <v>129113794</v>
       </c>
       <c r="B176" t="n">
-        <v>8439</v>
+        <v>87033</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>106554</v>
+        <v>6003295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>706990</v>
+        <v>707144</v>
       </c>
       <c r="R176" t="n">
-        <v>6670767</v>
+        <v>6670568</v>
       </c>
       <c r="S176" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20360,32 +20360,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129108275</v>
+        <v>129108056</v>
       </c>
       <c r="B177" t="n">
-        <v>87027</v>
+        <v>98778</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20395,10 +20395,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>706961</v>
+        <v>707017</v>
       </c>
       <c r="R177" t="n">
-        <v>6670741</v>
+        <v>6670761</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20457,48 +20457,48 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129113803</v>
+        <v>129108275</v>
       </c>
       <c r="B178" t="n">
-        <v>91326</v>
+        <v>87055</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3215</v>
+        <v>449</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>707144</v>
+        <v>706961</v>
       </c>
       <c r="R178" t="n">
-        <v>6670568</v>
+        <v>6670741</v>
       </c>
       <c r="S178" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20554,10 +20554,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129108056</v>
+        <v>129113803</v>
       </c>
       <c r="B179" t="n">
-        <v>98749</v>
+        <v>91354</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20565,37 +20565,37 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>219862</v>
+        <v>3215</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>707017</v>
+        <v>707144</v>
       </c>
       <c r="R179" t="n">
-        <v>6670761</v>
+        <v>6670568</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20651,32 +20651,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129109796</v>
+        <v>129110679</v>
       </c>
       <c r="B180" t="n">
-        <v>91564</v>
+        <v>106384</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1205</v>
+        <v>220785</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20686,10 +20686,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>706790</v>
+        <v>706880</v>
       </c>
       <c r="R180" t="n">
-        <v>6670404</v>
+        <v>6670333</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20748,32 +20748,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129111132</v>
+        <v>129112011</v>
       </c>
       <c r="B181" t="n">
-        <v>91553</v>
+        <v>98778</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1202</v>
+        <v>219862</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20783,10 +20783,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>707028</v>
+        <v>707031</v>
       </c>
       <c r="R181" t="n">
-        <v>6670245</v>
+        <v>6670179</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20848,7 +20848,7 @@
         <v>129109438</v>
       </c>
       <c r="B182" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20942,48 +20942,48 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129110811</v>
+        <v>129108563</v>
       </c>
       <c r="B183" t="n">
-        <v>80149</v>
+        <v>98662</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>706912</v>
+        <v>706958</v>
       </c>
       <c r="R183" t="n">
-        <v>6670280</v>
+        <v>6670705</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21039,32 +21039,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129111077</v>
+        <v>129109796</v>
       </c>
       <c r="B184" t="n">
-        <v>80149</v>
+        <v>91592</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21074,13 +21074,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>706998</v>
+        <v>706790</v>
       </c>
       <c r="R184" t="n">
-        <v>6670322</v>
+        <v>6670404</v>
       </c>
       <c r="S184" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21136,32 +21136,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129112011</v>
+        <v>129111132</v>
       </c>
       <c r="B185" t="n">
-        <v>98749</v>
+        <v>91581</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>219862</v>
+        <v>1202</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21171,10 +21171,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>707031</v>
+        <v>707028</v>
       </c>
       <c r="R185" t="n">
-        <v>6670179</v>
+        <v>6670245</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21233,32 +21233,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129110679</v>
+        <v>129110811</v>
       </c>
       <c r="B186" t="n">
-        <v>106355</v>
+        <v>80175</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220785</v>
+        <v>6458</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21268,10 +21268,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>706880</v>
+        <v>706912</v>
       </c>
       <c r="R186" t="n">
-        <v>6670333</v>
+        <v>6670280</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21330,48 +21330,48 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129108563</v>
+        <v>129111077</v>
       </c>
       <c r="B187" t="n">
-        <v>98633</v>
+        <v>80175</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>706958</v>
+        <v>706998</v>
       </c>
       <c r="R187" t="n">
-        <v>6670705</v>
+        <v>6670322</v>
       </c>
       <c r="S187" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>129110639</v>
       </c>
       <c r="B188" t="n">
-        <v>99946</v>
+        <v>99975</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>129112656</v>
       </c>
       <c r="B189" t="n">
-        <v>92847</v>
+        <v>92875</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>129110767</v>
       </c>
       <c r="B190" t="n">
-        <v>103252</v>
+        <v>103281</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>129108900</v>
       </c>
       <c r="B191" t="n">
-        <v>86968</v>
+        <v>86996</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>129109832</v>
       </c>
       <c r="B192" t="n">
-        <v>91610</v>
+        <v>91638</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>129113814</v>
       </c>
       <c r="B193" t="n">
-        <v>86968</v>
+        <v>86996</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>129109340</v>
       </c>
       <c r="B194" t="n">
-        <v>86897</v>
+        <v>86925</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22128,48 +22128,48 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129112836</v>
+        <v>129109288</v>
       </c>
       <c r="B195" t="n">
-        <v>91777</v>
+        <v>91090</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1106</v>
+        <v>5741</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>707141</v>
+        <v>706876</v>
       </c>
       <c r="R195" t="n">
-        <v>6670348</v>
+        <v>6670589</v>
       </c>
       <c r="S195" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22225,48 +22225,48 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129109288</v>
+        <v>129112836</v>
       </c>
       <c r="B196" t="n">
-        <v>91062</v>
+        <v>91805</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5741</v>
+        <v>1106</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>706876</v>
+        <v>707141</v>
       </c>
       <c r="R196" t="n">
-        <v>6670589</v>
+        <v>6670348</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -22322,10 +22322,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129108939</v>
+        <v>129112425</v>
       </c>
       <c r="B197" t="n">
-        <v>110858</v>
+        <v>103281</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22333,16 +22333,16 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>219711</v>
+        <v>222002</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -22353,14 +22353,14 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>707027</v>
+        <v>707055</v>
       </c>
       <c r="R197" t="n">
-        <v>6670701</v>
+        <v>6670286</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22419,10 +22419,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129112425</v>
+        <v>129108939</v>
       </c>
       <c r="B198" t="n">
-        <v>103252</v>
+        <v>110887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22430,16 +22430,16 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>222002</v>
+        <v>219711</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -22450,14 +22450,14 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>707055</v>
+        <v>707027</v>
       </c>
       <c r="R198" t="n">
-        <v>6670286</v>
+        <v>6670701</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22519,7 +22519,7 @@
         <v>129109238</v>
       </c>
       <c r="B199" t="n">
-        <v>104198</v>
+        <v>104227</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22613,10 +22613,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129112733</v>
+        <v>129111205</v>
       </c>
       <c r="B200" t="n">
-        <v>90317</v>
+        <v>92877</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22624,23 +22624,19 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1595</v>
+        <v>6047725</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
@@ -22648,10 +22644,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>707129</v>
+        <v>707000</v>
       </c>
       <c r="R200" t="n">
-        <v>6670306</v>
+        <v>6670196</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22706,14 +22702,18 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY200" t="inlineStr"/>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129112410</v>
+        <v>129108856</v>
       </c>
       <c r="B201" t="n">
-        <v>89562</v>
+        <v>98662</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22721,34 +22721,43 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5581</v>
+        <v>504</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Gulfotsskölding</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Pluteus romellii</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Britzelm.) Sacc.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>707055</v>
+        <v>707027</v>
       </c>
       <c r="R201" t="n">
-        <v>6670286</v>
+        <v>6670701</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22807,32 +22816,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129112379</v>
+        <v>129112410</v>
       </c>
       <c r="B202" t="n">
-        <v>102974</v>
+        <v>89590</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>223246</v>
+        <v>5581</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gulfotsskölding</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Pluteus romellii</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Britzelm.) Sacc.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22842,13 +22851,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>707012</v>
+        <v>707055</v>
       </c>
       <c r="R202" t="n">
-        <v>6670187</v>
+        <v>6670286</v>
       </c>
       <c r="S202" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22904,30 +22913,34 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129111205</v>
+        <v>129112405</v>
       </c>
       <c r="B203" t="n">
-        <v>92849</v>
+        <v>91141</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6047725</v>
+        <v>937</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr"/>
+          <t>Lentaria epichnoa</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
@@ -22935,10 +22948,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>707000</v>
+        <v>707055</v>
       </c>
       <c r="R203" t="n">
-        <v>6670196</v>
+        <v>6670286</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22993,40 +23006,36 @@
           <t>Viktor Lund, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY203" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129112405</v>
+        <v>129112733</v>
       </c>
       <c r="B204" t="n">
-        <v>91113</v>
+        <v>90345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>937</v>
+        <v>1595</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -23036,10 +23045,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>707055</v>
+        <v>707129</v>
       </c>
       <c r="R204" t="n">
-        <v>6670286</v>
+        <v>6670306</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23098,57 +23107,48 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129108856</v>
+        <v>129112379</v>
       </c>
       <c r="B205" t="n">
-        <v>98633</v>
+        <v>103003</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>504</v>
+        <v>223246</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>707027</v>
+        <v>707012</v>
       </c>
       <c r="R205" t="n">
-        <v>6670701</v>
+        <v>6670187</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>129109887</v>
       </c>
       <c r="B206" t="n">
-        <v>88759</v>
+        <v>88787</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23301,10 +23301,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129110527</v>
+        <v>129108973</v>
       </c>
       <c r="B207" t="n">
-        <v>4995</v>
+        <v>87099</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23312,34 +23312,30 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100517</v>
+        <v>3624</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Åttafläckig praktbagge</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Buprestis octoguttata</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>706802</v>
+        <v>707027</v>
       </c>
       <c r="R207" t="n">
-        <v>6670363</v>
+        <v>6670701</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23398,30 +23394,34 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129108973</v>
+        <v>129108444</v>
       </c>
       <c r="B208" t="n">
-        <v>87071</v>
+        <v>91116</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>3624</v>
+        <v>5747</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
@@ -23429,10 +23429,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>707027</v>
+        <v>706954</v>
       </c>
       <c r="R208" t="n">
-        <v>6670701</v>
+        <v>6670717</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23491,48 +23491,48 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129112015</v>
+        <v>129108141</v>
       </c>
       <c r="B209" t="n">
-        <v>87005</v>
+        <v>92899</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>707031</v>
+        <v>707011</v>
       </c>
       <c r="R209" t="n">
-        <v>6670179</v>
+        <v>6670734</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23588,10 +23588,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129112905</v>
+        <v>129112015</v>
       </c>
       <c r="B210" t="n">
-        <v>80149</v>
+        <v>87033</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23599,34 +23599,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6458</v>
+        <v>6003295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>707166</v>
+        <v>707031</v>
       </c>
       <c r="R210" t="n">
-        <v>6670369</v>
+        <v>6670179</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23688,7 +23688,7 @@
         <v>129110564</v>
       </c>
       <c r="B211" t="n">
-        <v>91610</v>
+        <v>91638</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23782,45 +23782,45 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129108444</v>
+        <v>129112905</v>
       </c>
       <c r="B212" t="n">
-        <v>91088</v>
+        <v>80175</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5747</v>
+        <v>6458</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>706954</v>
+        <v>707166</v>
       </c>
       <c r="R212" t="n">
-        <v>6670717</v>
+        <v>6670369</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23879,10 +23879,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129108141</v>
+        <v>129110527</v>
       </c>
       <c r="B213" t="n">
-        <v>92871</v>
+        <v>4995</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23890,37 +23890,37 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>5964</v>
+        <v>100517</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Åttafläckig praktbagge</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Buprestis octoguttata</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>707011</v>
+        <v>706802</v>
       </c>
       <c r="R213" t="n">
-        <v>6670734</v>
+        <v>6670363</v>
       </c>
       <c r="S213" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23976,10 +23976,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129108076</v>
+        <v>129111662</v>
       </c>
       <c r="B214" t="n">
-        <v>101823</v>
+        <v>92875</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23987,37 +23987,37 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221235</v>
+        <v>4366</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>707017</v>
+        <v>707011</v>
       </c>
       <c r="R214" t="n">
-        <v>6670761</v>
+        <v>6670220</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24073,48 +24073,48 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129113073</v>
+        <v>129114035</v>
       </c>
       <c r="B215" t="n">
-        <v>80149</v>
+        <v>86834</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6458</v>
+        <v>3762</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>707212</v>
+        <v>707165</v>
       </c>
       <c r="R215" t="n">
-        <v>6670436</v>
+        <v>6670655</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24170,10 +24170,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129111662</v>
+        <v>129110955</v>
       </c>
       <c r="B216" t="n">
-        <v>92847</v>
+        <v>86834</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24181,21 +24181,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24205,13 +24205,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>707011</v>
+        <v>706983</v>
       </c>
       <c r="R216" t="n">
-        <v>6670220</v>
+        <v>6670276</v>
       </c>
       <c r="S216" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -24267,48 +24267,48 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129114035</v>
+        <v>129113073</v>
       </c>
       <c r="B217" t="n">
-        <v>86806</v>
+        <v>80175</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>3762</v>
+        <v>6458</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>707165</v>
+        <v>707212</v>
       </c>
       <c r="R217" t="n">
-        <v>6670655</v>
+        <v>6670436</v>
       </c>
       <c r="S217" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24364,10 +24364,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129110955</v>
+        <v>129108076</v>
       </c>
       <c r="B218" t="n">
-        <v>86806</v>
+        <v>101852</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24375,34 +24375,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>3762</v>
+        <v>221235</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>706983</v>
+        <v>707017</v>
       </c>
       <c r="R218" t="n">
-        <v>6670276</v>
+        <v>6670761</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24464,7 +24464,7 @@
         <v>129108289</v>
       </c>
       <c r="B219" t="n">
-        <v>43982</v>
+        <v>43985</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>129111122</v>
       </c>
       <c r="B220" t="n">
-        <v>91788</v>
+        <v>91816</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24659,10 +24659,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129112862</v>
+        <v>129108567</v>
       </c>
       <c r="B221" t="n">
-        <v>96073</v>
+        <v>86834</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24670,37 +24670,37 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2818</v>
+        <v>3762</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>707141</v>
+        <v>706958</v>
       </c>
       <c r="R221" t="n">
-        <v>6670348</v>
+        <v>6670705</v>
       </c>
       <c r="S221" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24756,10 +24756,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129108567</v>
+        <v>129112111</v>
       </c>
       <c r="B222" t="n">
-        <v>86806</v>
+        <v>92899</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24767,34 +24767,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Bergbofjärden, Upl</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>706958</v>
+        <v>707012</v>
       </c>
       <c r="R222" t="n">
-        <v>6670705</v>
+        <v>6670187</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -24853,10 +24853,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129112111</v>
+        <v>129112862</v>
       </c>
       <c r="B223" t="n">
-        <v>92871</v>
+        <v>96102</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24864,37 +24864,37 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5964</v>
+        <v>2818</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Bergbofjärden, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>707012</v>
+        <v>707141</v>
       </c>
       <c r="R223" t="n">
-        <v>6670187</v>
+        <v>6670348</v>
       </c>
       <c r="S223" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>129108458</v>
       </c>
       <c r="B224" t="n">
-        <v>80374</v>
+        <v>80400</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25042,45 +25042,54 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129112901</v>
+        <v>129108653</v>
       </c>
       <c r="B225" t="n">
-        <v>91113</v>
+        <v>98662</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>937</v>
+        <v>504</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Ladrudan, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>707166</v>
+        <v>706984</v>
       </c>
       <c r="R225" t="n">
-        <v>6670369</v>
+        <v>6670689</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25139,54 +25148,45 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129108653</v>
+        <v>129112901</v>
       </c>
       <c r="B226" t="n">
-        <v>98633</v>
+        <v>91141</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>504</v>
+        <v>937</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Ladrudan, Upl</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>706984</v>
+        <v>707166</v>
       </c>
       <c r="R226" t="n">
-        <v>6670689</v>
+        <v>6670369</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25248,7 +25248,7 @@
         <v>129108591</v>
       </c>
       <c r="B227" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>129108343</v>
       </c>
       <c r="B228" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>129108561</v>
       </c>
       <c r="B229" t="n">
-        <v>101823</v>
+        <v>101852</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>129109815</v>
       </c>
       <c r="B230" t="n">
-        <v>101823</v>
+        <v>101852</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>129112746</v>
       </c>
       <c r="B231" t="n">
-        <v>102974</v>
+        <v>103003</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25730,10 +25730,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129108929</v>
+        <v>129113799</v>
       </c>
       <c r="B232" t="n">
-        <v>92871</v>
+        <v>92536</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25741,37 +25741,37 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>707027</v>
+        <v>707144</v>
       </c>
       <c r="R232" t="n">
-        <v>6670701</v>
+        <v>6670568</v>
       </c>
       <c r="S232" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -25827,10 +25827,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129113799</v>
+        <v>129108929</v>
       </c>
       <c r="B233" t="n">
-        <v>92508</v>
+        <v>92899</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25838,37 +25838,37 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>707144</v>
+        <v>707027</v>
       </c>
       <c r="R233" t="n">
-        <v>6670568</v>
+        <v>6670701</v>
       </c>
       <c r="S233" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -26021,45 +26021,45 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129114064</v>
+        <v>129108059</v>
       </c>
       <c r="B235" t="n">
-        <v>92327</v>
+        <v>92536</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>232138</v>
+        <v>4769</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Prästskatens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>707168</v>
+        <v>707017</v>
       </c>
       <c r="R235" t="n">
-        <v>6670669</v>
+        <v>6670761</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26121,7 +26121,7 @@
         <v>129108620</v>
       </c>
       <c r="B236" t="n">
-        <v>98749</v>
+        <v>98778</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>129109794</v>
       </c>
       <c r="B237" t="n">
-        <v>104198</v>
+        <v>104227</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26312,45 +26312,45 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129108059</v>
+        <v>129114064</v>
       </c>
       <c r="B238" t="n">
-        <v>92508</v>
+        <v>92355</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4769</v>
+        <v>232138</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Prästskatens naturreservat, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>707017</v>
+        <v>707168</v>
       </c>
       <c r="R238" t="n">
-        <v>6670761</v>
+        <v>6670669</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26412,7 +26412,7 @@
         <v>129112433</v>
       </c>
       <c r="B239" t="n">
-        <v>89567</v>
+        <v>89595</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY239"/>
+  <dimension ref="A1:AY240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26508,6 +26508,115 @@
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>130108048</v>
+      </c>
+      <c r="B240" t="n">
+        <v>86933</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>248952</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Blåfotad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Cortinarius barbaricus</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>(Brandrud) Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Simphällarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>707120</v>
+      </c>
+      <c r="R240" t="n">
+        <v>6670803</v>
+      </c>
+      <c r="S240" t="n">
+        <v>10</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
+      <c r="AG240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Mattias Andersson, Kristoffer Stighäll, Bengt Boström, Birgitta Wasstorp, Lukas Stenbäck, Mats Nordin, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -26513,7 +26513,7 @@
         <v>130108048</v>
       </c>
       <c r="B240" t="n">
-        <v>86949</v>
+        <v>87036</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -16292,7 +16292,7 @@
         <v>0</v>
       </c>
       <c r="AE135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG135" t="b">
         <v>0</v>
@@ -20534,7 +20534,7 @@
         <v>0</v>
       </c>
       <c r="AE178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG178" t="b">
         <v>0</v>
@@ -26001,7 +26001,7 @@
         <v>0</v>
       </c>
       <c r="AE234" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG234" t="b">
         <v>0</v>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -26513,7 +26513,7 @@
         <v>130108048</v>
       </c>
       <c r="B240" t="n">
-        <v>87036</v>
+        <v>87039</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY240"/>
+  <dimension ref="A1:AY241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26617,6 +26617,107 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>129111260</v>
+      </c>
+      <c r="B241" t="n">
+        <v>93149</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp agg.</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Bergbofjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>707000</v>
+      </c>
+      <c r="R241" t="n">
+        <v>6670196</v>
+      </c>
+      <c r="S241" t="n">
+        <v>10</v>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF241" t="inlineStr"/>
+      <c r="AG241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT241" t="inlineStr"/>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -26622,7 +26622,7 @@
         <v>129111260</v>
       </c>
       <c r="B241" t="n">
-        <v>93149</v>
+        <v>93155</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -26622,7 +26622,7 @@
         <v>129111260</v>
       </c>
       <c r="B241" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -26622,7 +26622,7 @@
         <v>129111260</v>
       </c>
       <c r="B241" t="n">
-        <v>93158</v>
+        <v>93163</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -26622,7 +26622,7 @@
         <v>129111260</v>
       </c>
       <c r="B241" t="n">
-        <v>93163</v>
+        <v>93165</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -26622,7 +26622,7 @@
         <v>129111260</v>
       </c>
       <c r="B241" t="n">
-        <v>93206</v>
+        <v>93209</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY241"/>
+  <dimension ref="A1:AY242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26718,6 +26718,115 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>133402166</v>
+      </c>
+      <c r="B242" t="n">
+        <v>87548</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>451</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Sotbandad spindling</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Cortinarius fuscoperonatus</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Väster-Kulla, NW Ladudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>707233</v>
+      </c>
+      <c r="R242" t="n">
+        <v>6670822</v>
+      </c>
+      <c r="S242" t="n">
+        <v>155</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT242" t="inlineStr"/>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>Eva Grönlund, Birgitta Wasstorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -26723,7 +26723,7 @@
         <v>133402166</v>
       </c>
       <c r="B242" t="n">
-        <v>87548</v>
+        <v>87550</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -26723,7 +26723,7 @@
         <v>133402166</v>
       </c>
       <c r="B242" t="n">
-        <v>87550</v>
+        <v>87558</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -26723,7 +26723,7 @@
         <v>133402166</v>
       </c>
       <c r="B242" t="n">
-        <v>87558</v>
+        <v>87576</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>

--- a/artfynd/A 55023-2025 artfynd.xlsx
+++ b/artfynd/A 55023-2025 artfynd.xlsx
@@ -26723,7 +26723,7 @@
         <v>133402166</v>
       </c>
       <c r="B242" t="n">
-        <v>87576</v>
+        <v>87586</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
